--- a/files/BUS331_Investment_Committee_Decision_Record_Student.xlsx
+++ b/files/BUS331_Investment_Committee_Decision_Record_Student.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Re0e3e2e2770b416e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMMITTEE ROSTER" sheetId="2" r:id="R21aa397ec988406c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 1" sheetId="3" r:id="Rd75abb7323fc4e18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 2 CLIENT 1" sheetId="4" r:id="Rc798855967a14e07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 2 CLIENT 2" sheetId="5" r:id="Rfafa407a8304407c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 2 CLIENT 3" sheetId="6" r:id="Ra5b103e2246c4ddf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 3" sheetId="7" r:id="Rd611c0b1f046436a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI AUDIT LOG" sheetId="8" r:id="R9ee6ec6e29f64bb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Re5d9bb9fc6394467"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMMITTEE ROSTER" sheetId="2" r:id="Rcf5eb79eba084c63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANALYST DECISION LOG" sheetId="3" r:id="Rcf54d98cd75449b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 1" sheetId="4" r:id="R07842bd965ca4690"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 2 CLIENT 1" sheetId="5" r:id="R0b2893e44b3a4b14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 2 CLIENT 2" sheetId="6" r:id="R903d9252853245b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 2 CLIENT 3" sheetId="7" r:id="Rd7ba186e58af45a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 3" sheetId="8" r:id="R9bed630886b9475c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI AUDIT LOG" sheetId="9" r:id="R7ebd1a91354543e3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +24,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="mmm d, yyyy"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -101,8 +102,14 @@
       <x:color rgb="FF4B6073"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF8A3027"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -144,8 +151,13 @@
         <x:fgColor rgb="FFF5F8FA"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFBE3DF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="19">
+  <x:borders count="22">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -199,6 +211,28 @@
     </x:border>
     <x:border>
       <x:left style="thin">
+        <x:color rgb="FF0B1F35"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FF0B1F35"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF0B1F35"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF0B1F35"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF0B1F35"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF0B1F35"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
         <x:color rgb="FFD9B973"/>
       </x:left>
       <x:right style="thin">
@@ -234,6 +268,33 @@
       <x:top style="thin">
         <x:color rgb="FFD9B973"/>
       </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9B973"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9B973"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9B973"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9B973"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9B973"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD9B973"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD9B973"/>
+      </x:top>
     </x:border>
     <x:border>
       <x:right style="thin">
@@ -262,6 +323,11 @@
       </x:bottom>
     </x:border>
     <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9B973"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
       <x:right style="thin">
         <x:color rgb="FFD9B973"/>
       </x:right>
@@ -270,14 +336,11 @@
       </x:bottom>
     </x:border>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD9B973"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FFD9B973"/>
+      <x:top style="medium">
+        <x:color rgb="FF0B1F35"/>
       </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD9B973"/>
+      <x:bottom style="medium">
+        <x:color rgb="FF0B1F35"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -288,32 +351,11 @@
         <x:color rgb="FFD9B973"/>
       </x:bottom>
     </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFD9B973"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD9B973"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD9B973"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:top style="thin">
-        <x:color rgb="FFD9B973"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:bottom style="thin">
-        <x:color rgb="FFD9B973"/>
-      </x:bottom>
-    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="99">
+  <x:cellXfs count="117">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -364,31 +406,36 @@
     <x:xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -414,124 +461,145 @@
     <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="12" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="12" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="21">
+  <x:dxfs count="49">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -595,6 +663,314 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFFF1C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF17623E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDF4E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7A5600"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7A5600"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF17623E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDF4E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7A5600"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7A5600"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF17623E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDF4E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7A5600"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7A5600"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF17623E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDF4E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7A5600"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7A5600"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3027"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFBE3DF"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -986,7 +1362,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>One auditable record for every approval gate | Student template</x:v>
+        <x:v>Analyst Decision Log + one auditable record for every approval gate | Student template</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -998,7 +1374,7 @@
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="9" t="str">
-        <x:v>Use this workbook to show how analysis became a committee decision. Complete the roster first, then use one decision sheet at each gate. Phase 2 requires a separate vote for each assigned client.</x:v>
+        <x:v>Use this workbook to show how analysis became a committee decision. Complete the roster, enter human-first Phase 1 judgments in the Analyst Decision Log, then use one decision sheet at each gate. Phase 2 requires a separate vote for each assigned client.</x:v>
       </x:c>
       <x:c r="B4" s="9"/>
       <x:c r="C4" s="9"/>
@@ -1021,10 +1397,10 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
-        <x:v>Before the meeting</x:v>
+        <x:v>Initial judgment</x:v>
       </x:c>
       <x:c r="B7" s="16" t="str">
-        <x:v>Circulate the pre-read and complete the evidence table.</x:v>
+        <x:v>Before AI use, each role records one provisional judgment for each assigned client and names the fact or assumption driving it.</x:v>
       </x:c>
       <x:c r="C7" s="16" t="str"/>
       <x:c r="D7" s="16" t="str"/>
@@ -1034,10 +1410,10 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="str">
-        <x:v>During challenge</x:v>
+        <x:v>AI interview + challenge</x:v>
       </x:c>
       <x:c r="B8" s="16" t="str">
-        <x:v>Record the strongest counterargument, source, and unresolved issue.</x:v>
+        <x:v>Summarize the bounded client interview and the strongest counterargument; do not paste a transcript as analysis.</x:v>
       </x:c>
       <x:c r="C8" s="16" t="str"/>
       <x:c r="D8" s="16" t="str"/>
@@ -1047,10 +1423,10 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
-        <x:v>At the vote</x:v>
+        <x:v>Human verification</x:v>
       </x:c>
       <x:c r="B9" s="16" t="str">
-        <x:v>Each of the four committee members votes Approve, Revise, or Reject.</x:v>
+        <x:v>Check client facts, calculations, and outside claims with an approved source and as-of date.</x:v>
       </x:c>
       <x:c r="C9" s="16" t="str"/>
       <x:c r="D9" s="16" t="str"/>
@@ -1060,10 +1436,10 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="14" t="str">
-        <x:v>After the vote</x:v>
+        <x:v>Final reasoning</x:v>
       </x:c>
       <x:c r="B10" s="16" t="str">
-        <x:v>Record dissent, conditions, action owners, due dates, and evidence of completion.</x:v>
+        <x:v>State what changed, the final judgment, and the guardrail later security and portfolio decisions must honor.</x:v>
       </x:c>
       <x:c r="C10" s="16" t="str"/>
       <x:c r="D10" s="16" t="str"/>
@@ -1073,10 +1449,10 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="14" t="str">
-        <x:v>Before the next gate</x:v>
+        <x:v>Committee gate</x:v>
       </x:c>
       <x:c r="B11" s="16" t="str">
-        <x:v>Confirm revisions are complete and the decision status is APPROVED.</x:v>
+        <x:v>Circulate the evidence, challenge the recommendation, vote, and record dissent, conditions, owners, and actions.</x:v>
       </x:c>
       <x:c r="C11" s="16" t="str"/>
       <x:c r="D11" s="16" t="str"/>
@@ -1172,21 +1548,31 @@
         <x:v>Overall readiness</x:v>
       </x:c>
       <x:c r="B21" s="28" t="str">
-        <x:f>IF(COUNTIF(C15:C19,"INCOMPLETE")&gt;0,"INCOMPLETE",IF(COUNTIF(C15:C19,"REVISION REQUIRED")&gt;0,"REVISION REQUIRED","READY FOR FINAL DEFENSE"))</x:f>
-        <x:v>INCOMPLETE</x:v>
+        <x:f>IF(B23&lt;&gt;"READY FOR PHASE 1 GATE","PHASE 1 LOG INCOMPLETE",IF(COUNTIF(C15:C19,"INCOMPLETE")&gt;0,"INCOMPLETE",IF(COUNTIF(C15:C19,"REVISION REQUIRED")&gt;0,"REVISION REQUIRED","READY FOR FINAL DEFENSE")))</x:f>
+        <x:v>PHASE 1 LOG INCOMPLETE</x:v>
       </x:c>
       <x:c r="C21" s="29"/>
     </x:row>
-    <x:row r="24" ht="28" customHeight="1">
-      <x:c r="A24" s="32" t="str">
+    <x:row r="23">
+      <x:c r="A23" s="25" t="str">
+        <x:v>Phase 1 log readiness</x:v>
+      </x:c>
+      <x:c r="B23" s="33" t="str">
+        <x:f>'ANALYST DECISION LOG'!K40</x:f>
+        <x:v>ENTER 3 CLIENTS</x:v>
+      </x:c>
+      <x:c r="C23" s="34"/>
+    </x:row>
+    <x:row r="25" ht="28" customHeight="1">
+      <x:c r="A25" s="37" t="str">
         <x:v>Canvas remains the authority for due dates, submission links, and course-grade weights.</x:v>
       </x:c>
-      <x:c r="B24" s="32"/>
-      <x:c r="C24" s="32"/>
-      <x:c r="D24" s="32"/>
-      <x:c r="E24" s="32"/>
-      <x:c r="F24" s="32"/>
-      <x:c r="G24" s="32"/>
+      <x:c r="B25" s="37"/>
+      <x:c r="C25" s="37"/>
+      <x:c r="D25" s="37"/>
+      <x:c r="E25" s="37"/>
+      <x:c r="F25" s="37"/>
+      <x:c r="G25" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1201,7 +1587,8 @@
     <x:mergeCell ref="B11:G11"/>
     <x:mergeCell ref="A13:H13"/>
     <x:mergeCell ref="B21:C21"/>
-    <x:mergeCell ref="A24:G24"/>
+    <x:mergeCell ref="B23:C23"/>
+    <x:mergeCell ref="A25:G25"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="C15:C19">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="APPROVED"/>
@@ -1212,6 +1599,15 @@
     <x:cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="APPROVED"/>
     <x:cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="REVISION"/>
     <x:cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="INCOMPLETE"/>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="B23:C23">
+    <x:cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="EVIDENCE READY"/>
+    <x:cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="REVISE"/>
+    <x:cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="INCOMPLETE"/>
+    <x:cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="MINIMUM"/>
+    <x:cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="REVIEW"/>
+    <x:cfRule type="containsText" dxfId="11" priority="12" operator="containsText" text="MISSING"/>
+    <x:cfRule type="containsText" dxfId="12" priority="13" operator="containsText" text="ENTER"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1256,95 +1652,95 @@
       <x:c r="H2" s="6"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="46" t="str">
+      <x:c r="A4" s="51" t="str">
         <x:v>Committee seat</x:v>
       </x:c>
-      <x:c r="B4" s="46" t="str">
+      <x:c r="B4" s="51" t="str">
         <x:v>Member name</x:v>
       </x:c>
-      <x:c r="C4" s="46" t="str">
+      <x:c r="C4" s="51" t="str">
         <x:v>Standing mandate</x:v>
       </x:c>
-      <x:c r="D4" s="46" t="str">
+      <x:c r="D4" s="51" t="str">
         <x:v>Phase 1 responsibility</x:v>
       </x:c>
-      <x:c r="E4" s="46" t="str">
+      <x:c r="E4" s="51" t="str">
         <x:v>Phase 2 responsibility</x:v>
       </x:c>
-      <x:c r="F4" s="46" t="str">
+      <x:c r="F4" s="51" t="str">
         <x:v>Phase 3 responsibility</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="72" customHeight="1">
-      <x:c r="A5" s="47" t="str">
-        <x:v>Committee Chair &amp; Client Mandate Lead</x:v>
-      </x:c>
-      <x:c r="B5" s="48" t="str"/>
-      <x:c r="C5" s="49" t="str">
-        <x:v>Own the meeting process, client suitability, decision record, and integration across all three phases.</x:v>
-      </x:c>
-      <x:c r="D5" s="49" t="str">
-        <x:v>Lead the RRTTLLU review, resolve client constraint conflicts, and frame the approval motion.</x:v>
-      </x:c>
-      <x:c r="E5" s="49" t="str">
-        <x:v>Test whether proposed allocations and securities stay inside each approved mandate.</x:v>
-      </x:c>
-      <x:c r="F5" s="49" t="str">
-        <x:v>Open the committee meeting, state the recommendation, record the vote, and close with actions.</x:v>
+      <x:c r="A5" s="52" t="str">
+        <x:v>Client and Macro Strategist</x:v>
+      </x:c>
+      <x:c r="B5" s="53" t="str"/>
+      <x:c r="C5" s="54" t="str">
+        <x:v>Own client discovery, the 12-month market view, IPS objectives and constraints, and the handoff from client needs to investment criteria.</x:v>
+      </x:c>
+      <x:c r="D5" s="54" t="str">
+        <x:v>Lead the client interview, document goals and RRTTLLU constraints, establish the macro context, and name unresolved information gaps.</x:v>
+      </x:c>
+      <x:c r="E5" s="54" t="str">
+        <x:v>Test whether proposed allocations and securities fit the approved client mandate and the committee's market view.</x:v>
+      </x:c>
+      <x:c r="F5" s="54" t="str">
+        <x:v>Defend client suitability, the macro assumptions, and the line from discovered need to recommendation.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="72" customHeight="1">
-      <x:c r="A6" s="47" t="str">
-        <x:v>Markets &amp; Economic Strategist</x:v>
-      </x:c>
-      <x:c r="B6" s="48" t="str"/>
-      <x:c r="C6" s="49" t="str">
-        <x:v>Own the 12-month macro thesis, scenario probabilities, data provenance, and transmission logic.</x:v>
-      </x:c>
-      <x:c r="D6" s="49" t="str">
-        <x:v>Build the human-first macro read, compare it with consensus, and propose base and bear scenarios.</x:v>
-      </x:c>
-      <x:c r="E6" s="49" t="str">
-        <x:v>Translate the approved thesis into expected returns, volatility, correlations, and macro filters.</x:v>
-      </x:c>
-      <x:c r="F6" s="49" t="str">
-        <x:v>Defend the market view and explain why the recommendation should work under the base case.</x:v>
+      <x:c r="A6" s="52" t="str">
+        <x:v>Fixed-Income Analyst</x:v>
+      </x:c>
+      <x:c r="B6" s="53" t="str"/>
+      <x:c r="C6" s="54" t="str">
+        <x:v>Own the income, capital-preservation, maturity, duration, credit-quality, liquidity, and tax questions that shape the fixed-income sleeve.</x:v>
+      </x:c>
+      <x:c r="D6" s="54" t="str">
+        <x:v>Translate cash-flow needs, time horizon, liquidity, taxes, and loss capacity into fixed-income questions and provisional guardrails.</x:v>
+      </x:c>
+      <x:c r="E6" s="54" t="str">
+        <x:v>Analyze yields, duration, credit, liquidity, and structure; recommend fixed-income exposures that meet the approved guardrails.</x:v>
+      </x:c>
+      <x:c r="F6" s="54" t="str">
+        <x:v>Defend the portfolio's income, capital-preservation, interest-rate, and credit-risk trade-offs.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="72" customHeight="1">
-      <x:c r="A7" s="47" t="str">
-        <x:v>Portfolio Construction Lead</x:v>
-      </x:c>
-      <x:c r="B7" s="48" t="str"/>
-      <x:c r="C7" s="49" t="str">
-        <x:v>Own capital-market expectations, optimization, security selection, allocation, and implementation feasibility.</x:v>
-      </x:c>
-      <x:c r="D7" s="49" t="str">
-        <x:v>Identify the portfolio decisions that the approved market view and client mandates must support.</x:v>
-      </x:c>
-      <x:c r="E7" s="49" t="str">
-        <x:v>Run the CME and Solver work, select securities, document weights, and propose implementation trades.</x:v>
-      </x:c>
-      <x:c r="F7" s="49" t="str">
-        <x:v>Defend portfolio construction, security-level choices, and the path from evidence to weights.</x:v>
+      <x:c r="A7" s="52" t="str">
+        <x:v>Fund and ETF Analyst</x:v>
+      </x:c>
+      <x:c r="B7" s="53" t="str"/>
+      <x:c r="C7" s="54" t="str">
+        <x:v>Own pooled-vehicle due diligence, diversification, benchmark fit, fees, liquidity, tax considerations, and active-versus-passive implementation.</x:v>
+      </x:c>
+      <x:c r="D7" s="54" t="str">
+        <x:v>Identify the client's diversification, access, liquidity, cost, tax, values, and vehicle requirements before screening products.</x:v>
+      </x:c>
+      <x:c r="E7" s="54" t="str">
+        <x:v>Evaluate funds and ETFs using objective, holdings, benchmark, fees, liquidity, tax efficiency, and tracking evidence.</x:v>
+      </x:c>
+      <x:c r="F7" s="54" t="str">
+        <x:v>Defend vehicle selection, implementation feasibility, diversification, and product-level due diligence.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="72" customHeight="1">
-      <x:c r="A8" s="47" t="str">
-        <x:v>Risk, Controls &amp; Challenge Lead</x:v>
-      </x:c>
-      <x:c r="B8" s="48" t="str"/>
-      <x:c r="C8" s="49" t="str">
-        <x:v>Own independent challenge, stress testing, hedge analysis, the AI audit, and mandate-breach escalation.</x:v>
-      </x:c>
-      <x:c r="D8" s="49" t="str">
-        <x:v>Challenge scenario assumptions, verify sources, and define the evidence required at the first gate.</x:v>
-      </x:c>
-      <x:c r="E8" s="49" t="str">
-        <x:v>Run the bear-case stress test, compare hedges, identify breaches, and require corrective action.</x:v>
-      </x:c>
-      <x:c r="F8" s="49" t="str">
-        <x:v>Present the strongest downside case and lead preparation for adversarial Q&amp;A.</x:v>
+      <x:c r="A8" s="52" t="str">
+        <x:v>Portfolio Manager and Risk Analyst</x:v>
+      </x:c>
+      <x:c r="B8" s="53" t="str"/>
+      <x:c r="C8" s="54" t="str">
+        <x:v>Own portfolio integration, risk capacity versus willingness, the drawdown tripwire, decision-log quality, stress testing, and mandate-breach escalation.</x:v>
+      </x:c>
+      <x:c r="D8" s="54" t="str">
+        <x:v>Reconcile risk capacity and willingness, set provisional portfolio guardrails, challenge assumptions, and audit the Analyst Decision Log.</x:v>
+      </x:c>
+      <x:c r="E8" s="54" t="str">
+        <x:v>Integrate the allocation, run bear-case stress tests, compare mitigants, identify breaches, and require corrective action.</x:v>
+      </x:c>
+      <x:c r="F8" s="54" t="str">
+        <x:v>State the integrated recommendation, present the strongest downside case, and lead preparation for adversarial Q&amp;A.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="23" customHeight="1">
@@ -1358,7 +1754,7 @@
       <x:c r="F10" s="11"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="51" t="str">
+      <x:c r="A11" s="56" t="str">
         <x:v>Evidence before opinion</x:v>
       </x:c>
       <x:c r="B11" s="16" t="str">
@@ -1370,7 +1766,7 @@
       <x:c r="F11" s="16" t="str"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="51" t="str">
+      <x:c r="A12" s="56" t="str">
         <x:v>Challenge the idea</x:v>
       </x:c>
       <x:c r="B12" s="16" t="str">
@@ -1382,7 +1778,7 @@
       <x:c r="F12" s="16" t="str"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="51" t="str">
+      <x:c r="A13" s="56" t="str">
         <x:v>No silent consent</x:v>
       </x:c>
       <x:c r="B13" s="16" t="str">
@@ -1394,7 +1790,7 @@
       <x:c r="F13" s="16" t="str"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="51" t="str">
+      <x:c r="A14" s="56" t="str">
         <x:v>No mandate breach</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
@@ -1406,7 +1802,7 @@
       <x:c r="F14" s="16" t="str"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="51" t="str">
+      <x:c r="A15" s="56" t="str">
         <x:v>Shared defense</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
@@ -1436,6 +1832,1258 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="27" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="19" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="32" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="32" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="27" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="34" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="19" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="28" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="36" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="34" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="16" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="21" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="19" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Analyst Decision Log</x:v>
+      </x:c>
+      <x:c r="B1" s="3"/>
+      <x:c r="C1" s="3"/>
+      <x:c r="D1" s="3"/>
+      <x:c r="E1" s="3"/>
+      <x:c r="F1" s="3"/>
+      <x:c r="G1" s="3"/>
+      <x:c r="H1" s="3"/>
+      <x:c r="I1" s="3"/>
+      <x:c r="J1" s="3"/>
+      <x:c r="K1" s="3"/>
+      <x:c r="L1" s="3"/>
+      <x:c r="M1" s="3"/>
+      <x:c r="N1" s="3"/>
+      <x:c r="O1" s="3"/>
+      <x:c r="P1" s="3"/>
+      <x:c r="Q1" s="3"/>
+      <x:c r="R1" s="3"/>
+      <x:c r="S1" s="3"/>
+      <x:c r="T1" s="3"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>Human-first judgment → AI interview and challenge → human verification → final reasoning → downstream guardrail</x:v>
+      </x:c>
+      <x:c r="B2" s="6"/>
+      <x:c r="C2" s="6"/>
+      <x:c r="D2" s="6"/>
+      <x:c r="E2" s="6"/>
+      <x:c r="F2" s="6"/>
+      <x:c r="G2" s="6"/>
+      <x:c r="H2" s="6"/>
+      <x:c r="I2" s="6"/>
+      <x:c r="J2" s="6"/>
+      <x:c r="K2" s="6"/>
+      <x:c r="L2" s="6"/>
+      <x:c r="M2" s="6"/>
+      <x:c r="N2" s="6"/>
+      <x:c r="O2" s="6"/>
+      <x:c r="P2" s="6"/>
+      <x:c r="Q2" s="6"/>
+      <x:c r="R2" s="6"/>
+      <x:c r="S2" s="6"/>
+      <x:c r="T2" s="6"/>
+    </x:row>
+    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4" s="58" t="str">
+        <x:v>Before using AI, each of the four roles records at least one initial judgment for each assigned client. Minimum Phase 1 evidence: 12 complete role-by-client entries across the team.</x:v>
+      </x:c>
+      <x:c r="B4" s="58"/>
+      <x:c r="C4" s="58"/>
+      <x:c r="D4" s="58"/>
+      <x:c r="E4" s="58"/>
+      <x:c r="F4" s="58"/>
+      <x:c r="G4" s="58"/>
+      <x:c r="H4" s="58"/>
+      <x:c r="I4" s="58"/>
+      <x:c r="J4" s="58"/>
+      <x:c r="K4" s="58"/>
+      <x:c r="L4" s="58"/>
+      <x:c r="M4" s="58"/>
+      <x:c r="N4" s="58"/>
+      <x:c r="O4" s="58"/>
+      <x:c r="P4" s="58"/>
+      <x:c r="Q4" s="58"/>
+      <x:c r="R4" s="58"/>
+      <x:c r="S4" s="58"/>
+      <x:c r="T4" s="58"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="37" t="str">
+        <x:v>Summarize AI output; do not paste transcripts. Unknown client information stays unknown. Do not enter real personal information or proprietary FactSet data into an AI tool.</x:v>
+      </x:c>
+      <x:c r="B5" s="37"/>
+      <x:c r="C5" s="37"/>
+      <x:c r="D5" s="37"/>
+      <x:c r="E5" s="37"/>
+      <x:c r="F5" s="37"/>
+      <x:c r="G5" s="37"/>
+      <x:c r="H5" s="37"/>
+      <x:c r="I5" s="37"/>
+      <x:c r="J5" s="37"/>
+      <x:c r="K5" s="37"/>
+      <x:c r="L5" s="37"/>
+      <x:c r="M5" s="37"/>
+      <x:c r="N5" s="37"/>
+      <x:c r="O5" s="37"/>
+      <x:c r="P5" s="37"/>
+      <x:c r="Q5" s="37"/>
+      <x:c r="R5" s="37"/>
+      <x:c r="S5" s="37"/>
+      <x:c r="T5" s="37"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="25" t="str">
+        <x:v>Team / committee</x:v>
+      </x:c>
+      <x:c r="B6" s="63" t="str"/>
+      <x:c r="C6" s="64" t="str"/>
+      <x:c r="D6" s="25" t="str">
+        <x:v>Assigned Client 1</x:v>
+      </x:c>
+      <x:c r="E6" s="63" t="str"/>
+      <x:c r="F6" s="64" t="str"/>
+      <x:c r="G6" s="25" t="str">
+        <x:v>Assigned Client 2</x:v>
+      </x:c>
+      <x:c r="H6" s="63" t="str"/>
+      <x:c r="I6" s="64" t="str"/>
+      <x:c r="J6" s="25" t="str">
+        <x:v>Assigned Client 3</x:v>
+      </x:c>
+      <x:c r="K6" s="63" t="str"/>
+      <x:c r="L6" s="64" t="str"/>
+    </x:row>
+    <x:row r="7" ht="48" customHeight="1">
+      <x:c r="A7" s="21" t="str">
+        <x:v>Decision ID</x:v>
+      </x:c>
+      <x:c r="B7" s="21" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="C7" s="21" t="str">
+        <x:v>Client</x:v>
+      </x:c>
+      <x:c r="D7" s="21" t="str">
+        <x:v>Owner role</x:v>
+      </x:c>
+      <x:c r="E7" s="21" t="str">
+        <x:v>Decision / question</x:v>
+      </x:c>
+      <x:c r="F7" s="21" t="str">
+        <x:v>Initial judgment</x:v>
+      </x:c>
+      <x:c r="G7" s="21" t="str">
+        <x:v>Confidence</x:v>
+      </x:c>
+      <x:c r="H7" s="21" t="str">
+        <x:v>Claim type</x:v>
+      </x:c>
+      <x:c r="I7" s="21" t="str">
+        <x:v>AI challenge prompt / purpose</x:v>
+      </x:c>
+      <x:c r="J7" s="21" t="str">
+        <x:v>AI output summary</x:v>
+      </x:c>
+      <x:c r="K7" s="21" t="str">
+        <x:v>Claim to verify</x:v>
+      </x:c>
+      <x:c r="L7" s="21" t="str">
+        <x:v>Verification source / link</x:v>
+      </x:c>
+      <x:c r="M7" s="21" t="str">
+        <x:v>Source as-of</x:v>
+      </x:c>
+      <x:c r="N7" s="21" t="str">
+        <x:v>Verification result</x:v>
+      </x:c>
+      <x:c r="O7" s="21" t="str">
+        <x:v>Change to reasoning</x:v>
+      </x:c>
+      <x:c r="P7" s="21" t="str">
+        <x:v>Final judgment and rationale</x:v>
+      </x:c>
+      <x:c r="Q7" s="21" t="str">
+        <x:v>Downstream investment guardrail</x:v>
+      </x:c>
+      <x:c r="R7" s="21" t="str">
+        <x:v>Peer reviewer</x:v>
+      </x:c>
+      <x:c r="S7" s="21" t="str">
+        <x:v>Peer review status</x:v>
+      </x:c>
+      <x:c r="T7" s="21" t="str">
+        <x:v>Entry status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="66" customHeight="1">
+      <x:c r="A8" s="82"/>
+      <x:c r="B8" s="91"/>
+      <x:c r="C8" s="83"/>
+      <x:c r="D8" s="83"/>
+      <x:c r="E8" s="83"/>
+      <x:c r="F8" s="83"/>
+      <x:c r="G8" s="83"/>
+      <x:c r="H8" s="83"/>
+      <x:c r="I8" s="83"/>
+      <x:c r="J8" s="83"/>
+      <x:c r="K8" s="83"/>
+      <x:c r="L8" s="83"/>
+      <x:c r="M8" s="91"/>
+      <x:c r="N8" s="83"/>
+      <x:c r="O8" s="83"/>
+      <x:c r="P8" s="83"/>
+      <x:c r="Q8" s="83"/>
+      <x:c r="R8" s="83"/>
+      <x:c r="S8" s="84"/>
+      <x:c r="T8" s="96" t="str">
+        <x:f>IF(COUNTA(A8:S8)=0,"NOT STARTED",IF(OR(A8="",B8="",C8="",D8="",E8="",F8="",G8="",H8="",I8="",J8="",K8="",L8="",M8="",N8="",O8="",P8="",Q8="",R8="",S8=""),"INCOMPLETE",IF(OR(S8="Needs revision",AND(OR(N8="Contradicted",N8="Not verifiable"),S8&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="66" customHeight="1">
+      <x:c r="A9" s="85"/>
+      <x:c r="B9" s="92"/>
+      <x:c r="C9" s="86"/>
+      <x:c r="D9" s="86"/>
+      <x:c r="E9" s="86"/>
+      <x:c r="F9" s="86"/>
+      <x:c r="G9" s="86"/>
+      <x:c r="H9" s="86"/>
+      <x:c r="I9" s="86"/>
+      <x:c r="J9" s="86"/>
+      <x:c r="K9" s="86"/>
+      <x:c r="L9" s="86"/>
+      <x:c r="M9" s="92"/>
+      <x:c r="N9" s="86"/>
+      <x:c r="O9" s="86"/>
+      <x:c r="P9" s="86"/>
+      <x:c r="Q9" s="86"/>
+      <x:c r="R9" s="86"/>
+      <x:c r="S9" s="87"/>
+      <x:c r="T9" s="96" t="str">
+        <x:f>IF(COUNTA(A9:S9)=0,"NOT STARTED",IF(OR(A9="",B9="",C9="",D9="",E9="",F9="",G9="",H9="",I9="",J9="",K9="",L9="",M9="",N9="",O9="",P9="",Q9="",R9="",S9=""),"INCOMPLETE",IF(OR(S9="Needs revision",AND(OR(N9="Contradicted",N9="Not verifiable"),S9&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="66" customHeight="1">
+      <x:c r="A10" s="85"/>
+      <x:c r="B10" s="92"/>
+      <x:c r="C10" s="86"/>
+      <x:c r="D10" s="86"/>
+      <x:c r="E10" s="86"/>
+      <x:c r="F10" s="86"/>
+      <x:c r="G10" s="86"/>
+      <x:c r="H10" s="86"/>
+      <x:c r="I10" s="86"/>
+      <x:c r="J10" s="86"/>
+      <x:c r="K10" s="86"/>
+      <x:c r="L10" s="86"/>
+      <x:c r="M10" s="92"/>
+      <x:c r="N10" s="86"/>
+      <x:c r="O10" s="86"/>
+      <x:c r="P10" s="86"/>
+      <x:c r="Q10" s="86"/>
+      <x:c r="R10" s="86"/>
+      <x:c r="S10" s="87"/>
+      <x:c r="T10" s="96" t="str">
+        <x:f>IF(COUNTA(A10:S10)=0,"NOT STARTED",IF(OR(A10="",B10="",C10="",D10="",E10="",F10="",G10="",H10="",I10="",J10="",K10="",L10="",M10="",N10="",O10="",P10="",Q10="",R10="",S10=""),"INCOMPLETE",IF(OR(S10="Needs revision",AND(OR(N10="Contradicted",N10="Not verifiable"),S10&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="66" customHeight="1">
+      <x:c r="A11" s="85"/>
+      <x:c r="B11" s="92"/>
+      <x:c r="C11" s="86"/>
+      <x:c r="D11" s="86"/>
+      <x:c r="E11" s="86"/>
+      <x:c r="F11" s="86"/>
+      <x:c r="G11" s="86"/>
+      <x:c r="H11" s="86"/>
+      <x:c r="I11" s="86"/>
+      <x:c r="J11" s="86"/>
+      <x:c r="K11" s="86"/>
+      <x:c r="L11" s="86"/>
+      <x:c r="M11" s="92"/>
+      <x:c r="N11" s="86"/>
+      <x:c r="O11" s="86"/>
+      <x:c r="P11" s="86"/>
+      <x:c r="Q11" s="86"/>
+      <x:c r="R11" s="86"/>
+      <x:c r="S11" s="87"/>
+      <x:c r="T11" s="96" t="str">
+        <x:f>IF(COUNTA(A11:S11)=0,"NOT STARTED",IF(OR(A11="",B11="",C11="",D11="",E11="",F11="",G11="",H11="",I11="",J11="",K11="",L11="",M11="",N11="",O11="",P11="",Q11="",R11="",S11=""),"INCOMPLETE",IF(OR(S11="Needs revision",AND(OR(N11="Contradicted",N11="Not verifiable"),S11&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="66" customHeight="1">
+      <x:c r="A12" s="85"/>
+      <x:c r="B12" s="92"/>
+      <x:c r="C12" s="86"/>
+      <x:c r="D12" s="86"/>
+      <x:c r="E12" s="86"/>
+      <x:c r="F12" s="86"/>
+      <x:c r="G12" s="86"/>
+      <x:c r="H12" s="86"/>
+      <x:c r="I12" s="86"/>
+      <x:c r="J12" s="86"/>
+      <x:c r="K12" s="86"/>
+      <x:c r="L12" s="86"/>
+      <x:c r="M12" s="92"/>
+      <x:c r="N12" s="86"/>
+      <x:c r="O12" s="86"/>
+      <x:c r="P12" s="86"/>
+      <x:c r="Q12" s="86"/>
+      <x:c r="R12" s="86"/>
+      <x:c r="S12" s="87"/>
+      <x:c r="T12" s="96" t="str">
+        <x:f>IF(COUNTA(A12:S12)=0,"NOT STARTED",IF(OR(A12="",B12="",C12="",D12="",E12="",F12="",G12="",H12="",I12="",J12="",K12="",L12="",M12="",N12="",O12="",P12="",Q12="",R12="",S12=""),"INCOMPLETE",IF(OR(S12="Needs revision",AND(OR(N12="Contradicted",N12="Not verifiable"),S12&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="66" customHeight="1">
+      <x:c r="A13" s="85"/>
+      <x:c r="B13" s="92"/>
+      <x:c r="C13" s="86"/>
+      <x:c r="D13" s="86"/>
+      <x:c r="E13" s="86"/>
+      <x:c r="F13" s="86"/>
+      <x:c r="G13" s="86"/>
+      <x:c r="H13" s="86"/>
+      <x:c r="I13" s="86"/>
+      <x:c r="J13" s="86"/>
+      <x:c r="K13" s="86"/>
+      <x:c r="L13" s="86"/>
+      <x:c r="M13" s="92"/>
+      <x:c r="N13" s="86"/>
+      <x:c r="O13" s="86"/>
+      <x:c r="P13" s="86"/>
+      <x:c r="Q13" s="86"/>
+      <x:c r="R13" s="86"/>
+      <x:c r="S13" s="87"/>
+      <x:c r="T13" s="96" t="str">
+        <x:f>IF(COUNTA(A13:S13)=0,"NOT STARTED",IF(OR(A13="",B13="",C13="",D13="",E13="",F13="",G13="",H13="",I13="",J13="",K13="",L13="",M13="",N13="",O13="",P13="",Q13="",R13="",S13=""),"INCOMPLETE",IF(OR(S13="Needs revision",AND(OR(N13="Contradicted",N13="Not verifiable"),S13&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="66" customHeight="1">
+      <x:c r="A14" s="85"/>
+      <x:c r="B14" s="92"/>
+      <x:c r="C14" s="86"/>
+      <x:c r="D14" s="86"/>
+      <x:c r="E14" s="86"/>
+      <x:c r="F14" s="86"/>
+      <x:c r="G14" s="86"/>
+      <x:c r="H14" s="86"/>
+      <x:c r="I14" s="86"/>
+      <x:c r="J14" s="86"/>
+      <x:c r="K14" s="86"/>
+      <x:c r="L14" s="86"/>
+      <x:c r="M14" s="92"/>
+      <x:c r="N14" s="86"/>
+      <x:c r="O14" s="86"/>
+      <x:c r="P14" s="86"/>
+      <x:c r="Q14" s="86"/>
+      <x:c r="R14" s="86"/>
+      <x:c r="S14" s="87"/>
+      <x:c r="T14" s="96" t="str">
+        <x:f>IF(COUNTA(A14:S14)=0,"NOT STARTED",IF(OR(A14="",B14="",C14="",D14="",E14="",F14="",G14="",H14="",I14="",J14="",K14="",L14="",M14="",N14="",O14="",P14="",Q14="",R14="",S14=""),"INCOMPLETE",IF(OR(S14="Needs revision",AND(OR(N14="Contradicted",N14="Not verifiable"),S14&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="66" customHeight="1">
+      <x:c r="A15" s="85"/>
+      <x:c r="B15" s="92"/>
+      <x:c r="C15" s="86"/>
+      <x:c r="D15" s="86"/>
+      <x:c r="E15" s="86"/>
+      <x:c r="F15" s="86"/>
+      <x:c r="G15" s="86"/>
+      <x:c r="H15" s="86"/>
+      <x:c r="I15" s="86"/>
+      <x:c r="J15" s="86"/>
+      <x:c r="K15" s="86"/>
+      <x:c r="L15" s="86"/>
+      <x:c r="M15" s="92"/>
+      <x:c r="N15" s="86"/>
+      <x:c r="O15" s="86"/>
+      <x:c r="P15" s="86"/>
+      <x:c r="Q15" s="86"/>
+      <x:c r="R15" s="86"/>
+      <x:c r="S15" s="87"/>
+      <x:c r="T15" s="96" t="str">
+        <x:f>IF(COUNTA(A15:S15)=0,"NOT STARTED",IF(OR(A15="",B15="",C15="",D15="",E15="",F15="",G15="",H15="",I15="",J15="",K15="",L15="",M15="",N15="",O15="",P15="",Q15="",R15="",S15=""),"INCOMPLETE",IF(OR(S15="Needs revision",AND(OR(N15="Contradicted",N15="Not verifiable"),S15&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="66" customHeight="1">
+      <x:c r="A16" s="85"/>
+      <x:c r="B16" s="92"/>
+      <x:c r="C16" s="86"/>
+      <x:c r="D16" s="86"/>
+      <x:c r="E16" s="86"/>
+      <x:c r="F16" s="86"/>
+      <x:c r="G16" s="86"/>
+      <x:c r="H16" s="86"/>
+      <x:c r="I16" s="86"/>
+      <x:c r="J16" s="86"/>
+      <x:c r="K16" s="86"/>
+      <x:c r="L16" s="86"/>
+      <x:c r="M16" s="92"/>
+      <x:c r="N16" s="86"/>
+      <x:c r="O16" s="86"/>
+      <x:c r="P16" s="86"/>
+      <x:c r="Q16" s="86"/>
+      <x:c r="R16" s="86"/>
+      <x:c r="S16" s="87"/>
+      <x:c r="T16" s="96" t="str">
+        <x:f>IF(COUNTA(A16:S16)=0,"NOT STARTED",IF(OR(A16="",B16="",C16="",D16="",E16="",F16="",G16="",H16="",I16="",J16="",K16="",L16="",M16="",N16="",O16="",P16="",Q16="",R16="",S16=""),"INCOMPLETE",IF(OR(S16="Needs revision",AND(OR(N16="Contradicted",N16="Not verifiable"),S16&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="66" customHeight="1">
+      <x:c r="A17" s="85"/>
+      <x:c r="B17" s="92"/>
+      <x:c r="C17" s="86"/>
+      <x:c r="D17" s="86"/>
+      <x:c r="E17" s="86"/>
+      <x:c r="F17" s="86"/>
+      <x:c r="G17" s="86"/>
+      <x:c r="H17" s="86"/>
+      <x:c r="I17" s="86"/>
+      <x:c r="J17" s="86"/>
+      <x:c r="K17" s="86"/>
+      <x:c r="L17" s="86"/>
+      <x:c r="M17" s="92"/>
+      <x:c r="N17" s="86"/>
+      <x:c r="O17" s="86"/>
+      <x:c r="P17" s="86"/>
+      <x:c r="Q17" s="86"/>
+      <x:c r="R17" s="86"/>
+      <x:c r="S17" s="87"/>
+      <x:c r="T17" s="96" t="str">
+        <x:f>IF(COUNTA(A17:S17)=0,"NOT STARTED",IF(OR(A17="",B17="",C17="",D17="",E17="",F17="",G17="",H17="",I17="",J17="",K17="",L17="",M17="",N17="",O17="",P17="",Q17="",R17="",S17=""),"INCOMPLETE",IF(OR(S17="Needs revision",AND(OR(N17="Contradicted",N17="Not verifiable"),S17&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="66" customHeight="1">
+      <x:c r="A18" s="85"/>
+      <x:c r="B18" s="92"/>
+      <x:c r="C18" s="86"/>
+      <x:c r="D18" s="86"/>
+      <x:c r="E18" s="86"/>
+      <x:c r="F18" s="86"/>
+      <x:c r="G18" s="86"/>
+      <x:c r="H18" s="86"/>
+      <x:c r="I18" s="86"/>
+      <x:c r="J18" s="86"/>
+      <x:c r="K18" s="86"/>
+      <x:c r="L18" s="86"/>
+      <x:c r="M18" s="92"/>
+      <x:c r="N18" s="86"/>
+      <x:c r="O18" s="86"/>
+      <x:c r="P18" s="86"/>
+      <x:c r="Q18" s="86"/>
+      <x:c r="R18" s="86"/>
+      <x:c r="S18" s="87"/>
+      <x:c r="T18" s="96" t="str">
+        <x:f>IF(COUNTA(A18:S18)=0,"NOT STARTED",IF(OR(A18="",B18="",C18="",D18="",E18="",F18="",G18="",H18="",I18="",J18="",K18="",L18="",M18="",N18="",O18="",P18="",Q18="",R18="",S18=""),"INCOMPLETE",IF(OR(S18="Needs revision",AND(OR(N18="Contradicted",N18="Not verifiable"),S18&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="66" customHeight="1">
+      <x:c r="A19" s="85"/>
+      <x:c r="B19" s="92"/>
+      <x:c r="C19" s="86"/>
+      <x:c r="D19" s="86"/>
+      <x:c r="E19" s="86"/>
+      <x:c r="F19" s="86"/>
+      <x:c r="G19" s="86"/>
+      <x:c r="H19" s="86"/>
+      <x:c r="I19" s="86"/>
+      <x:c r="J19" s="86"/>
+      <x:c r="K19" s="86"/>
+      <x:c r="L19" s="86"/>
+      <x:c r="M19" s="92"/>
+      <x:c r="N19" s="86"/>
+      <x:c r="O19" s="86"/>
+      <x:c r="P19" s="86"/>
+      <x:c r="Q19" s="86"/>
+      <x:c r="R19" s="86"/>
+      <x:c r="S19" s="87"/>
+      <x:c r="T19" s="96" t="str">
+        <x:f>IF(COUNTA(A19:S19)=0,"NOT STARTED",IF(OR(A19="",B19="",C19="",D19="",E19="",F19="",G19="",H19="",I19="",J19="",K19="",L19="",M19="",N19="",O19="",P19="",Q19="",R19="",S19=""),"INCOMPLETE",IF(OR(S19="Needs revision",AND(OR(N19="Contradicted",N19="Not verifiable"),S19&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="66" customHeight="1">
+      <x:c r="A20" s="85"/>
+      <x:c r="B20" s="92"/>
+      <x:c r="C20" s="86"/>
+      <x:c r="D20" s="86"/>
+      <x:c r="E20" s="86"/>
+      <x:c r="F20" s="86"/>
+      <x:c r="G20" s="86"/>
+      <x:c r="H20" s="86"/>
+      <x:c r="I20" s="86"/>
+      <x:c r="J20" s="86"/>
+      <x:c r="K20" s="86"/>
+      <x:c r="L20" s="86"/>
+      <x:c r="M20" s="92"/>
+      <x:c r="N20" s="86"/>
+      <x:c r="O20" s="86"/>
+      <x:c r="P20" s="86"/>
+      <x:c r="Q20" s="86"/>
+      <x:c r="R20" s="86"/>
+      <x:c r="S20" s="87"/>
+      <x:c r="T20" s="96" t="str">
+        <x:f>IF(COUNTA(A20:S20)=0,"NOT STARTED",IF(OR(A20="",B20="",C20="",D20="",E20="",F20="",G20="",H20="",I20="",J20="",K20="",L20="",M20="",N20="",O20="",P20="",Q20="",R20="",S20=""),"INCOMPLETE",IF(OR(S20="Needs revision",AND(OR(N20="Contradicted",N20="Not verifiable"),S20&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="66" customHeight="1">
+      <x:c r="A21" s="85"/>
+      <x:c r="B21" s="92"/>
+      <x:c r="C21" s="86"/>
+      <x:c r="D21" s="86"/>
+      <x:c r="E21" s="86"/>
+      <x:c r="F21" s="86"/>
+      <x:c r="G21" s="86"/>
+      <x:c r="H21" s="86"/>
+      <x:c r="I21" s="86"/>
+      <x:c r="J21" s="86"/>
+      <x:c r="K21" s="86"/>
+      <x:c r="L21" s="86"/>
+      <x:c r="M21" s="92"/>
+      <x:c r="N21" s="86"/>
+      <x:c r="O21" s="86"/>
+      <x:c r="P21" s="86"/>
+      <x:c r="Q21" s="86"/>
+      <x:c r="R21" s="86"/>
+      <x:c r="S21" s="87"/>
+      <x:c r="T21" s="96" t="str">
+        <x:f>IF(COUNTA(A21:S21)=0,"NOT STARTED",IF(OR(A21="",B21="",C21="",D21="",E21="",F21="",G21="",H21="",I21="",J21="",K21="",L21="",M21="",N21="",O21="",P21="",Q21="",R21="",S21=""),"INCOMPLETE",IF(OR(S21="Needs revision",AND(OR(N21="Contradicted",N21="Not verifiable"),S21&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="66" customHeight="1">
+      <x:c r="A22" s="85"/>
+      <x:c r="B22" s="92"/>
+      <x:c r="C22" s="86"/>
+      <x:c r="D22" s="86"/>
+      <x:c r="E22" s="86"/>
+      <x:c r="F22" s="86"/>
+      <x:c r="G22" s="86"/>
+      <x:c r="H22" s="86"/>
+      <x:c r="I22" s="86"/>
+      <x:c r="J22" s="86"/>
+      <x:c r="K22" s="86"/>
+      <x:c r="L22" s="86"/>
+      <x:c r="M22" s="92"/>
+      <x:c r="N22" s="86"/>
+      <x:c r="O22" s="86"/>
+      <x:c r="P22" s="86"/>
+      <x:c r="Q22" s="86"/>
+      <x:c r="R22" s="86"/>
+      <x:c r="S22" s="87"/>
+      <x:c r="T22" s="96" t="str">
+        <x:f>IF(COUNTA(A22:S22)=0,"NOT STARTED",IF(OR(A22="",B22="",C22="",D22="",E22="",F22="",G22="",H22="",I22="",J22="",K22="",L22="",M22="",N22="",O22="",P22="",Q22="",R22="",S22=""),"INCOMPLETE",IF(OR(S22="Needs revision",AND(OR(N22="Contradicted",N22="Not verifiable"),S22&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="66" customHeight="1">
+      <x:c r="A23" s="85"/>
+      <x:c r="B23" s="92"/>
+      <x:c r="C23" s="86"/>
+      <x:c r="D23" s="86"/>
+      <x:c r="E23" s="86"/>
+      <x:c r="F23" s="86"/>
+      <x:c r="G23" s="86"/>
+      <x:c r="H23" s="86"/>
+      <x:c r="I23" s="86"/>
+      <x:c r="J23" s="86"/>
+      <x:c r="K23" s="86"/>
+      <x:c r="L23" s="86"/>
+      <x:c r="M23" s="92"/>
+      <x:c r="N23" s="86"/>
+      <x:c r="O23" s="86"/>
+      <x:c r="P23" s="86"/>
+      <x:c r="Q23" s="86"/>
+      <x:c r="R23" s="86"/>
+      <x:c r="S23" s="87"/>
+      <x:c r="T23" s="96" t="str">
+        <x:f>IF(COUNTA(A23:S23)=0,"NOT STARTED",IF(OR(A23="",B23="",C23="",D23="",E23="",F23="",G23="",H23="",I23="",J23="",K23="",L23="",M23="",N23="",O23="",P23="",Q23="",R23="",S23=""),"INCOMPLETE",IF(OR(S23="Needs revision",AND(OR(N23="Contradicted",N23="Not verifiable"),S23&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="66" customHeight="1">
+      <x:c r="A24" s="85"/>
+      <x:c r="B24" s="92"/>
+      <x:c r="C24" s="86"/>
+      <x:c r="D24" s="86"/>
+      <x:c r="E24" s="86"/>
+      <x:c r="F24" s="86"/>
+      <x:c r="G24" s="86"/>
+      <x:c r="H24" s="86"/>
+      <x:c r="I24" s="86"/>
+      <x:c r="J24" s="86"/>
+      <x:c r="K24" s="86"/>
+      <x:c r="L24" s="86"/>
+      <x:c r="M24" s="92"/>
+      <x:c r="N24" s="86"/>
+      <x:c r="O24" s="86"/>
+      <x:c r="P24" s="86"/>
+      <x:c r="Q24" s="86"/>
+      <x:c r="R24" s="86"/>
+      <x:c r="S24" s="87"/>
+      <x:c r="T24" s="96" t="str">
+        <x:f>IF(COUNTA(A24:S24)=0,"NOT STARTED",IF(OR(A24="",B24="",C24="",D24="",E24="",F24="",G24="",H24="",I24="",J24="",K24="",L24="",M24="",N24="",O24="",P24="",Q24="",R24="",S24=""),"INCOMPLETE",IF(OR(S24="Needs revision",AND(OR(N24="Contradicted",N24="Not verifiable"),S24&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="66" customHeight="1">
+      <x:c r="A25" s="85"/>
+      <x:c r="B25" s="92"/>
+      <x:c r="C25" s="86"/>
+      <x:c r="D25" s="86"/>
+      <x:c r="E25" s="86"/>
+      <x:c r="F25" s="86"/>
+      <x:c r="G25" s="86"/>
+      <x:c r="H25" s="86"/>
+      <x:c r="I25" s="86"/>
+      <x:c r="J25" s="86"/>
+      <x:c r="K25" s="86"/>
+      <x:c r="L25" s="86"/>
+      <x:c r="M25" s="92"/>
+      <x:c r="N25" s="86"/>
+      <x:c r="O25" s="86"/>
+      <x:c r="P25" s="86"/>
+      <x:c r="Q25" s="86"/>
+      <x:c r="R25" s="86"/>
+      <x:c r="S25" s="87"/>
+      <x:c r="T25" s="96" t="str">
+        <x:f>IF(COUNTA(A25:S25)=0,"NOT STARTED",IF(OR(A25="",B25="",C25="",D25="",E25="",F25="",G25="",H25="",I25="",J25="",K25="",L25="",M25="",N25="",O25="",P25="",Q25="",R25="",S25=""),"INCOMPLETE",IF(OR(S25="Needs revision",AND(OR(N25="Contradicted",N25="Not verifiable"),S25&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="66" customHeight="1">
+      <x:c r="A26" s="85"/>
+      <x:c r="B26" s="92"/>
+      <x:c r="C26" s="86"/>
+      <x:c r="D26" s="86"/>
+      <x:c r="E26" s="86"/>
+      <x:c r="F26" s="86"/>
+      <x:c r="G26" s="86"/>
+      <x:c r="H26" s="86"/>
+      <x:c r="I26" s="86"/>
+      <x:c r="J26" s="86"/>
+      <x:c r="K26" s="86"/>
+      <x:c r="L26" s="86"/>
+      <x:c r="M26" s="92"/>
+      <x:c r="N26" s="86"/>
+      <x:c r="O26" s="86"/>
+      <x:c r="P26" s="86"/>
+      <x:c r="Q26" s="86"/>
+      <x:c r="R26" s="86"/>
+      <x:c r="S26" s="87"/>
+      <x:c r="T26" s="96" t="str">
+        <x:f>IF(COUNTA(A26:S26)=0,"NOT STARTED",IF(OR(A26="",B26="",C26="",D26="",E26="",F26="",G26="",H26="",I26="",J26="",K26="",L26="",M26="",N26="",O26="",P26="",Q26="",R26="",S26=""),"INCOMPLETE",IF(OR(S26="Needs revision",AND(OR(N26="Contradicted",N26="Not verifiable"),S26&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="66" customHeight="1">
+      <x:c r="A27" s="85"/>
+      <x:c r="B27" s="92"/>
+      <x:c r="C27" s="86"/>
+      <x:c r="D27" s="86"/>
+      <x:c r="E27" s="86"/>
+      <x:c r="F27" s="86"/>
+      <x:c r="G27" s="86"/>
+      <x:c r="H27" s="86"/>
+      <x:c r="I27" s="86"/>
+      <x:c r="J27" s="86"/>
+      <x:c r="K27" s="86"/>
+      <x:c r="L27" s="86"/>
+      <x:c r="M27" s="92"/>
+      <x:c r="N27" s="86"/>
+      <x:c r="O27" s="86"/>
+      <x:c r="P27" s="86"/>
+      <x:c r="Q27" s="86"/>
+      <x:c r="R27" s="86"/>
+      <x:c r="S27" s="87"/>
+      <x:c r="T27" s="96" t="str">
+        <x:f>IF(COUNTA(A27:S27)=0,"NOT STARTED",IF(OR(A27="",B27="",C27="",D27="",E27="",F27="",G27="",H27="",I27="",J27="",K27="",L27="",M27="",N27="",O27="",P27="",Q27="",R27="",S27=""),"INCOMPLETE",IF(OR(S27="Needs revision",AND(OR(N27="Contradicted",N27="Not verifiable"),S27&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="66" customHeight="1">
+      <x:c r="A28" s="85"/>
+      <x:c r="B28" s="92"/>
+      <x:c r="C28" s="86"/>
+      <x:c r="D28" s="86"/>
+      <x:c r="E28" s="86"/>
+      <x:c r="F28" s="86"/>
+      <x:c r="G28" s="86"/>
+      <x:c r="H28" s="86"/>
+      <x:c r="I28" s="86"/>
+      <x:c r="J28" s="86"/>
+      <x:c r="K28" s="86"/>
+      <x:c r="L28" s="86"/>
+      <x:c r="M28" s="92"/>
+      <x:c r="N28" s="86"/>
+      <x:c r="O28" s="86"/>
+      <x:c r="P28" s="86"/>
+      <x:c r="Q28" s="86"/>
+      <x:c r="R28" s="86"/>
+      <x:c r="S28" s="87"/>
+      <x:c r="T28" s="96" t="str">
+        <x:f>IF(COUNTA(A28:S28)=0,"NOT STARTED",IF(OR(A28="",B28="",C28="",D28="",E28="",F28="",G28="",H28="",I28="",J28="",K28="",L28="",M28="",N28="",O28="",P28="",Q28="",R28="",S28=""),"INCOMPLETE",IF(OR(S28="Needs revision",AND(OR(N28="Contradicted",N28="Not verifiable"),S28&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="66" customHeight="1">
+      <x:c r="A29" s="85"/>
+      <x:c r="B29" s="92"/>
+      <x:c r="C29" s="86"/>
+      <x:c r="D29" s="86"/>
+      <x:c r="E29" s="86"/>
+      <x:c r="F29" s="86"/>
+      <x:c r="G29" s="86"/>
+      <x:c r="H29" s="86"/>
+      <x:c r="I29" s="86"/>
+      <x:c r="J29" s="86"/>
+      <x:c r="K29" s="86"/>
+      <x:c r="L29" s="86"/>
+      <x:c r="M29" s="92"/>
+      <x:c r="N29" s="86"/>
+      <x:c r="O29" s="86"/>
+      <x:c r="P29" s="86"/>
+      <x:c r="Q29" s="86"/>
+      <x:c r="R29" s="86"/>
+      <x:c r="S29" s="87"/>
+      <x:c r="T29" s="96" t="str">
+        <x:f>IF(COUNTA(A29:S29)=0,"NOT STARTED",IF(OR(A29="",B29="",C29="",D29="",E29="",F29="",G29="",H29="",I29="",J29="",K29="",L29="",M29="",N29="",O29="",P29="",Q29="",R29="",S29=""),"INCOMPLETE",IF(OR(S29="Needs revision",AND(OR(N29="Contradicted",N29="Not verifiable"),S29&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="66" customHeight="1">
+      <x:c r="A30" s="85"/>
+      <x:c r="B30" s="92"/>
+      <x:c r="C30" s="86"/>
+      <x:c r="D30" s="86"/>
+      <x:c r="E30" s="86"/>
+      <x:c r="F30" s="86"/>
+      <x:c r="G30" s="86"/>
+      <x:c r="H30" s="86"/>
+      <x:c r="I30" s="86"/>
+      <x:c r="J30" s="86"/>
+      <x:c r="K30" s="86"/>
+      <x:c r="L30" s="86"/>
+      <x:c r="M30" s="92"/>
+      <x:c r="N30" s="86"/>
+      <x:c r="O30" s="86"/>
+      <x:c r="P30" s="86"/>
+      <x:c r="Q30" s="86"/>
+      <x:c r="R30" s="86"/>
+      <x:c r="S30" s="87"/>
+      <x:c r="T30" s="96" t="str">
+        <x:f>IF(COUNTA(A30:S30)=0,"NOT STARTED",IF(OR(A30="",B30="",C30="",D30="",E30="",F30="",G30="",H30="",I30="",J30="",K30="",L30="",M30="",N30="",O30="",P30="",Q30="",R30="",S30=""),"INCOMPLETE",IF(OR(S30="Needs revision",AND(OR(N30="Contradicted",N30="Not verifiable"),S30&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="66" customHeight="1">
+      <x:c r="A31" s="85"/>
+      <x:c r="B31" s="92"/>
+      <x:c r="C31" s="86"/>
+      <x:c r="D31" s="86"/>
+      <x:c r="E31" s="86"/>
+      <x:c r="F31" s="86"/>
+      <x:c r="G31" s="86"/>
+      <x:c r="H31" s="86"/>
+      <x:c r="I31" s="86"/>
+      <x:c r="J31" s="86"/>
+      <x:c r="K31" s="86"/>
+      <x:c r="L31" s="86"/>
+      <x:c r="M31" s="92"/>
+      <x:c r="N31" s="86"/>
+      <x:c r="O31" s="86"/>
+      <x:c r="P31" s="86"/>
+      <x:c r="Q31" s="86"/>
+      <x:c r="R31" s="86"/>
+      <x:c r="S31" s="87"/>
+      <x:c r="T31" s="96" t="str">
+        <x:f>IF(COUNTA(A31:S31)=0,"NOT STARTED",IF(OR(A31="",B31="",C31="",D31="",E31="",F31="",G31="",H31="",I31="",J31="",K31="",L31="",M31="",N31="",O31="",P31="",Q31="",R31="",S31=""),"INCOMPLETE",IF(OR(S31="Needs revision",AND(OR(N31="Contradicted",N31="Not verifiable"),S31&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="66" customHeight="1">
+      <x:c r="A32" s="85"/>
+      <x:c r="B32" s="92"/>
+      <x:c r="C32" s="86"/>
+      <x:c r="D32" s="86"/>
+      <x:c r="E32" s="86"/>
+      <x:c r="F32" s="86"/>
+      <x:c r="G32" s="86"/>
+      <x:c r="H32" s="86"/>
+      <x:c r="I32" s="86"/>
+      <x:c r="J32" s="86"/>
+      <x:c r="K32" s="86"/>
+      <x:c r="L32" s="86"/>
+      <x:c r="M32" s="92"/>
+      <x:c r="N32" s="86"/>
+      <x:c r="O32" s="86"/>
+      <x:c r="P32" s="86"/>
+      <x:c r="Q32" s="86"/>
+      <x:c r="R32" s="86"/>
+      <x:c r="S32" s="87"/>
+      <x:c r="T32" s="96" t="str">
+        <x:f>IF(COUNTA(A32:S32)=0,"NOT STARTED",IF(OR(A32="",B32="",C32="",D32="",E32="",F32="",G32="",H32="",I32="",J32="",K32="",L32="",M32="",N32="",O32="",P32="",Q32="",R32="",S32=""),"INCOMPLETE",IF(OR(S32="Needs revision",AND(OR(N32="Contradicted",N32="Not verifiable"),S32&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="66" customHeight="1">
+      <x:c r="A33" s="85"/>
+      <x:c r="B33" s="92"/>
+      <x:c r="C33" s="86"/>
+      <x:c r="D33" s="86"/>
+      <x:c r="E33" s="86"/>
+      <x:c r="F33" s="86"/>
+      <x:c r="G33" s="86"/>
+      <x:c r="H33" s="86"/>
+      <x:c r="I33" s="86"/>
+      <x:c r="J33" s="86"/>
+      <x:c r="K33" s="86"/>
+      <x:c r="L33" s="86"/>
+      <x:c r="M33" s="92"/>
+      <x:c r="N33" s="86"/>
+      <x:c r="O33" s="86"/>
+      <x:c r="P33" s="86"/>
+      <x:c r="Q33" s="86"/>
+      <x:c r="R33" s="86"/>
+      <x:c r="S33" s="87"/>
+      <x:c r="T33" s="96" t="str">
+        <x:f>IF(COUNTA(A33:S33)=0,"NOT STARTED",IF(OR(A33="",B33="",C33="",D33="",E33="",F33="",G33="",H33="",I33="",J33="",K33="",L33="",M33="",N33="",O33="",P33="",Q33="",R33="",S33=""),"INCOMPLETE",IF(OR(S33="Needs revision",AND(OR(N33="Contradicted",N33="Not verifiable"),S33&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="66" customHeight="1">
+      <x:c r="A34" s="85"/>
+      <x:c r="B34" s="92"/>
+      <x:c r="C34" s="86"/>
+      <x:c r="D34" s="86"/>
+      <x:c r="E34" s="86"/>
+      <x:c r="F34" s="86"/>
+      <x:c r="G34" s="86"/>
+      <x:c r="H34" s="86"/>
+      <x:c r="I34" s="86"/>
+      <x:c r="J34" s="86"/>
+      <x:c r="K34" s="86"/>
+      <x:c r="L34" s="86"/>
+      <x:c r="M34" s="92"/>
+      <x:c r="N34" s="86"/>
+      <x:c r="O34" s="86"/>
+      <x:c r="P34" s="86"/>
+      <x:c r="Q34" s="86"/>
+      <x:c r="R34" s="86"/>
+      <x:c r="S34" s="87"/>
+      <x:c r="T34" s="96" t="str">
+        <x:f>IF(COUNTA(A34:S34)=0,"NOT STARTED",IF(OR(A34="",B34="",C34="",D34="",E34="",F34="",G34="",H34="",I34="",J34="",K34="",L34="",M34="",N34="",O34="",P34="",Q34="",R34="",S34=""),"INCOMPLETE",IF(OR(S34="Needs revision",AND(OR(N34="Contradicted",N34="Not verifiable"),S34&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="66" customHeight="1">
+      <x:c r="A35" s="85"/>
+      <x:c r="B35" s="92"/>
+      <x:c r="C35" s="86"/>
+      <x:c r="D35" s="86"/>
+      <x:c r="E35" s="86"/>
+      <x:c r="F35" s="86"/>
+      <x:c r="G35" s="86"/>
+      <x:c r="H35" s="86"/>
+      <x:c r="I35" s="86"/>
+      <x:c r="J35" s="86"/>
+      <x:c r="K35" s="86"/>
+      <x:c r="L35" s="86"/>
+      <x:c r="M35" s="92"/>
+      <x:c r="N35" s="86"/>
+      <x:c r="O35" s="86"/>
+      <x:c r="P35" s="86"/>
+      <x:c r="Q35" s="86"/>
+      <x:c r="R35" s="86"/>
+      <x:c r="S35" s="87"/>
+      <x:c r="T35" s="96" t="str">
+        <x:f>IF(COUNTA(A35:S35)=0,"NOT STARTED",IF(OR(A35="",B35="",C35="",D35="",E35="",F35="",G35="",H35="",I35="",J35="",K35="",L35="",M35="",N35="",O35="",P35="",Q35="",R35="",S35=""),"INCOMPLETE",IF(OR(S35="Needs revision",AND(OR(N35="Contradicted",N35="Not verifiable"),S35&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="66" customHeight="1">
+      <x:c r="A36" s="85"/>
+      <x:c r="B36" s="92"/>
+      <x:c r="C36" s="86"/>
+      <x:c r="D36" s="86"/>
+      <x:c r="E36" s="86"/>
+      <x:c r="F36" s="86"/>
+      <x:c r="G36" s="86"/>
+      <x:c r="H36" s="86"/>
+      <x:c r="I36" s="86"/>
+      <x:c r="J36" s="86"/>
+      <x:c r="K36" s="86"/>
+      <x:c r="L36" s="86"/>
+      <x:c r="M36" s="92"/>
+      <x:c r="N36" s="86"/>
+      <x:c r="O36" s="86"/>
+      <x:c r="P36" s="86"/>
+      <x:c r="Q36" s="86"/>
+      <x:c r="R36" s="86"/>
+      <x:c r="S36" s="87"/>
+      <x:c r="T36" s="96" t="str">
+        <x:f>IF(COUNTA(A36:S36)=0,"NOT STARTED",IF(OR(A36="",B36="",C36="",D36="",E36="",F36="",G36="",H36="",I36="",J36="",K36="",L36="",M36="",N36="",O36="",P36="",Q36="",R36="",S36=""),"INCOMPLETE",IF(OR(S36="Needs revision",AND(OR(N36="Contradicted",N36="Not verifiable"),S36&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="66" customHeight="1">
+      <x:c r="A37" s="88"/>
+      <x:c r="B37" s="93"/>
+      <x:c r="C37" s="89"/>
+      <x:c r="D37" s="89"/>
+      <x:c r="E37" s="89"/>
+      <x:c r="F37" s="89"/>
+      <x:c r="G37" s="89"/>
+      <x:c r="H37" s="89"/>
+      <x:c r="I37" s="89"/>
+      <x:c r="J37" s="89"/>
+      <x:c r="K37" s="89"/>
+      <x:c r="L37" s="89"/>
+      <x:c r="M37" s="93"/>
+      <x:c r="N37" s="89"/>
+      <x:c r="O37" s="89"/>
+      <x:c r="P37" s="89"/>
+      <x:c r="Q37" s="89"/>
+      <x:c r="R37" s="89"/>
+      <x:c r="S37" s="90"/>
+      <x:c r="T37" s="96" t="str">
+        <x:f>IF(COUNTA(A37:S37)=0,"NOT STARTED",IF(OR(A37="",B37="",C37="",D37="",E37="",F37="",G37="",H37="",I37="",J37="",K37="",L37="",M37="",N37="",O37="",P37="",Q37="",R37="",S37=""),"INCOMPLETE",IF(OR(S37="Needs revision",AND(OR(N37="Contradicted",N37="Not verifiable"),S37&lt;&gt;"Cleared after revision")),"REVISE / FLAG","EVIDENCE READY")))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="23" customHeight="1">
+      <x:c r="A39" s="11" t="str">
+        <x:v>PHASE 1 READINESS</x:v>
+      </x:c>
+      <x:c r="B39" s="11"/>
+      <x:c r="C39" s="11"/>
+      <x:c r="D39" s="11"/>
+      <x:c r="E39" s="11"/>
+      <x:c r="F39" s="11"/>
+      <x:c r="G39" s="11"/>
+      <x:c r="H39" s="11"/>
+      <x:c r="I39" s="11"/>
+      <x:c r="J39" s="11"/>
+      <x:c r="K39" s="11"/>
+      <x:c r="L39" s="11"/>
+      <x:c r="M39" s="11"/>
+      <x:c r="N39" s="11"/>
+      <x:c r="O39" s="11"/>
+      <x:c r="P39" s="11"/>
+      <x:c r="Q39" s="11"/>
+      <x:c r="R39" s="11"/>
+      <x:c r="S39" s="11"/>
+      <x:c r="T39" s="11"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="25" t="str">
+        <x:v>Evidence-ready entries</x:v>
+      </x:c>
+      <x:c r="B40" s="97" t="n">
+        <x:f>COUNTIF(T8:T37,"EVIDENCE READY")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C40" s="97" t="str"/>
+      <x:c r="D40" s="25" t="str">
+        <x:v>Entries to revise / flag</x:v>
+      </x:c>
+      <x:c r="E40" s="99" t="n">
+        <x:f>COUNTIF(T8:T37,"REVISE / FLAG")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F40" s="99" t="str"/>
+      <x:c r="G40" s="25" t="str">
+        <x:v>Minimum required</x:v>
+      </x:c>
+      <x:c r="H40" s="57" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J40" s="25" t="str">
+        <x:v>Log readiness</x:v>
+      </x:c>
+      <x:c r="K40" s="100" t="str">
+        <x:f>IF(OR(E6="",H6="",K6=""),"ENTER 3 CLIENTS",IF(COUNTIF(B47:D50,"READY")&lt;H40,"COVERAGE INCOMPLETE",IF(COUNTIF(T8:T37,"INCOMPLETE")+E40&gt;0,"REVIEW LOG","READY FOR PHASE 1 GATE")))</x:f>
+        <x:v>ENTER 3 CLIENTS</x:v>
+      </x:c>
+      <x:c r="L40" s="101"/>
+      <x:c r="M40" s="102"/>
+    </x:row>
+    <x:row r="42" ht="34" customHeight="1">
+      <x:c r="A42" s="104" t="str">
+        <x:v>Evidence-ready means the entry shows the initial judgment, the AI challenge, a human-verified source and as-of date, what changed, the final reasoning, a downstream guardrail, and peer review. Contradicted or unverifiable material claims must be revised or carried to the committee as an explicit open issue.</x:v>
+      </x:c>
+      <x:c r="B42" s="104"/>
+      <x:c r="C42" s="104"/>
+      <x:c r="D42" s="104"/>
+      <x:c r="E42" s="104"/>
+      <x:c r="F42" s="104"/>
+      <x:c r="G42" s="104"/>
+      <x:c r="H42" s="104"/>
+      <x:c r="I42" s="104"/>
+      <x:c r="J42" s="104"/>
+      <x:c r="K42" s="104"/>
+      <x:c r="L42" s="104"/>
+      <x:c r="M42" s="104"/>
+      <x:c r="N42" s="104"/>
+      <x:c r="O42" s="104"/>
+      <x:c r="P42" s="104"/>
+      <x:c r="Q42" s="104"/>
+      <x:c r="R42" s="104"/>
+      <x:c r="S42" s="104"/>
+      <x:c r="T42" s="104"/>
+    </x:row>
+    <x:row r="45" ht="23" customHeight="1">
+      <x:c r="A45" s="11" t="str">
+        <x:v>ROLE × CLIENT COVERAGE</x:v>
+      </x:c>
+      <x:c r="B45" s="11"/>
+      <x:c r="C45" s="11"/>
+      <x:c r="D45" s="11"/>
+      <x:c r="E45" s="11"/>
+      <x:c r="F45" s="11"/>
+      <x:c r="G45" s="11"/>
+      <x:c r="H45" s="11"/>
+      <x:c r="I45" s="11"/>
+      <x:c r="J45" s="11"/>
+      <x:c r="K45" s="11"/>
+      <x:c r="L45" s="11"/>
+      <x:c r="M45" s="11"/>
+      <x:c r="N45" s="11"/>
+      <x:c r="O45" s="11"/>
+      <x:c r="P45" s="11"/>
+      <x:c r="Q45" s="11"/>
+      <x:c r="R45" s="11"/>
+      <x:c r="S45" s="11"/>
+      <x:c r="T45" s="11"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="21" t="str">
+        <x:v>Committee role</x:v>
+      </x:c>
+      <x:c r="B46" s="21" t="str">
+        <x:v>Assigned Client 1</x:v>
+      </x:c>
+      <x:c r="C46" s="21" t="str">
+        <x:v>Assigned Client 2</x:v>
+      </x:c>
+      <x:c r="D46" s="21" t="str">
+        <x:v>Assigned Client 3</x:v>
+      </x:c>
+      <x:c r="E46" s="21" t="str">
+        <x:v>Role coverage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="52" t="str">
+        <x:v>Client and Macro Strategist</x:v>
+      </x:c>
+      <x:c r="B47" s="107" t="str">
+        <x:f>IF(OR($E$6="",COUNTIFS($C$8:$C$37,$E$6,$D$8:$D$37,$A47,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+      <x:c r="C47" s="107" t="str">
+        <x:f>IF(OR($H$6="",COUNTIFS($C$8:$C$37,$H$6,$D$8:$D$37,$A47,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+      <x:c r="D47" s="107" t="str">
+        <x:f>IF(OR($K$6="",COUNTIFS($C$8:$C$37,$K$6,$D$8:$D$37,$A47,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+      <x:c r="E47" s="107" t="str">
+        <x:f>IF(COUNTIF(B47:D47,"MISSING")&gt;0,"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="52" t="str">
+        <x:v>Fixed-Income Analyst</x:v>
+      </x:c>
+      <x:c r="B48" s="107" t="str">
+        <x:f>IF(OR($E$6="",COUNTIFS($C$8:$C$37,$E$6,$D$8:$D$37,$A48,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+      <x:c r="C48" s="107" t="str">
+        <x:f>IF(OR($H$6="",COUNTIFS($C$8:$C$37,$H$6,$D$8:$D$37,$A48,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+      <x:c r="D48" s="107" t="str">
+        <x:f>IF(OR($K$6="",COUNTIFS($C$8:$C$37,$K$6,$D$8:$D$37,$A48,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+      <x:c r="E48" s="107" t="str">
+        <x:f>IF(COUNTIF(B48:D48,"MISSING")&gt;0,"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="52" t="str">
+        <x:v>Fund and ETF Analyst</x:v>
+      </x:c>
+      <x:c r="B49" s="107" t="str">
+        <x:f>IF(OR($E$6="",COUNTIFS($C$8:$C$37,$E$6,$D$8:$D$37,$A49,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+      <x:c r="C49" s="107" t="str">
+        <x:f>IF(OR($H$6="",COUNTIFS($C$8:$C$37,$H$6,$D$8:$D$37,$A49,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+      <x:c r="D49" s="107" t="str">
+        <x:f>IF(OR($K$6="",COUNTIFS($C$8:$C$37,$K$6,$D$8:$D$37,$A49,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+      <x:c r="E49" s="107" t="str">
+        <x:f>IF(COUNTIF(B49:D49,"MISSING")&gt;0,"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="52" t="str">
+        <x:v>Portfolio Manager and Risk Analyst</x:v>
+      </x:c>
+      <x:c r="B50" s="107" t="str">
+        <x:f>IF(OR($E$6="",COUNTIFS($C$8:$C$37,$E$6,$D$8:$D$37,$A50,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+      <x:c r="C50" s="107" t="str">
+        <x:f>IF(OR($H$6="",COUNTIFS($C$8:$C$37,$H$6,$D$8:$D$37,$A50,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+      <x:c r="D50" s="107" t="str">
+        <x:f>IF(OR($K$6="",COUNTIFS($C$8:$C$37,$K$6,$D$8:$D$37,$A50,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+      <x:c r="E50" s="107" t="str">
+        <x:f>IF(COUNTIF(B50:D50,"MISSING")&gt;0,"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="30" customHeight="1">
+      <x:c r="A52" s="104" t="str">
+        <x:v>The Phase 1 gate remains closed until every role has at least one evidence-ready entry for each of the three assigned clients. The client names in row 6 must match the Client column exactly.</x:v>
+      </x:c>
+      <x:c r="B52" s="104"/>
+      <x:c r="C52" s="104"/>
+      <x:c r="D52" s="104"/>
+      <x:c r="E52" s="104"/>
+      <x:c r="F52" s="104"/>
+      <x:c r="G52" s="104"/>
+      <x:c r="H52" s="104"/>
+      <x:c r="I52" s="104"/>
+      <x:c r="J52" s="104"/>
+      <x:c r="K52" s="104"/>
+      <x:c r="L52" s="104"/>
+      <x:c r="M52" s="104"/>
+      <x:c r="N52" s="104"/>
+      <x:c r="O52" s="104"/>
+      <x:c r="P52" s="104"/>
+      <x:c r="Q52" s="104"/>
+      <x:c r="R52" s="104"/>
+      <x:c r="S52" s="104"/>
+      <x:c r="T52" s="104"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:T1"/>
+    <x:mergeCell ref="A2:T2"/>
+    <x:mergeCell ref="A4:T4"/>
+    <x:mergeCell ref="A5:T5"/>
+    <x:mergeCell ref="B6:C6"/>
+    <x:mergeCell ref="E6:F6"/>
+    <x:mergeCell ref="H6:I6"/>
+    <x:mergeCell ref="K6:L6"/>
+    <x:mergeCell ref="A39:T39"/>
+    <x:mergeCell ref="B40:C40"/>
+    <x:mergeCell ref="E40:F40"/>
+    <x:mergeCell ref="K40:M40"/>
+    <x:mergeCell ref="A42:T42"/>
+    <x:mergeCell ref="A45:T45"/>
+    <x:mergeCell ref="A52:T52"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="T8:T37">
+    <x:cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="EVIDENCE READY"/>
+    <x:cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="REVISE"/>
+    <x:cfRule type="containsText" dxfId="15" priority="3" operator="containsText" text="INCOMPLETE"/>
+    <x:cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="MINIMUM"/>
+    <x:cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="REVIEW"/>
+    <x:cfRule type="containsText" dxfId="18" priority="6" operator="containsText" text="MISSING"/>
+    <x:cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="ENTER"/>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="K40:M40">
+    <x:cfRule type="containsText" dxfId="20" priority="8" operator="containsText" text="EVIDENCE READY"/>
+    <x:cfRule type="containsText" dxfId="21" priority="9" operator="containsText" text="REVISE"/>
+    <x:cfRule type="containsText" dxfId="22" priority="10" operator="containsText" text="INCOMPLETE"/>
+    <x:cfRule type="containsText" dxfId="23" priority="11" operator="containsText" text="MINIMUM"/>
+    <x:cfRule type="containsText" dxfId="24" priority="12" operator="containsText" text="REVIEW"/>
+    <x:cfRule type="containsText" dxfId="25" priority="13" operator="containsText" text="MISSING"/>
+    <x:cfRule type="containsText" dxfId="26" priority="14" operator="containsText" text="ENTER"/>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="B47:E50">
+    <x:cfRule type="containsText" dxfId="27" priority="15" operator="containsText" text="EVIDENCE READY"/>
+    <x:cfRule type="containsText" dxfId="28" priority="16" operator="containsText" text="REVISE"/>
+    <x:cfRule type="containsText" dxfId="29" priority="17" operator="containsText" text="INCOMPLETE"/>
+    <x:cfRule type="containsText" dxfId="30" priority="18" operator="containsText" text="MINIMUM"/>
+    <x:cfRule type="containsText" dxfId="31" priority="19" operator="containsText" text="REVIEW"/>
+    <x:cfRule type="containsText" dxfId="32" priority="20" operator="containsText" text="MISSING"/>
+    <x:cfRule type="containsText" dxfId="33" priority="21" operator="containsText" text="ENTER"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="5">
+    <x:dataValidation type="list" sqref="D8:D37">
+      <x:formula1>"Client and Macro Strategist,Fixed-Income Analyst,Fund and ETF Analyst,Portfolio Manager and Risk Analyst"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="G8:G37">
+      <x:formula1>"Low,Medium,High"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="H8:H37">
+      <x:formula1>"Client fact,Analyst assumption,Market claim,Product / security claim"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="N8:N37">
+      <x:formula1>"Confirmed,Qualified,Contradicted,Not verifiable"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="S8:S37">
+      <x:formula1>"Cleared,Cleared after revision,Needs revision"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
@@ -1474,21 +3122,21 @@
       <x:c r="A4" s="25" t="str">
         <x:v>Team / Committee Name</x:v>
       </x:c>
-      <x:c r="B4" s="64"/>
-      <x:c r="C4" s="65"/>
+      <x:c r="B4" s="82"/>
+      <x:c r="C4" s="84"/>
       <x:c r="D4" s="25" t="str">
         <x:v>Recorder</x:v>
       </x:c>
-      <x:c r="E4" s="76"/>
-      <x:c r="F4" s="77"/>
-      <x:c r="G4" s="78"/>
+      <x:c r="E4" s="63"/>
+      <x:c r="F4" s="110"/>
+      <x:c r="G4" s="64"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="25" t="str">
         <x:v>Scope: all three clients</x:v>
       </x:c>
-      <x:c r="B5" s="66"/>
-      <x:c r="C5" s="67"/>
+      <x:c r="B5" s="85"/>
+      <x:c r="C5" s="87"/>
       <x:c r="D5" s="25" t="str">
         <x:v>Gate</x:v>
       </x:c>
@@ -1502,14 +3150,14 @@
       <x:c r="A6" s="25" t="str">
         <x:v>Meeting Date</x:v>
       </x:c>
-      <x:c r="B6" s="79"/>
-      <x:c r="C6" s="80"/>
+      <x:c r="B6" s="111"/>
+      <x:c r="C6" s="112"/>
       <x:c r="D6" s="25" t="str">
         <x:v>Meeting Chair</x:v>
       </x:c>
-      <x:c r="E6" s="76"/>
-      <x:c r="F6" s="77"/>
-      <x:c r="G6" s="78"/>
+      <x:c r="E6" s="63"/>
+      <x:c r="F6" s="110"/>
+      <x:c r="G6" s="64"/>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
       <x:c r="A8" s="11" t="str">
@@ -1547,68 +3195,68 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="64" t="str"/>
-      <x:c r="B10" s="86" t="str"/>
-      <x:c r="C10" s="89" t="str"/>
-      <x:c r="D10" s="86" t="str"/>
-      <x:c r="E10" s="86" t="str"/>
-      <x:c r="F10" s="86" t="str"/>
-      <x:c r="G10" s="65" t="str">
+      <x:c r="A10" s="82" t="str"/>
+      <x:c r="B10" s="83" t="str"/>
+      <x:c r="C10" s="91" t="str"/>
+      <x:c r="D10" s="83" t="str"/>
+      <x:c r="E10" s="83" t="str"/>
+      <x:c r="F10" s="83" t="str"/>
+      <x:c r="G10" s="84" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="66" t="str"/>
-      <x:c r="B11" s="87" t="str"/>
-      <x:c r="C11" s="90" t="str"/>
-      <x:c r="D11" s="87" t="str"/>
-      <x:c r="E11" s="87" t="str"/>
-      <x:c r="F11" s="87" t="str"/>
-      <x:c r="G11" s="67" t="str">
+      <x:c r="A11" s="85" t="str"/>
+      <x:c r="B11" s="86" t="str"/>
+      <x:c r="C11" s="92" t="str"/>
+      <x:c r="D11" s="86" t="str"/>
+      <x:c r="E11" s="86" t="str"/>
+      <x:c r="F11" s="86" t="str"/>
+      <x:c r="G11" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="66" t="str"/>
-      <x:c r="B12" s="87" t="str"/>
-      <x:c r="C12" s="90" t="str"/>
-      <x:c r="D12" s="87" t="str"/>
-      <x:c r="E12" s="87" t="str"/>
-      <x:c r="F12" s="87" t="str"/>
-      <x:c r="G12" s="67" t="str">
+      <x:c r="A12" s="85" t="str"/>
+      <x:c r="B12" s="86" t="str"/>
+      <x:c r="C12" s="92" t="str"/>
+      <x:c r="D12" s="86" t="str"/>
+      <x:c r="E12" s="86" t="str"/>
+      <x:c r="F12" s="86" t="str"/>
+      <x:c r="G12" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="66" t="str"/>
-      <x:c r="B13" s="87" t="str"/>
-      <x:c r="C13" s="90" t="str"/>
-      <x:c r="D13" s="87" t="str"/>
-      <x:c r="E13" s="87" t="str"/>
-      <x:c r="F13" s="87" t="str"/>
-      <x:c r="G13" s="67" t="str">
+      <x:c r="A13" s="85" t="str"/>
+      <x:c r="B13" s="86" t="str"/>
+      <x:c r="C13" s="92" t="str"/>
+      <x:c r="D13" s="86" t="str"/>
+      <x:c r="E13" s="86" t="str"/>
+      <x:c r="F13" s="86" t="str"/>
+      <x:c r="G13" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="66" t="str"/>
-      <x:c r="B14" s="87" t="str"/>
-      <x:c r="C14" s="90" t="str"/>
-      <x:c r="D14" s="87" t="str"/>
-      <x:c r="E14" s="87" t="str"/>
-      <x:c r="F14" s="87" t="str"/>
-      <x:c r="G14" s="67" t="str">
+      <x:c r="A14" s="85" t="str"/>
+      <x:c r="B14" s="86" t="str"/>
+      <x:c r="C14" s="92" t="str"/>
+      <x:c r="D14" s="86" t="str"/>
+      <x:c r="E14" s="86" t="str"/>
+      <x:c r="F14" s="86" t="str"/>
+      <x:c r="G14" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="68" t="str"/>
-      <x:c r="B15" s="88" t="str"/>
-      <x:c r="C15" s="91" t="str"/>
-      <x:c r="D15" s="88" t="str"/>
-      <x:c r="E15" s="88" t="str"/>
-      <x:c r="F15" s="88" t="str"/>
-      <x:c r="G15" s="69" t="str">
+      <x:c r="A15" s="88" t="str"/>
+      <x:c r="B15" s="89" t="str"/>
+      <x:c r="C15" s="93" t="str"/>
+      <x:c r="D15" s="89" t="str"/>
+      <x:c r="E15" s="89" t="str"/>
+      <x:c r="F15" s="89" t="str"/>
+      <x:c r="G15" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
@@ -1616,11 +3264,11 @@
       <x:c r="A17" s="25" t="str">
         <x:v>Evidence status</x:v>
       </x:c>
-      <x:c r="B17" s="92" t="str">
+      <x:c r="B17" s="30" t="str">
         <x:f>IF(COUNTIF(G10:G15,"Reviewed")=6,"EVIDENCE COMPLETE","EVIDENCE INCOMPLETE")</x:f>
         <x:v>EVIDENCE INCOMPLETE</x:v>
       </x:c>
-      <x:c r="C17" s="92"/>
+      <x:c r="C17" s="30"/>
     </x:row>
     <x:row r="19" ht="23" customHeight="1">
       <x:c r="A19" s="11" t="str">
@@ -1635,24 +3283,24 @@
       <x:c r="H19" s="11"/>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
-      <x:c r="A20" s="32" t="str">
+      <x:c r="A20" s="37" t="str">
         <x:v>Write the exact motion presented to the committee. It must name the recommendation, scope, and any conditions.</x:v>
       </x:c>
-      <x:c r="B20" s="32"/>
-      <x:c r="C20" s="32"/>
-      <x:c r="D20" s="32"/>
-      <x:c r="E20" s="32"/>
-      <x:c r="F20" s="32"/>
-      <x:c r="G20" s="32"/>
+      <x:c r="B20" s="37"/>
+      <x:c r="C20" s="37"/>
+      <x:c r="D20" s="37"/>
+      <x:c r="E20" s="37"/>
+      <x:c r="F20" s="37"/>
+      <x:c r="G20" s="37"/>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
-      <x:c r="A21" s="76"/>
-      <x:c r="B21" s="77"/>
-      <x:c r="C21" s="77"/>
-      <x:c r="D21" s="77"/>
-      <x:c r="E21" s="77"/>
-      <x:c r="F21" s="77"/>
-      <x:c r="G21" s="78"/>
+      <x:c r="A21" s="63"/>
+      <x:c r="B21" s="110"/>
+      <x:c r="C21" s="110"/>
+      <x:c r="D21" s="110"/>
+      <x:c r="E21" s="110"/>
+      <x:c r="F21" s="110"/>
+      <x:c r="G21" s="64"/>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
       <x:c r="A23" s="11" t="str">
@@ -1690,48 +3338,48 @@
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="94" t="str">
-        <x:v>Chair &amp; Mandate</x:v>
-      </x:c>
-      <x:c r="B25" s="64" t="str"/>
-      <x:c r="C25" s="86" t="str"/>
-      <x:c r="D25" s="86" t="str"/>
-      <x:c r="E25" s="86" t="str"/>
-      <x:c r="F25" s="86" t="str"/>
-      <x:c r="G25" s="65" t="str"/>
+      <x:c r="A25" s="114" t="str">
+        <x:v>Client &amp; Macro</x:v>
+      </x:c>
+      <x:c r="B25" s="82" t="str"/>
+      <x:c r="C25" s="83" t="str"/>
+      <x:c r="D25" s="83" t="str"/>
+      <x:c r="E25" s="83" t="str"/>
+      <x:c r="F25" s="83" t="str"/>
+      <x:c r="G25" s="84" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="94" t="str">
-        <x:v>Markets Strategist</x:v>
-      </x:c>
-      <x:c r="B26" s="66" t="str"/>
-      <x:c r="C26" s="87" t="str"/>
-      <x:c r="D26" s="87" t="str"/>
-      <x:c r="E26" s="87" t="str"/>
-      <x:c r="F26" s="87" t="str"/>
-      <x:c r="G26" s="67" t="str"/>
+      <x:c r="A26" s="114" t="str">
+        <x:v>Fixed Income</x:v>
+      </x:c>
+      <x:c r="B26" s="85" t="str"/>
+      <x:c r="C26" s="86" t="str"/>
+      <x:c r="D26" s="86" t="str"/>
+      <x:c r="E26" s="86" t="str"/>
+      <x:c r="F26" s="86" t="str"/>
+      <x:c r="G26" s="87" t="str"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="94" t="str">
-        <x:v>Portfolio Lead</x:v>
-      </x:c>
-      <x:c r="B27" s="66" t="str"/>
-      <x:c r="C27" s="87" t="str"/>
-      <x:c r="D27" s="87" t="str"/>
-      <x:c r="E27" s="87" t="str"/>
-      <x:c r="F27" s="87" t="str"/>
-      <x:c r="G27" s="67" t="str"/>
+      <x:c r="A27" s="114" t="str">
+        <x:v>Fund &amp; ETF</x:v>
+      </x:c>
+      <x:c r="B27" s="85" t="str"/>
+      <x:c r="C27" s="86" t="str"/>
+      <x:c r="D27" s="86" t="str"/>
+      <x:c r="E27" s="86" t="str"/>
+      <x:c r="F27" s="86" t="str"/>
+      <x:c r="G27" s="87" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="94" t="str">
-        <x:v>Risk &amp; Challenge</x:v>
-      </x:c>
-      <x:c r="B28" s="68" t="str"/>
-      <x:c r="C28" s="88" t="str"/>
-      <x:c r="D28" s="88" t="str"/>
-      <x:c r="E28" s="88" t="str"/>
-      <x:c r="F28" s="88" t="str"/>
-      <x:c r="G28" s="69" t="str"/>
+      <x:c r="A28" s="114" t="str">
+        <x:v>Portfolio &amp; Risk</x:v>
+      </x:c>
+      <x:c r="B28" s="88" t="str"/>
+      <x:c r="C28" s="89" t="str"/>
+      <x:c r="D28" s="89" t="str"/>
+      <x:c r="E28" s="89" t="str"/>
+      <x:c r="F28" s="89" t="str"/>
+      <x:c r="G28" s="90" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="25" t="str">
@@ -1756,22 +3404,22 @@
       <x:c r="H32" s="11"/>
     </x:row>
     <x:row r="33" ht="34" customHeight="1">
-      <x:c r="A33" s="64"/>
-      <x:c r="B33" s="86"/>
-      <x:c r="C33" s="86"/>
-      <x:c r="D33" s="86"/>
-      <x:c r="E33" s="86"/>
-      <x:c r="F33" s="86"/>
-      <x:c r="G33" s="65"/>
+      <x:c r="A33" s="82"/>
+      <x:c r="B33" s="83"/>
+      <x:c r="C33" s="83"/>
+      <x:c r="D33" s="83"/>
+      <x:c r="E33" s="83"/>
+      <x:c r="F33" s="83"/>
+      <x:c r="G33" s="84"/>
     </x:row>
     <x:row r="34" ht="34" customHeight="1">
-      <x:c r="A34" s="68"/>
-      <x:c r="B34" s="88"/>
-      <x:c r="C34" s="88"/>
-      <x:c r="D34" s="88"/>
-      <x:c r="E34" s="88"/>
-      <x:c r="F34" s="88"/>
-      <x:c r="G34" s="69"/>
+      <x:c r="A34" s="88"/>
+      <x:c r="B34" s="89"/>
+      <x:c r="C34" s="89"/>
+      <x:c r="D34" s="89"/>
+      <x:c r="E34" s="89"/>
+      <x:c r="F34" s="89"/>
+      <x:c r="G34" s="90"/>
     </x:row>
     <x:row r="36" ht="23" customHeight="1">
       <x:c r="A36" s="11" t="str">
@@ -1809,70 +3457,70 @@
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="64" t="str"/>
-      <x:c r="B38" s="86" t="str"/>
-      <x:c r="C38" s="89" t="str"/>
-      <x:c r="D38" s="86" t="str"/>
-      <x:c r="E38" s="86" t="str">
+      <x:c r="A38" s="82" t="str"/>
+      <x:c r="B38" s="83" t="str"/>
+      <x:c r="C38" s="91" t="str"/>
+      <x:c r="D38" s="83" t="str"/>
+      <x:c r="E38" s="83" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F38" s="86" t="str"/>
-      <x:c r="G38" s="65" t="str"/>
+      <x:c r="F38" s="83" t="str"/>
+      <x:c r="G38" s="84" t="str"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="66" t="str"/>
-      <x:c r="B39" s="87" t="str"/>
-      <x:c r="C39" s="90" t="str"/>
-      <x:c r="D39" s="87" t="str"/>
-      <x:c r="E39" s="87" t="str">
+      <x:c r="A39" s="85" t="str"/>
+      <x:c r="B39" s="86" t="str"/>
+      <x:c r="C39" s="92" t="str"/>
+      <x:c r="D39" s="86" t="str"/>
+      <x:c r="E39" s="86" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F39" s="87" t="str"/>
-      <x:c r="G39" s="67" t="str"/>
+      <x:c r="F39" s="86" t="str"/>
+      <x:c r="G39" s="87" t="str"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="66" t="str"/>
-      <x:c r="B40" s="87" t="str"/>
-      <x:c r="C40" s="90" t="str"/>
-      <x:c r="D40" s="87" t="str"/>
-      <x:c r="E40" s="87" t="str">
+      <x:c r="A40" s="85" t="str"/>
+      <x:c r="B40" s="86" t="str"/>
+      <x:c r="C40" s="92" t="str"/>
+      <x:c r="D40" s="86" t="str"/>
+      <x:c r="E40" s="86" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F40" s="87" t="str"/>
-      <x:c r="G40" s="67" t="str"/>
+      <x:c r="F40" s="86" t="str"/>
+      <x:c r="G40" s="87" t="str"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="66" t="str"/>
-      <x:c r="B41" s="87" t="str"/>
-      <x:c r="C41" s="90" t="str"/>
-      <x:c r="D41" s="87" t="str"/>
-      <x:c r="E41" s="87" t="str">
+      <x:c r="A41" s="85" t="str"/>
+      <x:c r="B41" s="86" t="str"/>
+      <x:c r="C41" s="92" t="str"/>
+      <x:c r="D41" s="86" t="str"/>
+      <x:c r="E41" s="86" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F41" s="87" t="str"/>
-      <x:c r="G41" s="67" t="str"/>
+      <x:c r="F41" s="86" t="str"/>
+      <x:c r="G41" s="87" t="str"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="68" t="str"/>
-      <x:c r="B42" s="88" t="str"/>
-      <x:c r="C42" s="91" t="str"/>
-      <x:c r="D42" s="88" t="str"/>
-      <x:c r="E42" s="88" t="str">
+      <x:c r="A42" s="88" t="str"/>
+      <x:c r="B42" s="89" t="str"/>
+      <x:c r="C42" s="93" t="str"/>
+      <x:c r="D42" s="89" t="str"/>
+      <x:c r="E42" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F42" s="88" t="str"/>
-      <x:c r="G42" s="69" t="str"/>
+      <x:c r="F42" s="89" t="str"/>
+      <x:c r="G42" s="90" t="str"/>
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
-      <x:c r="A44" s="96" t="str">
+      <x:c r="A44" s="104" t="str">
         <x:v>Approval requires four Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
       </x:c>
-      <x:c r="B44" s="96"/>
-      <x:c r="C44" s="96"/>
-      <x:c r="D44" s="96"/>
-      <x:c r="E44" s="96"/>
-      <x:c r="F44" s="96"/>
-      <x:c r="G44" s="96"/>
+      <x:c r="B44" s="104"/>
+      <x:c r="C44" s="104"/>
+      <x:c r="D44" s="104"/>
+      <x:c r="E44" s="104"/>
+      <x:c r="F44" s="104"/>
+      <x:c r="G44" s="104"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1897,493 +3545,9 @@
     <x:mergeCell ref="A44:G44"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B30:C30">
-    <x:cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="APPROVED"/>
-    <x:cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="REVISION"/>
-    <x:cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="INCOMPLETE"/>
-  </x:conditionalFormatting>
-  <x:dataValidations count="3">
-    <x:dataValidation type="list" sqref="G10:G15">
-      <x:formula1>"Not reviewed,Reviewed,Needs follow-up"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="C25:C28">
-      <x:formula1>"Approve,Revise,Reject"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="E38:E42">
-      <x:formula1>"Open,Complete"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="4" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>BUS331 Investment Committee — Phase 2 Decision Record</x:v>
-      </x:c>
-      <x:c r="B1" s="3"/>
-      <x:c r="C1" s="3"/>
-      <x:c r="D1" s="3"/>
-      <x:c r="E1" s="3"/>
-      <x:c r="F1" s="3"/>
-      <x:c r="G1" s="3"/>
-      <x:c r="H1" s="3"/>
-    </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="6" t="str">
-        <x:v>Build &amp; Challenge | All four committee members review, vote, and sign this record.</x:v>
-      </x:c>
-      <x:c r="B2" s="6"/>
-      <x:c r="C2" s="6"/>
-      <x:c r="D2" s="6"/>
-      <x:c r="E2" s="6"/>
-      <x:c r="F2" s="6"/>
-      <x:c r="G2" s="6"/>
-      <x:c r="H2" s="6"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="25" t="str">
-        <x:v>Team / Committee Name</x:v>
-      </x:c>
-      <x:c r="B4" s="64"/>
-      <x:c r="C4" s="65"/>
-      <x:c r="D4" s="25" t="str">
-        <x:v>Recorder</x:v>
-      </x:c>
-      <x:c r="E4" s="76"/>
-      <x:c r="F4" s="77"/>
-      <x:c r="G4" s="78"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="25" t="str">
-        <x:v>Client name / case</x:v>
-      </x:c>
-      <x:c r="B5" s="66"/>
-      <x:c r="C5" s="67"/>
-      <x:c r="D5" s="25" t="str">
-        <x:v>Gate</x:v>
-      </x:c>
-      <x:c r="E5" s="14" t="str">
-        <x:v>Approve, revise, or reject Client 1 portfolio</x:v>
-      </x:c>
-      <x:c r="F5" s="14"/>
-      <x:c r="G5" s="14"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="25" t="str">
-        <x:v>Meeting Date</x:v>
-      </x:c>
-      <x:c r="B6" s="79"/>
-      <x:c r="C6" s="80"/>
-      <x:c r="D6" s="25" t="str">
-        <x:v>Meeting Chair</x:v>
-      </x:c>
-      <x:c r="E6" s="76"/>
-      <x:c r="F6" s="77"/>
-      <x:c r="G6" s="78"/>
-    </x:row>
-    <x:row r="8" ht="23" customHeight="1">
-      <x:c r="A8" s="11" t="str">
-        <x:v>EVIDENCE REVIEWED</x:v>
-      </x:c>
-      <x:c r="B8" s="11"/>
-      <x:c r="C8" s="11"/>
-      <x:c r="D8" s="11"/>
-      <x:c r="E8" s="11"/>
-      <x:c r="F8" s="11"/>
-      <x:c r="G8" s="11"/>
-      <x:c r="H8" s="11"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="21" t="str">
-        <x:v>Evidence item</x:v>
-      </x:c>
-      <x:c r="B9" s="21" t="str">
-        <x:v>Location / file</x:v>
-      </x:c>
-      <x:c r="C9" s="21" t="str">
-        <x:v>Source date</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="str">
-        <x:v>Prepared by</x:v>
-      </x:c>
-      <x:c r="E9" s="21" t="str">
-        <x:v>Reviewed by</x:v>
-      </x:c>
-      <x:c r="F9" s="21" t="str">
-        <x:v>Key issue</x:v>
-      </x:c>
-      <x:c r="G9" s="21" t="str">
-        <x:v>Review status</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="64" t="str"/>
-      <x:c r="B10" s="86" t="str"/>
-      <x:c r="C10" s="89" t="str"/>
-      <x:c r="D10" s="86" t="str"/>
-      <x:c r="E10" s="86" t="str"/>
-      <x:c r="F10" s="86" t="str"/>
-      <x:c r="G10" s="65" t="str">
-        <x:v>Not reviewed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="66" t="str"/>
-      <x:c r="B11" s="87" t="str"/>
-      <x:c r="C11" s="90" t="str"/>
-      <x:c r="D11" s="87" t="str"/>
-      <x:c r="E11" s="87" t="str"/>
-      <x:c r="F11" s="87" t="str"/>
-      <x:c r="G11" s="67" t="str">
-        <x:v>Not reviewed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="66" t="str"/>
-      <x:c r="B12" s="87" t="str"/>
-      <x:c r="C12" s="90" t="str"/>
-      <x:c r="D12" s="87" t="str"/>
-      <x:c r="E12" s="87" t="str"/>
-      <x:c r="F12" s="87" t="str"/>
-      <x:c r="G12" s="67" t="str">
-        <x:v>Not reviewed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="66" t="str"/>
-      <x:c r="B13" s="87" t="str"/>
-      <x:c r="C13" s="90" t="str"/>
-      <x:c r="D13" s="87" t="str"/>
-      <x:c r="E13" s="87" t="str"/>
-      <x:c r="F13" s="87" t="str"/>
-      <x:c r="G13" s="67" t="str">
-        <x:v>Not reviewed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="66" t="str"/>
-      <x:c r="B14" s="87" t="str"/>
-      <x:c r="C14" s="90" t="str"/>
-      <x:c r="D14" s="87" t="str"/>
-      <x:c r="E14" s="87" t="str"/>
-      <x:c r="F14" s="87" t="str"/>
-      <x:c r="G14" s="67" t="str">
-        <x:v>Not reviewed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="68" t="str"/>
-      <x:c r="B15" s="88" t="str"/>
-      <x:c r="C15" s="91" t="str"/>
-      <x:c r="D15" s="88" t="str"/>
-      <x:c r="E15" s="88" t="str"/>
-      <x:c r="F15" s="88" t="str"/>
-      <x:c r="G15" s="69" t="str">
-        <x:v>Not reviewed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="25" t="str">
-        <x:v>Evidence status</x:v>
-      </x:c>
-      <x:c r="B17" s="92" t="str">
-        <x:f>IF(COUNTIF(G10:G15,"Reviewed")=6,"EVIDENCE COMPLETE","EVIDENCE INCOMPLETE")</x:f>
-        <x:v>EVIDENCE INCOMPLETE</x:v>
-      </x:c>
-      <x:c r="C17" s="92"/>
-    </x:row>
-    <x:row r="19" ht="23" customHeight="1">
-      <x:c r="A19" s="11" t="str">
-        <x:v>MOTION</x:v>
-      </x:c>
-      <x:c r="B19" s="11"/>
-      <x:c r="C19" s="11"/>
-      <x:c r="D19" s="11"/>
-      <x:c r="E19" s="11"/>
-      <x:c r="F19" s="11"/>
-      <x:c r="G19" s="11"/>
-      <x:c r="H19" s="11"/>
-    </x:row>
-    <x:row r="20" ht="30" customHeight="1">
-      <x:c r="A20" s="32" t="str">
-        <x:v>Write the exact motion presented to the committee. It must name the recommendation, scope, and any conditions.</x:v>
-      </x:c>
-      <x:c r="B20" s="32"/>
-      <x:c r="C20" s="32"/>
-      <x:c r="D20" s="32"/>
-      <x:c r="E20" s="32"/>
-      <x:c r="F20" s="32"/>
-      <x:c r="G20" s="32"/>
-    </x:row>
-    <x:row r="21" ht="42" customHeight="1">
-      <x:c r="A21" s="76"/>
-      <x:c r="B21" s="77"/>
-      <x:c r="C21" s="77"/>
-      <x:c r="D21" s="77"/>
-      <x:c r="E21" s="77"/>
-      <x:c r="F21" s="77"/>
-      <x:c r="G21" s="78"/>
-    </x:row>
-    <x:row r="23" ht="23" customHeight="1">
-      <x:c r="A23" s="11" t="str">
-        <x:v>COMMITTEE VOTE</x:v>
-      </x:c>
-      <x:c r="B23" s="11"/>
-      <x:c r="C23" s="11"/>
-      <x:c r="D23" s="11"/>
-      <x:c r="E23" s="11"/>
-      <x:c r="F23" s="11"/>
-      <x:c r="G23" s="11"/>
-      <x:c r="H23" s="11"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="21" t="str">
-        <x:v>Committee seat</x:v>
-      </x:c>
-      <x:c r="B24" s="21" t="str">
-        <x:v>Member name</x:v>
-      </x:c>
-      <x:c r="C24" s="21" t="str">
-        <x:v>Vote</x:v>
-      </x:c>
-      <x:c r="D24" s="21" t="str">
-        <x:v>Reservation / condition</x:v>
-      </x:c>
-      <x:c r="E24" s="21" t="str">
-        <x:v>Evidence cited</x:v>
-      </x:c>
-      <x:c r="F24" s="21" t="str">
-        <x:v>Initials</x:v>
-      </x:c>
-      <x:c r="G24" s="21" t="str">
-        <x:v>Follow-up owner</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="94" t="str">
-        <x:v>Chair &amp; Mandate</x:v>
-      </x:c>
-      <x:c r="B25" s="64" t="str"/>
-      <x:c r="C25" s="86" t="str"/>
-      <x:c r="D25" s="86" t="str"/>
-      <x:c r="E25" s="86" t="str"/>
-      <x:c r="F25" s="86" t="str"/>
-      <x:c r="G25" s="65" t="str"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="94" t="str">
-        <x:v>Markets Strategist</x:v>
-      </x:c>
-      <x:c r="B26" s="66" t="str"/>
-      <x:c r="C26" s="87" t="str"/>
-      <x:c r="D26" s="87" t="str"/>
-      <x:c r="E26" s="87" t="str"/>
-      <x:c r="F26" s="87" t="str"/>
-      <x:c r="G26" s="67" t="str"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="94" t="str">
-        <x:v>Portfolio Lead</x:v>
-      </x:c>
-      <x:c r="B27" s="66" t="str"/>
-      <x:c r="C27" s="87" t="str"/>
-      <x:c r="D27" s="87" t="str"/>
-      <x:c r="E27" s="87" t="str"/>
-      <x:c r="F27" s="87" t="str"/>
-      <x:c r="G27" s="67" t="str"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="94" t="str">
-        <x:v>Risk &amp; Challenge</x:v>
-      </x:c>
-      <x:c r="B28" s="68" t="str"/>
-      <x:c r="C28" s="88" t="str"/>
-      <x:c r="D28" s="88" t="str"/>
-      <x:c r="E28" s="88" t="str"/>
-      <x:c r="F28" s="88" t="str"/>
-      <x:c r="G28" s="69" t="str"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="25" t="str">
-        <x:v>Decision status</x:v>
-      </x:c>
-      <x:c r="B30" s="28" t="str">
-        <x:f>IF(COUNTIF(C25:C28,"Revise")+COUNTIF(C25:C28,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C28,"Approve")=4,"APPROVED","INCOMPLETE"))</x:f>
-        <x:v>INCOMPLETE</x:v>
-      </x:c>
-      <x:c r="C30" s="29"/>
-    </x:row>
-    <x:row r="32" ht="23" customHeight="1">
-      <x:c r="A32" s="11" t="str">
-        <x:v>DISSENT, RESERVATIONS &amp; CONDITIONS</x:v>
-      </x:c>
-      <x:c r="B32" s="11"/>
-      <x:c r="C32" s="11"/>
-      <x:c r="D32" s="11"/>
-      <x:c r="E32" s="11"/>
-      <x:c r="F32" s="11"/>
-      <x:c r="G32" s="11"/>
-      <x:c r="H32" s="11"/>
-    </x:row>
-    <x:row r="33" ht="34" customHeight="1">
-      <x:c r="A33" s="64"/>
-      <x:c r="B33" s="86"/>
-      <x:c r="C33" s="86"/>
-      <x:c r="D33" s="86"/>
-      <x:c r="E33" s="86"/>
-      <x:c r="F33" s="86"/>
-      <x:c r="G33" s="65"/>
-    </x:row>
-    <x:row r="34" ht="34" customHeight="1">
-      <x:c r="A34" s="68"/>
-      <x:c r="B34" s="88"/>
-      <x:c r="C34" s="88"/>
-      <x:c r="D34" s="88"/>
-      <x:c r="E34" s="88"/>
-      <x:c r="F34" s="88"/>
-      <x:c r="G34" s="69"/>
-    </x:row>
-    <x:row r="36" ht="23" customHeight="1">
-      <x:c r="A36" s="11" t="str">
-        <x:v>ACTION ITEMS</x:v>
-      </x:c>
-      <x:c r="B36" s="11"/>
-      <x:c r="C36" s="11"/>
-      <x:c r="D36" s="11"/>
-      <x:c r="E36" s="11"/>
-      <x:c r="F36" s="11"/>
-      <x:c r="G36" s="11"/>
-      <x:c r="H36" s="11"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="21" t="str">
-        <x:v>Action required</x:v>
-      </x:c>
-      <x:c r="B37" s="21" t="str">
-        <x:v>Owner</x:v>
-      </x:c>
-      <x:c r="C37" s="21" t="str">
-        <x:v>Due date</x:v>
-      </x:c>
-      <x:c r="D37" s="21" t="str">
-        <x:v>Evidence of completion</x:v>
-      </x:c>
-      <x:c r="E37" s="21" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="F37" s="21" t="str">
-        <x:v>Committee check</x:v>
-      </x:c>
-      <x:c r="G37" s="21" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="64" t="str"/>
-      <x:c r="B38" s="86" t="str"/>
-      <x:c r="C38" s="89" t="str"/>
-      <x:c r="D38" s="86" t="str"/>
-      <x:c r="E38" s="86" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F38" s="86" t="str"/>
-      <x:c r="G38" s="65" t="str"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="66" t="str"/>
-      <x:c r="B39" s="87" t="str"/>
-      <x:c r="C39" s="90" t="str"/>
-      <x:c r="D39" s="87" t="str"/>
-      <x:c r="E39" s="87" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F39" s="87" t="str"/>
-      <x:c r="G39" s="67" t="str"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="66" t="str"/>
-      <x:c r="B40" s="87" t="str"/>
-      <x:c r="C40" s="90" t="str"/>
-      <x:c r="D40" s="87" t="str"/>
-      <x:c r="E40" s="87" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F40" s="87" t="str"/>
-      <x:c r="G40" s="67" t="str"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="66" t="str"/>
-      <x:c r="B41" s="87" t="str"/>
-      <x:c r="C41" s="90" t="str"/>
-      <x:c r="D41" s="87" t="str"/>
-      <x:c r="E41" s="87" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F41" s="87" t="str"/>
-      <x:c r="G41" s="67" t="str"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="68" t="str"/>
-      <x:c r="B42" s="88" t="str"/>
-      <x:c r="C42" s="91" t="str"/>
-      <x:c r="D42" s="88" t="str"/>
-      <x:c r="E42" s="88" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F42" s="88" t="str"/>
-      <x:c r="G42" s="69" t="str"/>
-    </x:row>
-    <x:row r="44" ht="32" customHeight="1">
-      <x:c r="A44" s="96" t="str">
-        <x:v>Approval requires four Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
-      </x:c>
-      <x:c r="B44" s="96"/>
-      <x:c r="C44" s="96"/>
-      <x:c r="D44" s="96"/>
-      <x:c r="E44" s="96"/>
-      <x:c r="F44" s="96"/>
-      <x:c r="G44" s="96"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:H2"/>
-    <x:mergeCell ref="B4:C4"/>
-    <x:mergeCell ref="B5:C5"/>
-    <x:mergeCell ref="B6:C6"/>
-    <x:mergeCell ref="E4:G4"/>
-    <x:mergeCell ref="E5:G5"/>
-    <x:mergeCell ref="E6:G6"/>
-    <x:mergeCell ref="A8:H8"/>
-    <x:mergeCell ref="B17:C17"/>
-    <x:mergeCell ref="A19:H19"/>
-    <x:mergeCell ref="A20:G20"/>
-    <x:mergeCell ref="A21:G21"/>
-    <x:mergeCell ref="A23:H23"/>
-    <x:mergeCell ref="B30:C30"/>
-    <x:mergeCell ref="A32:H32"/>
-    <x:mergeCell ref="A33:G34"/>
-    <x:mergeCell ref="A36:H36"/>
-    <x:mergeCell ref="A44:G44"/>
-  </x:mergeCells>
-  <x:conditionalFormatting sqref="B30:C30">
-    <x:cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="APPROVED"/>
-    <x:cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="REVISION"/>
-    <x:cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="INCOMPLETE"/>
+    <x:cfRule type="containsText" dxfId="34" priority="1" operator="containsText" text="APPROVED"/>
+    <x:cfRule type="containsText" dxfId="35" priority="2" operator="containsText" text="REVISION"/>
+    <x:cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="INCOMPLETE"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="G10:G15">
@@ -2442,26 +3606,26 @@
       <x:c r="A4" s="25" t="str">
         <x:v>Team / Committee Name</x:v>
       </x:c>
-      <x:c r="B4" s="64"/>
-      <x:c r="C4" s="65"/>
+      <x:c r="B4" s="82"/>
+      <x:c r="C4" s="84"/>
       <x:c r="D4" s="25" t="str">
         <x:v>Recorder</x:v>
       </x:c>
-      <x:c r="E4" s="76"/>
-      <x:c r="F4" s="77"/>
-      <x:c r="G4" s="78"/>
+      <x:c r="E4" s="63"/>
+      <x:c r="F4" s="110"/>
+      <x:c r="G4" s="64"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="25" t="str">
         <x:v>Client name / case</x:v>
       </x:c>
-      <x:c r="B5" s="66"/>
-      <x:c r="C5" s="67"/>
+      <x:c r="B5" s="85"/>
+      <x:c r="C5" s="87"/>
       <x:c r="D5" s="25" t="str">
         <x:v>Gate</x:v>
       </x:c>
       <x:c r="E5" s="14" t="str">
-        <x:v>Approve, revise, or reject Client 2 portfolio</x:v>
+        <x:v>Approve, revise, or reject Client 1 portfolio</x:v>
       </x:c>
       <x:c r="F5" s="14"/>
       <x:c r="G5" s="14"/>
@@ -2470,14 +3634,14 @@
       <x:c r="A6" s="25" t="str">
         <x:v>Meeting Date</x:v>
       </x:c>
-      <x:c r="B6" s="79"/>
-      <x:c r="C6" s="80"/>
+      <x:c r="B6" s="111"/>
+      <x:c r="C6" s="112"/>
       <x:c r="D6" s="25" t="str">
         <x:v>Meeting Chair</x:v>
       </x:c>
-      <x:c r="E6" s="76"/>
-      <x:c r="F6" s="77"/>
-      <x:c r="G6" s="78"/>
+      <x:c r="E6" s="63"/>
+      <x:c r="F6" s="110"/>
+      <x:c r="G6" s="64"/>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
       <x:c r="A8" s="11" t="str">
@@ -2515,68 +3679,68 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="64" t="str"/>
-      <x:c r="B10" s="86" t="str"/>
-      <x:c r="C10" s="89" t="str"/>
-      <x:c r="D10" s="86" t="str"/>
-      <x:c r="E10" s="86" t="str"/>
-      <x:c r="F10" s="86" t="str"/>
-      <x:c r="G10" s="65" t="str">
+      <x:c r="A10" s="82" t="str"/>
+      <x:c r="B10" s="83" t="str"/>
+      <x:c r="C10" s="91" t="str"/>
+      <x:c r="D10" s="83" t="str"/>
+      <x:c r="E10" s="83" t="str"/>
+      <x:c r="F10" s="83" t="str"/>
+      <x:c r="G10" s="84" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="66" t="str"/>
-      <x:c r="B11" s="87" t="str"/>
-      <x:c r="C11" s="90" t="str"/>
-      <x:c r="D11" s="87" t="str"/>
-      <x:c r="E11" s="87" t="str"/>
-      <x:c r="F11" s="87" t="str"/>
-      <x:c r="G11" s="67" t="str">
+      <x:c r="A11" s="85" t="str"/>
+      <x:c r="B11" s="86" t="str"/>
+      <x:c r="C11" s="92" t="str"/>
+      <x:c r="D11" s="86" t="str"/>
+      <x:c r="E11" s="86" t="str"/>
+      <x:c r="F11" s="86" t="str"/>
+      <x:c r="G11" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="66" t="str"/>
-      <x:c r="B12" s="87" t="str"/>
-      <x:c r="C12" s="90" t="str"/>
-      <x:c r="D12" s="87" t="str"/>
-      <x:c r="E12" s="87" t="str"/>
-      <x:c r="F12" s="87" t="str"/>
-      <x:c r="G12" s="67" t="str">
+      <x:c r="A12" s="85" t="str"/>
+      <x:c r="B12" s="86" t="str"/>
+      <x:c r="C12" s="92" t="str"/>
+      <x:c r="D12" s="86" t="str"/>
+      <x:c r="E12" s="86" t="str"/>
+      <x:c r="F12" s="86" t="str"/>
+      <x:c r="G12" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="66" t="str"/>
-      <x:c r="B13" s="87" t="str"/>
-      <x:c r="C13" s="90" t="str"/>
-      <x:c r="D13" s="87" t="str"/>
-      <x:c r="E13" s="87" t="str"/>
-      <x:c r="F13" s="87" t="str"/>
-      <x:c r="G13" s="67" t="str">
+      <x:c r="A13" s="85" t="str"/>
+      <x:c r="B13" s="86" t="str"/>
+      <x:c r="C13" s="92" t="str"/>
+      <x:c r="D13" s="86" t="str"/>
+      <x:c r="E13" s="86" t="str"/>
+      <x:c r="F13" s="86" t="str"/>
+      <x:c r="G13" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="66" t="str"/>
-      <x:c r="B14" s="87" t="str"/>
-      <x:c r="C14" s="90" t="str"/>
-      <x:c r="D14" s="87" t="str"/>
-      <x:c r="E14" s="87" t="str"/>
-      <x:c r="F14" s="87" t="str"/>
-      <x:c r="G14" s="67" t="str">
+      <x:c r="A14" s="85" t="str"/>
+      <x:c r="B14" s="86" t="str"/>
+      <x:c r="C14" s="92" t="str"/>
+      <x:c r="D14" s="86" t="str"/>
+      <x:c r="E14" s="86" t="str"/>
+      <x:c r="F14" s="86" t="str"/>
+      <x:c r="G14" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="68" t="str"/>
-      <x:c r="B15" s="88" t="str"/>
-      <x:c r="C15" s="91" t="str"/>
-      <x:c r="D15" s="88" t="str"/>
-      <x:c r="E15" s="88" t="str"/>
-      <x:c r="F15" s="88" t="str"/>
-      <x:c r="G15" s="69" t="str">
+      <x:c r="A15" s="88" t="str"/>
+      <x:c r="B15" s="89" t="str"/>
+      <x:c r="C15" s="93" t="str"/>
+      <x:c r="D15" s="89" t="str"/>
+      <x:c r="E15" s="89" t="str"/>
+      <x:c r="F15" s="89" t="str"/>
+      <x:c r="G15" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
@@ -2584,11 +3748,11 @@
       <x:c r="A17" s="25" t="str">
         <x:v>Evidence status</x:v>
       </x:c>
-      <x:c r="B17" s="92" t="str">
+      <x:c r="B17" s="30" t="str">
         <x:f>IF(COUNTIF(G10:G15,"Reviewed")=6,"EVIDENCE COMPLETE","EVIDENCE INCOMPLETE")</x:f>
         <x:v>EVIDENCE INCOMPLETE</x:v>
       </x:c>
-      <x:c r="C17" s="92"/>
+      <x:c r="C17" s="30"/>
     </x:row>
     <x:row r="19" ht="23" customHeight="1">
       <x:c r="A19" s="11" t="str">
@@ -2603,24 +3767,24 @@
       <x:c r="H19" s="11"/>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
-      <x:c r="A20" s="32" t="str">
+      <x:c r="A20" s="37" t="str">
         <x:v>Write the exact motion presented to the committee. It must name the recommendation, scope, and any conditions.</x:v>
       </x:c>
-      <x:c r="B20" s="32"/>
-      <x:c r="C20" s="32"/>
-      <x:c r="D20" s="32"/>
-      <x:c r="E20" s="32"/>
-      <x:c r="F20" s="32"/>
-      <x:c r="G20" s="32"/>
+      <x:c r="B20" s="37"/>
+      <x:c r="C20" s="37"/>
+      <x:c r="D20" s="37"/>
+      <x:c r="E20" s="37"/>
+      <x:c r="F20" s="37"/>
+      <x:c r="G20" s="37"/>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
-      <x:c r="A21" s="76"/>
-      <x:c r="B21" s="77"/>
-      <x:c r="C21" s="77"/>
-      <x:c r="D21" s="77"/>
-      <x:c r="E21" s="77"/>
-      <x:c r="F21" s="77"/>
-      <x:c r="G21" s="78"/>
+      <x:c r="A21" s="63"/>
+      <x:c r="B21" s="110"/>
+      <x:c r="C21" s="110"/>
+      <x:c r="D21" s="110"/>
+      <x:c r="E21" s="110"/>
+      <x:c r="F21" s="110"/>
+      <x:c r="G21" s="64"/>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
       <x:c r="A23" s="11" t="str">
@@ -2658,48 +3822,48 @@
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="94" t="str">
-        <x:v>Chair &amp; Mandate</x:v>
-      </x:c>
-      <x:c r="B25" s="64" t="str"/>
-      <x:c r="C25" s="86" t="str"/>
-      <x:c r="D25" s="86" t="str"/>
-      <x:c r="E25" s="86" t="str"/>
-      <x:c r="F25" s="86" t="str"/>
-      <x:c r="G25" s="65" t="str"/>
+      <x:c r="A25" s="114" t="str">
+        <x:v>Client &amp; Macro</x:v>
+      </x:c>
+      <x:c r="B25" s="82" t="str"/>
+      <x:c r="C25" s="83" t="str"/>
+      <x:c r="D25" s="83" t="str"/>
+      <x:c r="E25" s="83" t="str"/>
+      <x:c r="F25" s="83" t="str"/>
+      <x:c r="G25" s="84" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="94" t="str">
-        <x:v>Markets Strategist</x:v>
-      </x:c>
-      <x:c r="B26" s="66" t="str"/>
-      <x:c r="C26" s="87" t="str"/>
-      <x:c r="D26" s="87" t="str"/>
-      <x:c r="E26" s="87" t="str"/>
-      <x:c r="F26" s="87" t="str"/>
-      <x:c r="G26" s="67" t="str"/>
+      <x:c r="A26" s="114" t="str">
+        <x:v>Fixed Income</x:v>
+      </x:c>
+      <x:c r="B26" s="85" t="str"/>
+      <x:c r="C26" s="86" t="str"/>
+      <x:c r="D26" s="86" t="str"/>
+      <x:c r="E26" s="86" t="str"/>
+      <x:c r="F26" s="86" t="str"/>
+      <x:c r="G26" s="87" t="str"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="94" t="str">
-        <x:v>Portfolio Lead</x:v>
-      </x:c>
-      <x:c r="B27" s="66" t="str"/>
-      <x:c r="C27" s="87" t="str"/>
-      <x:c r="D27" s="87" t="str"/>
-      <x:c r="E27" s="87" t="str"/>
-      <x:c r="F27" s="87" t="str"/>
-      <x:c r="G27" s="67" t="str"/>
+      <x:c r="A27" s="114" t="str">
+        <x:v>Fund &amp; ETF</x:v>
+      </x:c>
+      <x:c r="B27" s="85" t="str"/>
+      <x:c r="C27" s="86" t="str"/>
+      <x:c r="D27" s="86" t="str"/>
+      <x:c r="E27" s="86" t="str"/>
+      <x:c r="F27" s="86" t="str"/>
+      <x:c r="G27" s="87" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="94" t="str">
-        <x:v>Risk &amp; Challenge</x:v>
-      </x:c>
-      <x:c r="B28" s="68" t="str"/>
-      <x:c r="C28" s="88" t="str"/>
-      <x:c r="D28" s="88" t="str"/>
-      <x:c r="E28" s="88" t="str"/>
-      <x:c r="F28" s="88" t="str"/>
-      <x:c r="G28" s="69" t="str"/>
+      <x:c r="A28" s="114" t="str">
+        <x:v>Portfolio &amp; Risk</x:v>
+      </x:c>
+      <x:c r="B28" s="88" t="str"/>
+      <x:c r="C28" s="89" t="str"/>
+      <x:c r="D28" s="89" t="str"/>
+      <x:c r="E28" s="89" t="str"/>
+      <x:c r="F28" s="89" t="str"/>
+      <x:c r="G28" s="90" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="25" t="str">
@@ -2724,22 +3888,22 @@
       <x:c r="H32" s="11"/>
     </x:row>
     <x:row r="33" ht="34" customHeight="1">
-      <x:c r="A33" s="64"/>
-      <x:c r="B33" s="86"/>
-      <x:c r="C33" s="86"/>
-      <x:c r="D33" s="86"/>
-      <x:c r="E33" s="86"/>
-      <x:c r="F33" s="86"/>
-      <x:c r="G33" s="65"/>
+      <x:c r="A33" s="82"/>
+      <x:c r="B33" s="83"/>
+      <x:c r="C33" s="83"/>
+      <x:c r="D33" s="83"/>
+      <x:c r="E33" s="83"/>
+      <x:c r="F33" s="83"/>
+      <x:c r="G33" s="84"/>
     </x:row>
     <x:row r="34" ht="34" customHeight="1">
-      <x:c r="A34" s="68"/>
-      <x:c r="B34" s="88"/>
-      <x:c r="C34" s="88"/>
-      <x:c r="D34" s="88"/>
-      <x:c r="E34" s="88"/>
-      <x:c r="F34" s="88"/>
-      <x:c r="G34" s="69"/>
+      <x:c r="A34" s="88"/>
+      <x:c r="B34" s="89"/>
+      <x:c r="C34" s="89"/>
+      <x:c r="D34" s="89"/>
+      <x:c r="E34" s="89"/>
+      <x:c r="F34" s="89"/>
+      <x:c r="G34" s="90"/>
     </x:row>
     <x:row r="36" ht="23" customHeight="1">
       <x:c r="A36" s="11" t="str">
@@ -2777,70 +3941,70 @@
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="64" t="str"/>
-      <x:c r="B38" s="86" t="str"/>
-      <x:c r="C38" s="89" t="str"/>
-      <x:c r="D38" s="86" t="str"/>
-      <x:c r="E38" s="86" t="str">
+      <x:c r="A38" s="82" t="str"/>
+      <x:c r="B38" s="83" t="str"/>
+      <x:c r="C38" s="91" t="str"/>
+      <x:c r="D38" s="83" t="str"/>
+      <x:c r="E38" s="83" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F38" s="86" t="str"/>
-      <x:c r="G38" s="65" t="str"/>
+      <x:c r="F38" s="83" t="str"/>
+      <x:c r="G38" s="84" t="str"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="66" t="str"/>
-      <x:c r="B39" s="87" t="str"/>
-      <x:c r="C39" s="90" t="str"/>
-      <x:c r="D39" s="87" t="str"/>
-      <x:c r="E39" s="87" t="str">
+      <x:c r="A39" s="85" t="str"/>
+      <x:c r="B39" s="86" t="str"/>
+      <x:c r="C39" s="92" t="str"/>
+      <x:c r="D39" s="86" t="str"/>
+      <x:c r="E39" s="86" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F39" s="87" t="str"/>
-      <x:c r="G39" s="67" t="str"/>
+      <x:c r="F39" s="86" t="str"/>
+      <x:c r="G39" s="87" t="str"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="66" t="str"/>
-      <x:c r="B40" s="87" t="str"/>
-      <x:c r="C40" s="90" t="str"/>
-      <x:c r="D40" s="87" t="str"/>
-      <x:c r="E40" s="87" t="str">
+      <x:c r="A40" s="85" t="str"/>
+      <x:c r="B40" s="86" t="str"/>
+      <x:c r="C40" s="92" t="str"/>
+      <x:c r="D40" s="86" t="str"/>
+      <x:c r="E40" s="86" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F40" s="87" t="str"/>
-      <x:c r="G40" s="67" t="str"/>
+      <x:c r="F40" s="86" t="str"/>
+      <x:c r="G40" s="87" t="str"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="66" t="str"/>
-      <x:c r="B41" s="87" t="str"/>
-      <x:c r="C41" s="90" t="str"/>
-      <x:c r="D41" s="87" t="str"/>
-      <x:c r="E41" s="87" t="str">
+      <x:c r="A41" s="85" t="str"/>
+      <x:c r="B41" s="86" t="str"/>
+      <x:c r="C41" s="92" t="str"/>
+      <x:c r="D41" s="86" t="str"/>
+      <x:c r="E41" s="86" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F41" s="87" t="str"/>
-      <x:c r="G41" s="67" t="str"/>
+      <x:c r="F41" s="86" t="str"/>
+      <x:c r="G41" s="87" t="str"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="68" t="str"/>
-      <x:c r="B42" s="88" t="str"/>
-      <x:c r="C42" s="91" t="str"/>
-      <x:c r="D42" s="88" t="str"/>
-      <x:c r="E42" s="88" t="str">
+      <x:c r="A42" s="88" t="str"/>
+      <x:c r="B42" s="89" t="str"/>
+      <x:c r="C42" s="93" t="str"/>
+      <x:c r="D42" s="89" t="str"/>
+      <x:c r="E42" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F42" s="88" t="str"/>
-      <x:c r="G42" s="69" t="str"/>
+      <x:c r="F42" s="89" t="str"/>
+      <x:c r="G42" s="90" t="str"/>
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
-      <x:c r="A44" s="96" t="str">
+      <x:c r="A44" s="104" t="str">
         <x:v>Approval requires four Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
       </x:c>
-      <x:c r="B44" s="96"/>
-      <x:c r="C44" s="96"/>
-      <x:c r="D44" s="96"/>
-      <x:c r="E44" s="96"/>
-      <x:c r="F44" s="96"/>
-      <x:c r="G44" s="96"/>
+      <x:c r="B44" s="104"/>
+      <x:c r="C44" s="104"/>
+      <x:c r="D44" s="104"/>
+      <x:c r="E44" s="104"/>
+      <x:c r="F44" s="104"/>
+      <x:c r="G44" s="104"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2865,9 +4029,9 @@
     <x:mergeCell ref="A44:G44"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B30:C30">
-    <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="APPROVED"/>
-    <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="REVISION"/>
-    <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="INCOMPLETE"/>
+    <x:cfRule type="containsText" dxfId="37" priority="1" operator="containsText" text="APPROVED"/>
+    <x:cfRule type="containsText" dxfId="38" priority="2" operator="containsText" text="REVISION"/>
+    <x:cfRule type="containsText" dxfId="39" priority="3" operator="containsText" text="INCOMPLETE"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="G10:G15">
@@ -2926,26 +4090,26 @@
       <x:c r="A4" s="25" t="str">
         <x:v>Team / Committee Name</x:v>
       </x:c>
-      <x:c r="B4" s="64"/>
-      <x:c r="C4" s="65"/>
+      <x:c r="B4" s="82"/>
+      <x:c r="C4" s="84"/>
       <x:c r="D4" s="25" t="str">
         <x:v>Recorder</x:v>
       </x:c>
-      <x:c r="E4" s="76"/>
-      <x:c r="F4" s="77"/>
-      <x:c r="G4" s="78"/>
+      <x:c r="E4" s="63"/>
+      <x:c r="F4" s="110"/>
+      <x:c r="G4" s="64"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="25" t="str">
         <x:v>Client name / case</x:v>
       </x:c>
-      <x:c r="B5" s="66"/>
-      <x:c r="C5" s="67"/>
+      <x:c r="B5" s="85"/>
+      <x:c r="C5" s="87"/>
       <x:c r="D5" s="25" t="str">
         <x:v>Gate</x:v>
       </x:c>
       <x:c r="E5" s="14" t="str">
-        <x:v>Approve, revise, or reject Client 3 portfolio</x:v>
+        <x:v>Approve, revise, or reject Client 2 portfolio</x:v>
       </x:c>
       <x:c r="F5" s="14"/>
       <x:c r="G5" s="14"/>
@@ -2954,14 +4118,14 @@
       <x:c r="A6" s="25" t="str">
         <x:v>Meeting Date</x:v>
       </x:c>
-      <x:c r="B6" s="79"/>
-      <x:c r="C6" s="80"/>
+      <x:c r="B6" s="111"/>
+      <x:c r="C6" s="112"/>
       <x:c r="D6" s="25" t="str">
         <x:v>Meeting Chair</x:v>
       </x:c>
-      <x:c r="E6" s="76"/>
-      <x:c r="F6" s="77"/>
-      <x:c r="G6" s="78"/>
+      <x:c r="E6" s="63"/>
+      <x:c r="F6" s="110"/>
+      <x:c r="G6" s="64"/>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
       <x:c r="A8" s="11" t="str">
@@ -2999,68 +4163,68 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="64" t="str"/>
-      <x:c r="B10" s="86" t="str"/>
-      <x:c r="C10" s="89" t="str"/>
-      <x:c r="D10" s="86" t="str"/>
-      <x:c r="E10" s="86" t="str"/>
-      <x:c r="F10" s="86" t="str"/>
-      <x:c r="G10" s="65" t="str">
+      <x:c r="A10" s="82" t="str"/>
+      <x:c r="B10" s="83" t="str"/>
+      <x:c r="C10" s="91" t="str"/>
+      <x:c r="D10" s="83" t="str"/>
+      <x:c r="E10" s="83" t="str"/>
+      <x:c r="F10" s="83" t="str"/>
+      <x:c r="G10" s="84" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="66" t="str"/>
-      <x:c r="B11" s="87" t="str"/>
-      <x:c r="C11" s="90" t="str"/>
-      <x:c r="D11" s="87" t="str"/>
-      <x:c r="E11" s="87" t="str"/>
-      <x:c r="F11" s="87" t="str"/>
-      <x:c r="G11" s="67" t="str">
+      <x:c r="A11" s="85" t="str"/>
+      <x:c r="B11" s="86" t="str"/>
+      <x:c r="C11" s="92" t="str"/>
+      <x:c r="D11" s="86" t="str"/>
+      <x:c r="E11" s="86" t="str"/>
+      <x:c r="F11" s="86" t="str"/>
+      <x:c r="G11" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="66" t="str"/>
-      <x:c r="B12" s="87" t="str"/>
-      <x:c r="C12" s="90" t="str"/>
-      <x:c r="D12" s="87" t="str"/>
-      <x:c r="E12" s="87" t="str"/>
-      <x:c r="F12" s="87" t="str"/>
-      <x:c r="G12" s="67" t="str">
+      <x:c r="A12" s="85" t="str"/>
+      <x:c r="B12" s="86" t="str"/>
+      <x:c r="C12" s="92" t="str"/>
+      <x:c r="D12" s="86" t="str"/>
+      <x:c r="E12" s="86" t="str"/>
+      <x:c r="F12" s="86" t="str"/>
+      <x:c r="G12" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="66" t="str"/>
-      <x:c r="B13" s="87" t="str"/>
-      <x:c r="C13" s="90" t="str"/>
-      <x:c r="D13" s="87" t="str"/>
-      <x:c r="E13" s="87" t="str"/>
-      <x:c r="F13" s="87" t="str"/>
-      <x:c r="G13" s="67" t="str">
+      <x:c r="A13" s="85" t="str"/>
+      <x:c r="B13" s="86" t="str"/>
+      <x:c r="C13" s="92" t="str"/>
+      <x:c r="D13" s="86" t="str"/>
+      <x:c r="E13" s="86" t="str"/>
+      <x:c r="F13" s="86" t="str"/>
+      <x:c r="G13" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="66" t="str"/>
-      <x:c r="B14" s="87" t="str"/>
-      <x:c r="C14" s="90" t="str"/>
-      <x:c r="D14" s="87" t="str"/>
-      <x:c r="E14" s="87" t="str"/>
-      <x:c r="F14" s="87" t="str"/>
-      <x:c r="G14" s="67" t="str">
+      <x:c r="A14" s="85" t="str"/>
+      <x:c r="B14" s="86" t="str"/>
+      <x:c r="C14" s="92" t="str"/>
+      <x:c r="D14" s="86" t="str"/>
+      <x:c r="E14" s="86" t="str"/>
+      <x:c r="F14" s="86" t="str"/>
+      <x:c r="G14" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="68" t="str"/>
-      <x:c r="B15" s="88" t="str"/>
-      <x:c r="C15" s="91" t="str"/>
-      <x:c r="D15" s="88" t="str"/>
-      <x:c r="E15" s="88" t="str"/>
-      <x:c r="F15" s="88" t="str"/>
-      <x:c r="G15" s="69" t="str">
+      <x:c r="A15" s="88" t="str"/>
+      <x:c r="B15" s="89" t="str"/>
+      <x:c r="C15" s="93" t="str"/>
+      <x:c r="D15" s="89" t="str"/>
+      <x:c r="E15" s="89" t="str"/>
+      <x:c r="F15" s="89" t="str"/>
+      <x:c r="G15" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
@@ -3068,11 +4232,11 @@
       <x:c r="A17" s="25" t="str">
         <x:v>Evidence status</x:v>
       </x:c>
-      <x:c r="B17" s="92" t="str">
+      <x:c r="B17" s="30" t="str">
         <x:f>IF(COUNTIF(G10:G15,"Reviewed")=6,"EVIDENCE COMPLETE","EVIDENCE INCOMPLETE")</x:f>
         <x:v>EVIDENCE INCOMPLETE</x:v>
       </x:c>
-      <x:c r="C17" s="92"/>
+      <x:c r="C17" s="30"/>
     </x:row>
     <x:row r="19" ht="23" customHeight="1">
       <x:c r="A19" s="11" t="str">
@@ -3087,24 +4251,24 @@
       <x:c r="H19" s="11"/>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
-      <x:c r="A20" s="32" t="str">
+      <x:c r="A20" s="37" t="str">
         <x:v>Write the exact motion presented to the committee. It must name the recommendation, scope, and any conditions.</x:v>
       </x:c>
-      <x:c r="B20" s="32"/>
-      <x:c r="C20" s="32"/>
-      <x:c r="D20" s="32"/>
-      <x:c r="E20" s="32"/>
-      <x:c r="F20" s="32"/>
-      <x:c r="G20" s="32"/>
+      <x:c r="B20" s="37"/>
+      <x:c r="C20" s="37"/>
+      <x:c r="D20" s="37"/>
+      <x:c r="E20" s="37"/>
+      <x:c r="F20" s="37"/>
+      <x:c r="G20" s="37"/>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
-      <x:c r="A21" s="76"/>
-      <x:c r="B21" s="77"/>
-      <x:c r="C21" s="77"/>
-      <x:c r="D21" s="77"/>
-      <x:c r="E21" s="77"/>
-      <x:c r="F21" s="77"/>
-      <x:c r="G21" s="78"/>
+      <x:c r="A21" s="63"/>
+      <x:c r="B21" s="110"/>
+      <x:c r="C21" s="110"/>
+      <x:c r="D21" s="110"/>
+      <x:c r="E21" s="110"/>
+      <x:c r="F21" s="110"/>
+      <x:c r="G21" s="64"/>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
       <x:c r="A23" s="11" t="str">
@@ -3142,48 +4306,48 @@
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="94" t="str">
-        <x:v>Chair &amp; Mandate</x:v>
-      </x:c>
-      <x:c r="B25" s="64" t="str"/>
-      <x:c r="C25" s="86" t="str"/>
-      <x:c r="D25" s="86" t="str"/>
-      <x:c r="E25" s="86" t="str"/>
-      <x:c r="F25" s="86" t="str"/>
-      <x:c r="G25" s="65" t="str"/>
+      <x:c r="A25" s="114" t="str">
+        <x:v>Client &amp; Macro</x:v>
+      </x:c>
+      <x:c r="B25" s="82" t="str"/>
+      <x:c r="C25" s="83" t="str"/>
+      <x:c r="D25" s="83" t="str"/>
+      <x:c r="E25" s="83" t="str"/>
+      <x:c r="F25" s="83" t="str"/>
+      <x:c r="G25" s="84" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="94" t="str">
-        <x:v>Markets Strategist</x:v>
-      </x:c>
-      <x:c r="B26" s="66" t="str"/>
-      <x:c r="C26" s="87" t="str"/>
-      <x:c r="D26" s="87" t="str"/>
-      <x:c r="E26" s="87" t="str"/>
-      <x:c r="F26" s="87" t="str"/>
-      <x:c r="G26" s="67" t="str"/>
+      <x:c r="A26" s="114" t="str">
+        <x:v>Fixed Income</x:v>
+      </x:c>
+      <x:c r="B26" s="85" t="str"/>
+      <x:c r="C26" s="86" t="str"/>
+      <x:c r="D26" s="86" t="str"/>
+      <x:c r="E26" s="86" t="str"/>
+      <x:c r="F26" s="86" t="str"/>
+      <x:c r="G26" s="87" t="str"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="94" t="str">
-        <x:v>Portfolio Lead</x:v>
-      </x:c>
-      <x:c r="B27" s="66" t="str"/>
-      <x:c r="C27" s="87" t="str"/>
-      <x:c r="D27" s="87" t="str"/>
-      <x:c r="E27" s="87" t="str"/>
-      <x:c r="F27" s="87" t="str"/>
-      <x:c r="G27" s="67" t="str"/>
+      <x:c r="A27" s="114" t="str">
+        <x:v>Fund &amp; ETF</x:v>
+      </x:c>
+      <x:c r="B27" s="85" t="str"/>
+      <x:c r="C27" s="86" t="str"/>
+      <x:c r="D27" s="86" t="str"/>
+      <x:c r="E27" s="86" t="str"/>
+      <x:c r="F27" s="86" t="str"/>
+      <x:c r="G27" s="87" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="94" t="str">
-        <x:v>Risk &amp; Challenge</x:v>
-      </x:c>
-      <x:c r="B28" s="68" t="str"/>
-      <x:c r="C28" s="88" t="str"/>
-      <x:c r="D28" s="88" t="str"/>
-      <x:c r="E28" s="88" t="str"/>
-      <x:c r="F28" s="88" t="str"/>
-      <x:c r="G28" s="69" t="str"/>
+      <x:c r="A28" s="114" t="str">
+        <x:v>Portfolio &amp; Risk</x:v>
+      </x:c>
+      <x:c r="B28" s="88" t="str"/>
+      <x:c r="C28" s="89" t="str"/>
+      <x:c r="D28" s="89" t="str"/>
+      <x:c r="E28" s="89" t="str"/>
+      <x:c r="F28" s="89" t="str"/>
+      <x:c r="G28" s="90" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="25" t="str">
@@ -3208,22 +4372,22 @@
       <x:c r="H32" s="11"/>
     </x:row>
     <x:row r="33" ht="34" customHeight="1">
-      <x:c r="A33" s="64"/>
-      <x:c r="B33" s="86"/>
-      <x:c r="C33" s="86"/>
-      <x:c r="D33" s="86"/>
-      <x:c r="E33" s="86"/>
-      <x:c r="F33" s="86"/>
-      <x:c r="G33" s="65"/>
+      <x:c r="A33" s="82"/>
+      <x:c r="B33" s="83"/>
+      <x:c r="C33" s="83"/>
+      <x:c r="D33" s="83"/>
+      <x:c r="E33" s="83"/>
+      <x:c r="F33" s="83"/>
+      <x:c r="G33" s="84"/>
     </x:row>
     <x:row r="34" ht="34" customHeight="1">
-      <x:c r="A34" s="68"/>
-      <x:c r="B34" s="88"/>
-      <x:c r="C34" s="88"/>
-      <x:c r="D34" s="88"/>
-      <x:c r="E34" s="88"/>
-      <x:c r="F34" s="88"/>
-      <x:c r="G34" s="69"/>
+      <x:c r="A34" s="88"/>
+      <x:c r="B34" s="89"/>
+      <x:c r="C34" s="89"/>
+      <x:c r="D34" s="89"/>
+      <x:c r="E34" s="89"/>
+      <x:c r="F34" s="89"/>
+      <x:c r="G34" s="90"/>
     </x:row>
     <x:row r="36" ht="23" customHeight="1">
       <x:c r="A36" s="11" t="str">
@@ -3261,70 +4425,70 @@
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="64" t="str"/>
-      <x:c r="B38" s="86" t="str"/>
-      <x:c r="C38" s="89" t="str"/>
-      <x:c r="D38" s="86" t="str"/>
-      <x:c r="E38" s="86" t="str">
+      <x:c r="A38" s="82" t="str"/>
+      <x:c r="B38" s="83" t="str"/>
+      <x:c r="C38" s="91" t="str"/>
+      <x:c r="D38" s="83" t="str"/>
+      <x:c r="E38" s="83" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F38" s="86" t="str"/>
-      <x:c r="G38" s="65" t="str"/>
+      <x:c r="F38" s="83" t="str"/>
+      <x:c r="G38" s="84" t="str"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="66" t="str"/>
-      <x:c r="B39" s="87" t="str"/>
-      <x:c r="C39" s="90" t="str"/>
-      <x:c r="D39" s="87" t="str"/>
-      <x:c r="E39" s="87" t="str">
+      <x:c r="A39" s="85" t="str"/>
+      <x:c r="B39" s="86" t="str"/>
+      <x:c r="C39" s="92" t="str"/>
+      <x:c r="D39" s="86" t="str"/>
+      <x:c r="E39" s="86" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F39" s="87" t="str"/>
-      <x:c r="G39" s="67" t="str"/>
+      <x:c r="F39" s="86" t="str"/>
+      <x:c r="G39" s="87" t="str"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="66" t="str"/>
-      <x:c r="B40" s="87" t="str"/>
-      <x:c r="C40" s="90" t="str"/>
-      <x:c r="D40" s="87" t="str"/>
-      <x:c r="E40" s="87" t="str">
+      <x:c r="A40" s="85" t="str"/>
+      <x:c r="B40" s="86" t="str"/>
+      <x:c r="C40" s="92" t="str"/>
+      <x:c r="D40" s="86" t="str"/>
+      <x:c r="E40" s="86" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F40" s="87" t="str"/>
-      <x:c r="G40" s="67" t="str"/>
+      <x:c r="F40" s="86" t="str"/>
+      <x:c r="G40" s="87" t="str"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="66" t="str"/>
-      <x:c r="B41" s="87" t="str"/>
-      <x:c r="C41" s="90" t="str"/>
-      <x:c r="D41" s="87" t="str"/>
-      <x:c r="E41" s="87" t="str">
+      <x:c r="A41" s="85" t="str"/>
+      <x:c r="B41" s="86" t="str"/>
+      <x:c r="C41" s="92" t="str"/>
+      <x:c r="D41" s="86" t="str"/>
+      <x:c r="E41" s="86" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F41" s="87" t="str"/>
-      <x:c r="G41" s="67" t="str"/>
+      <x:c r="F41" s="86" t="str"/>
+      <x:c r="G41" s="87" t="str"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="68" t="str"/>
-      <x:c r="B42" s="88" t="str"/>
-      <x:c r="C42" s="91" t="str"/>
-      <x:c r="D42" s="88" t="str"/>
-      <x:c r="E42" s="88" t="str">
+      <x:c r="A42" s="88" t="str"/>
+      <x:c r="B42" s="89" t="str"/>
+      <x:c r="C42" s="93" t="str"/>
+      <x:c r="D42" s="89" t="str"/>
+      <x:c r="E42" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F42" s="88" t="str"/>
-      <x:c r="G42" s="69" t="str"/>
+      <x:c r="F42" s="89" t="str"/>
+      <x:c r="G42" s="90" t="str"/>
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
-      <x:c r="A44" s="96" t="str">
+      <x:c r="A44" s="104" t="str">
         <x:v>Approval requires four Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
       </x:c>
-      <x:c r="B44" s="96"/>
-      <x:c r="C44" s="96"/>
-      <x:c r="D44" s="96"/>
-      <x:c r="E44" s="96"/>
-      <x:c r="F44" s="96"/>
-      <x:c r="G44" s="96"/>
+      <x:c r="B44" s="104"/>
+      <x:c r="C44" s="104"/>
+      <x:c r="D44" s="104"/>
+      <x:c r="E44" s="104"/>
+      <x:c r="F44" s="104"/>
+      <x:c r="G44" s="104"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3349,9 +4513,9 @@
     <x:mergeCell ref="A44:G44"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B30:C30">
-    <x:cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="APPROVED"/>
-    <x:cfRule type="containsText" dxfId="16" priority="2" operator="containsText" text="REVISION"/>
-    <x:cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="INCOMPLETE"/>
+    <x:cfRule type="containsText" dxfId="40" priority="1" operator="containsText" text="APPROVED"/>
+    <x:cfRule type="containsText" dxfId="41" priority="2" operator="containsText" text="REVISION"/>
+    <x:cfRule type="containsText" dxfId="42" priority="3" operator="containsText" text="INCOMPLETE"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="G10:G15">
@@ -3384,7 +4548,7 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>BUS331 Investment Committee — Phase 3 Decision Record</x:v>
+        <x:v>BUS331 Investment Committee — Phase 2 Decision Record</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -3396,7 +4560,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Defend the Recommendation | All four committee members review, vote, and sign this record.</x:v>
+        <x:v>Build &amp; Challenge | All four committee members review, vote, and sign this record.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -3410,26 +4574,26 @@
       <x:c r="A4" s="25" t="str">
         <x:v>Team / Committee Name</x:v>
       </x:c>
-      <x:c r="B4" s="64"/>
-      <x:c r="C4" s="65"/>
+      <x:c r="B4" s="82"/>
+      <x:c r="C4" s="84"/>
       <x:c r="D4" s="25" t="str">
         <x:v>Recorder</x:v>
       </x:c>
-      <x:c r="E4" s="76"/>
-      <x:c r="F4" s="77"/>
-      <x:c r="G4" s="78"/>
+      <x:c r="E4" s="63"/>
+      <x:c r="F4" s="110"/>
+      <x:c r="G4" s="64"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="25" t="str">
-        <x:v>Scope: integrated recommendation</x:v>
-      </x:c>
-      <x:c r="B5" s="66"/>
-      <x:c r="C5" s="67"/>
+        <x:v>Client name / case</x:v>
+      </x:c>
+      <x:c r="B5" s="85"/>
+      <x:c r="C5" s="87"/>
       <x:c r="D5" s="25" t="str">
         <x:v>Gate</x:v>
       </x:c>
       <x:c r="E5" s="14" t="str">
-        <x:v>Issue final recommendation and implementation plan</x:v>
+        <x:v>Approve, revise, or reject Client 3 portfolio</x:v>
       </x:c>
       <x:c r="F5" s="14"/>
       <x:c r="G5" s="14"/>
@@ -3438,14 +4602,14 @@
       <x:c r="A6" s="25" t="str">
         <x:v>Meeting Date</x:v>
       </x:c>
-      <x:c r="B6" s="79"/>
-      <x:c r="C6" s="80"/>
+      <x:c r="B6" s="111"/>
+      <x:c r="C6" s="112"/>
       <x:c r="D6" s="25" t="str">
         <x:v>Meeting Chair</x:v>
       </x:c>
-      <x:c r="E6" s="76"/>
-      <x:c r="F6" s="77"/>
-      <x:c r="G6" s="78"/>
+      <x:c r="E6" s="63"/>
+      <x:c r="F6" s="110"/>
+      <x:c r="G6" s="64"/>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
       <x:c r="A8" s="11" t="str">
@@ -3483,68 +4647,68 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="64" t="str"/>
-      <x:c r="B10" s="86" t="str"/>
-      <x:c r="C10" s="89" t="str"/>
-      <x:c r="D10" s="86" t="str"/>
-      <x:c r="E10" s="86" t="str"/>
-      <x:c r="F10" s="86" t="str"/>
-      <x:c r="G10" s="65" t="str">
+      <x:c r="A10" s="82" t="str"/>
+      <x:c r="B10" s="83" t="str"/>
+      <x:c r="C10" s="91" t="str"/>
+      <x:c r="D10" s="83" t="str"/>
+      <x:c r="E10" s="83" t="str"/>
+      <x:c r="F10" s="83" t="str"/>
+      <x:c r="G10" s="84" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="66" t="str"/>
-      <x:c r="B11" s="87" t="str"/>
-      <x:c r="C11" s="90" t="str"/>
-      <x:c r="D11" s="87" t="str"/>
-      <x:c r="E11" s="87" t="str"/>
-      <x:c r="F11" s="87" t="str"/>
-      <x:c r="G11" s="67" t="str">
+      <x:c r="A11" s="85" t="str"/>
+      <x:c r="B11" s="86" t="str"/>
+      <x:c r="C11" s="92" t="str"/>
+      <x:c r="D11" s="86" t="str"/>
+      <x:c r="E11" s="86" t="str"/>
+      <x:c r="F11" s="86" t="str"/>
+      <x:c r="G11" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="66" t="str"/>
-      <x:c r="B12" s="87" t="str"/>
-      <x:c r="C12" s="90" t="str"/>
-      <x:c r="D12" s="87" t="str"/>
-      <x:c r="E12" s="87" t="str"/>
-      <x:c r="F12" s="87" t="str"/>
-      <x:c r="G12" s="67" t="str">
+      <x:c r="A12" s="85" t="str"/>
+      <x:c r="B12" s="86" t="str"/>
+      <x:c r="C12" s="92" t="str"/>
+      <x:c r="D12" s="86" t="str"/>
+      <x:c r="E12" s="86" t="str"/>
+      <x:c r="F12" s="86" t="str"/>
+      <x:c r="G12" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="66" t="str"/>
-      <x:c r="B13" s="87" t="str"/>
-      <x:c r="C13" s="90" t="str"/>
-      <x:c r="D13" s="87" t="str"/>
-      <x:c r="E13" s="87" t="str"/>
-      <x:c r="F13" s="87" t="str"/>
-      <x:c r="G13" s="67" t="str">
+      <x:c r="A13" s="85" t="str"/>
+      <x:c r="B13" s="86" t="str"/>
+      <x:c r="C13" s="92" t="str"/>
+      <x:c r="D13" s="86" t="str"/>
+      <x:c r="E13" s="86" t="str"/>
+      <x:c r="F13" s="86" t="str"/>
+      <x:c r="G13" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="66" t="str"/>
-      <x:c r="B14" s="87" t="str"/>
-      <x:c r="C14" s="90" t="str"/>
-      <x:c r="D14" s="87" t="str"/>
-      <x:c r="E14" s="87" t="str"/>
-      <x:c r="F14" s="87" t="str"/>
-      <x:c r="G14" s="67" t="str">
+      <x:c r="A14" s="85" t="str"/>
+      <x:c r="B14" s="86" t="str"/>
+      <x:c r="C14" s="92" t="str"/>
+      <x:c r="D14" s="86" t="str"/>
+      <x:c r="E14" s="86" t="str"/>
+      <x:c r="F14" s="86" t="str"/>
+      <x:c r="G14" s="87" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="68" t="str"/>
-      <x:c r="B15" s="88" t="str"/>
-      <x:c r="C15" s="91" t="str"/>
-      <x:c r="D15" s="88" t="str"/>
-      <x:c r="E15" s="88" t="str"/>
-      <x:c r="F15" s="88" t="str"/>
-      <x:c r="G15" s="69" t="str">
+      <x:c r="A15" s="88" t="str"/>
+      <x:c r="B15" s="89" t="str"/>
+      <x:c r="C15" s="93" t="str"/>
+      <x:c r="D15" s="89" t="str"/>
+      <x:c r="E15" s="89" t="str"/>
+      <x:c r="F15" s="89" t="str"/>
+      <x:c r="G15" s="90" t="str">
         <x:v>Not reviewed</x:v>
       </x:c>
     </x:row>
@@ -3552,11 +4716,11 @@
       <x:c r="A17" s="25" t="str">
         <x:v>Evidence status</x:v>
       </x:c>
-      <x:c r="B17" s="92" t="str">
+      <x:c r="B17" s="30" t="str">
         <x:f>IF(COUNTIF(G10:G15,"Reviewed")=6,"EVIDENCE COMPLETE","EVIDENCE INCOMPLETE")</x:f>
         <x:v>EVIDENCE INCOMPLETE</x:v>
       </x:c>
-      <x:c r="C17" s="92"/>
+      <x:c r="C17" s="30"/>
     </x:row>
     <x:row r="19" ht="23" customHeight="1">
       <x:c r="A19" s="11" t="str">
@@ -3571,24 +4735,24 @@
       <x:c r="H19" s="11"/>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
-      <x:c r="A20" s="32" t="str">
+      <x:c r="A20" s="37" t="str">
         <x:v>Write the exact motion presented to the committee. It must name the recommendation, scope, and any conditions.</x:v>
       </x:c>
-      <x:c r="B20" s="32"/>
-      <x:c r="C20" s="32"/>
-      <x:c r="D20" s="32"/>
-      <x:c r="E20" s="32"/>
-      <x:c r="F20" s="32"/>
-      <x:c r="G20" s="32"/>
+      <x:c r="B20" s="37"/>
+      <x:c r="C20" s="37"/>
+      <x:c r="D20" s="37"/>
+      <x:c r="E20" s="37"/>
+      <x:c r="F20" s="37"/>
+      <x:c r="G20" s="37"/>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
-      <x:c r="A21" s="76"/>
-      <x:c r="B21" s="77"/>
-      <x:c r="C21" s="77"/>
-      <x:c r="D21" s="77"/>
-      <x:c r="E21" s="77"/>
-      <x:c r="F21" s="77"/>
-      <x:c r="G21" s="78"/>
+      <x:c r="A21" s="63"/>
+      <x:c r="B21" s="110"/>
+      <x:c r="C21" s="110"/>
+      <x:c r="D21" s="110"/>
+      <x:c r="E21" s="110"/>
+      <x:c r="F21" s="110"/>
+      <x:c r="G21" s="64"/>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
       <x:c r="A23" s="11" t="str">
@@ -3626,48 +4790,48 @@
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="94" t="str">
-        <x:v>Chair &amp; Mandate</x:v>
-      </x:c>
-      <x:c r="B25" s="64" t="str"/>
-      <x:c r="C25" s="86" t="str"/>
-      <x:c r="D25" s="86" t="str"/>
-      <x:c r="E25" s="86" t="str"/>
-      <x:c r="F25" s="86" t="str"/>
-      <x:c r="G25" s="65" t="str"/>
+      <x:c r="A25" s="114" t="str">
+        <x:v>Client &amp; Macro</x:v>
+      </x:c>
+      <x:c r="B25" s="82" t="str"/>
+      <x:c r="C25" s="83" t="str"/>
+      <x:c r="D25" s="83" t="str"/>
+      <x:c r="E25" s="83" t="str"/>
+      <x:c r="F25" s="83" t="str"/>
+      <x:c r="G25" s="84" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="94" t="str">
-        <x:v>Markets Strategist</x:v>
-      </x:c>
-      <x:c r="B26" s="66" t="str"/>
-      <x:c r="C26" s="87" t="str"/>
-      <x:c r="D26" s="87" t="str"/>
-      <x:c r="E26" s="87" t="str"/>
-      <x:c r="F26" s="87" t="str"/>
-      <x:c r="G26" s="67" t="str"/>
+      <x:c r="A26" s="114" t="str">
+        <x:v>Fixed Income</x:v>
+      </x:c>
+      <x:c r="B26" s="85" t="str"/>
+      <x:c r="C26" s="86" t="str"/>
+      <x:c r="D26" s="86" t="str"/>
+      <x:c r="E26" s="86" t="str"/>
+      <x:c r="F26" s="86" t="str"/>
+      <x:c r="G26" s="87" t="str"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="94" t="str">
-        <x:v>Portfolio Lead</x:v>
-      </x:c>
-      <x:c r="B27" s="66" t="str"/>
-      <x:c r="C27" s="87" t="str"/>
-      <x:c r="D27" s="87" t="str"/>
-      <x:c r="E27" s="87" t="str"/>
-      <x:c r="F27" s="87" t="str"/>
-      <x:c r="G27" s="67" t="str"/>
+      <x:c r="A27" s="114" t="str">
+        <x:v>Fund &amp; ETF</x:v>
+      </x:c>
+      <x:c r="B27" s="85" t="str"/>
+      <x:c r="C27" s="86" t="str"/>
+      <x:c r="D27" s="86" t="str"/>
+      <x:c r="E27" s="86" t="str"/>
+      <x:c r="F27" s="86" t="str"/>
+      <x:c r="G27" s="87" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="94" t="str">
-        <x:v>Risk &amp; Challenge</x:v>
-      </x:c>
-      <x:c r="B28" s="68" t="str"/>
-      <x:c r="C28" s="88" t="str"/>
-      <x:c r="D28" s="88" t="str"/>
-      <x:c r="E28" s="88" t="str"/>
-      <x:c r="F28" s="88" t="str"/>
-      <x:c r="G28" s="69" t="str"/>
+      <x:c r="A28" s="114" t="str">
+        <x:v>Portfolio &amp; Risk</x:v>
+      </x:c>
+      <x:c r="B28" s="88" t="str"/>
+      <x:c r="C28" s="89" t="str"/>
+      <x:c r="D28" s="89" t="str"/>
+      <x:c r="E28" s="89" t="str"/>
+      <x:c r="F28" s="89" t="str"/>
+      <x:c r="G28" s="90" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="25" t="str">
@@ -3692,22 +4856,22 @@
       <x:c r="H32" s="11"/>
     </x:row>
     <x:row r="33" ht="34" customHeight="1">
-      <x:c r="A33" s="64"/>
-      <x:c r="B33" s="86"/>
-      <x:c r="C33" s="86"/>
-      <x:c r="D33" s="86"/>
-      <x:c r="E33" s="86"/>
-      <x:c r="F33" s="86"/>
-      <x:c r="G33" s="65"/>
+      <x:c r="A33" s="82"/>
+      <x:c r="B33" s="83"/>
+      <x:c r="C33" s="83"/>
+      <x:c r="D33" s="83"/>
+      <x:c r="E33" s="83"/>
+      <x:c r="F33" s="83"/>
+      <x:c r="G33" s="84"/>
     </x:row>
     <x:row r="34" ht="34" customHeight="1">
-      <x:c r="A34" s="68"/>
-      <x:c r="B34" s="88"/>
-      <x:c r="C34" s="88"/>
-      <x:c r="D34" s="88"/>
-      <x:c r="E34" s="88"/>
-      <x:c r="F34" s="88"/>
-      <x:c r="G34" s="69"/>
+      <x:c r="A34" s="88"/>
+      <x:c r="B34" s="89"/>
+      <x:c r="C34" s="89"/>
+      <x:c r="D34" s="89"/>
+      <x:c r="E34" s="89"/>
+      <x:c r="F34" s="89"/>
+      <x:c r="G34" s="90"/>
     </x:row>
     <x:row r="36" ht="23" customHeight="1">
       <x:c r="A36" s="11" t="str">
@@ -3745,70 +4909,70 @@
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="64" t="str"/>
-      <x:c r="B38" s="86" t="str"/>
-      <x:c r="C38" s="89" t="str"/>
-      <x:c r="D38" s="86" t="str"/>
-      <x:c r="E38" s="86" t="str">
+      <x:c r="A38" s="82" t="str"/>
+      <x:c r="B38" s="83" t="str"/>
+      <x:c r="C38" s="91" t="str"/>
+      <x:c r="D38" s="83" t="str"/>
+      <x:c r="E38" s="83" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F38" s="86" t="str"/>
-      <x:c r="G38" s="65" t="str"/>
+      <x:c r="F38" s="83" t="str"/>
+      <x:c r="G38" s="84" t="str"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="66" t="str"/>
-      <x:c r="B39" s="87" t="str"/>
-      <x:c r="C39" s="90" t="str"/>
-      <x:c r="D39" s="87" t="str"/>
-      <x:c r="E39" s="87" t="str">
+      <x:c r="A39" s="85" t="str"/>
+      <x:c r="B39" s="86" t="str"/>
+      <x:c r="C39" s="92" t="str"/>
+      <x:c r="D39" s="86" t="str"/>
+      <x:c r="E39" s="86" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F39" s="87" t="str"/>
-      <x:c r="G39" s="67" t="str"/>
+      <x:c r="F39" s="86" t="str"/>
+      <x:c r="G39" s="87" t="str"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="66" t="str"/>
-      <x:c r="B40" s="87" t="str"/>
-      <x:c r="C40" s="90" t="str"/>
-      <x:c r="D40" s="87" t="str"/>
-      <x:c r="E40" s="87" t="str">
+      <x:c r="A40" s="85" t="str"/>
+      <x:c r="B40" s="86" t="str"/>
+      <x:c r="C40" s="92" t="str"/>
+      <x:c r="D40" s="86" t="str"/>
+      <x:c r="E40" s="86" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F40" s="87" t="str"/>
-      <x:c r="G40" s="67" t="str"/>
+      <x:c r="F40" s="86" t="str"/>
+      <x:c r="G40" s="87" t="str"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="66" t="str"/>
-      <x:c r="B41" s="87" t="str"/>
-      <x:c r="C41" s="90" t="str"/>
-      <x:c r="D41" s="87" t="str"/>
-      <x:c r="E41" s="87" t="str">
+      <x:c r="A41" s="85" t="str"/>
+      <x:c r="B41" s="86" t="str"/>
+      <x:c r="C41" s="92" t="str"/>
+      <x:c r="D41" s="86" t="str"/>
+      <x:c r="E41" s="86" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F41" s="87" t="str"/>
-      <x:c r="G41" s="67" t="str"/>
+      <x:c r="F41" s="86" t="str"/>
+      <x:c r="G41" s="87" t="str"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="68" t="str"/>
-      <x:c r="B42" s="88" t="str"/>
-      <x:c r="C42" s="91" t="str"/>
-      <x:c r="D42" s="88" t="str"/>
-      <x:c r="E42" s="88" t="str">
+      <x:c r="A42" s="88" t="str"/>
+      <x:c r="B42" s="89" t="str"/>
+      <x:c r="C42" s="93" t="str"/>
+      <x:c r="D42" s="89" t="str"/>
+      <x:c r="E42" s="89" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="F42" s="88" t="str"/>
-      <x:c r="G42" s="69" t="str"/>
+      <x:c r="F42" s="89" t="str"/>
+      <x:c r="G42" s="90" t="str"/>
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
-      <x:c r="A44" s="96" t="str">
+      <x:c r="A44" s="104" t="str">
         <x:v>Approval requires four Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
       </x:c>
-      <x:c r="B44" s="96"/>
-      <x:c r="C44" s="96"/>
-      <x:c r="D44" s="96"/>
-      <x:c r="E44" s="96"/>
-      <x:c r="F44" s="96"/>
-      <x:c r="G44" s="96"/>
+      <x:c r="B44" s="104"/>
+      <x:c r="C44" s="104"/>
+      <x:c r="D44" s="104"/>
+      <x:c r="E44" s="104"/>
+      <x:c r="F44" s="104"/>
+      <x:c r="G44" s="104"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3833,9 +4997,9 @@
     <x:mergeCell ref="A44:G44"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B30:C30">
-    <x:cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="APPROVED"/>
-    <x:cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="REVISION"/>
-    <x:cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="INCOMPLETE"/>
+    <x:cfRule type="containsText" dxfId="43" priority="1" operator="containsText" text="APPROVED"/>
+    <x:cfRule type="containsText" dxfId="44" priority="2" operator="containsText" text="REVISION"/>
+    <x:cfRule type="containsText" dxfId="45" priority="3" operator="containsText" text="INCOMPLETE"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="G10:G15">
@@ -3856,6 +5020,490 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="4" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>BUS331 Investment Committee — Phase 3 Decision Record</x:v>
+      </x:c>
+      <x:c r="B1" s="3"/>
+      <x:c r="C1" s="3"/>
+      <x:c r="D1" s="3"/>
+      <x:c r="E1" s="3"/>
+      <x:c r="F1" s="3"/>
+      <x:c r="G1" s="3"/>
+      <x:c r="H1" s="3"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>Defend the Recommendation | All four committee members review, vote, and sign this record.</x:v>
+      </x:c>
+      <x:c r="B2" s="6"/>
+      <x:c r="C2" s="6"/>
+      <x:c r="D2" s="6"/>
+      <x:c r="E2" s="6"/>
+      <x:c r="F2" s="6"/>
+      <x:c r="G2" s="6"/>
+      <x:c r="H2" s="6"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="25" t="str">
+        <x:v>Team / Committee Name</x:v>
+      </x:c>
+      <x:c r="B4" s="82"/>
+      <x:c r="C4" s="84"/>
+      <x:c r="D4" s="25" t="str">
+        <x:v>Recorder</x:v>
+      </x:c>
+      <x:c r="E4" s="63"/>
+      <x:c r="F4" s="110"/>
+      <x:c r="G4" s="64"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="25" t="str">
+        <x:v>Scope: integrated recommendation</x:v>
+      </x:c>
+      <x:c r="B5" s="85"/>
+      <x:c r="C5" s="87"/>
+      <x:c r="D5" s="25" t="str">
+        <x:v>Gate</x:v>
+      </x:c>
+      <x:c r="E5" s="14" t="str">
+        <x:v>Issue final recommendation and implementation plan</x:v>
+      </x:c>
+      <x:c r="F5" s="14"/>
+      <x:c r="G5" s="14"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="25" t="str">
+        <x:v>Meeting Date</x:v>
+      </x:c>
+      <x:c r="B6" s="111"/>
+      <x:c r="C6" s="112"/>
+      <x:c r="D6" s="25" t="str">
+        <x:v>Meeting Chair</x:v>
+      </x:c>
+      <x:c r="E6" s="63"/>
+      <x:c r="F6" s="110"/>
+      <x:c r="G6" s="64"/>
+    </x:row>
+    <x:row r="8" ht="23" customHeight="1">
+      <x:c r="A8" s="11" t="str">
+        <x:v>EVIDENCE REVIEWED</x:v>
+      </x:c>
+      <x:c r="B8" s="11"/>
+      <x:c r="C8" s="11"/>
+      <x:c r="D8" s="11"/>
+      <x:c r="E8" s="11"/>
+      <x:c r="F8" s="11"/>
+      <x:c r="G8" s="11"/>
+      <x:c r="H8" s="11"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="21" t="str">
+        <x:v>Evidence item</x:v>
+      </x:c>
+      <x:c r="B9" s="21" t="str">
+        <x:v>Location / file</x:v>
+      </x:c>
+      <x:c r="C9" s="21" t="str">
+        <x:v>Source date</x:v>
+      </x:c>
+      <x:c r="D9" s="21" t="str">
+        <x:v>Prepared by</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="str">
+        <x:v>Reviewed by</x:v>
+      </x:c>
+      <x:c r="F9" s="21" t="str">
+        <x:v>Key issue</x:v>
+      </x:c>
+      <x:c r="G9" s="21" t="str">
+        <x:v>Review status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="82" t="str"/>
+      <x:c r="B10" s="83" t="str"/>
+      <x:c r="C10" s="91" t="str"/>
+      <x:c r="D10" s="83" t="str"/>
+      <x:c r="E10" s="83" t="str"/>
+      <x:c r="F10" s="83" t="str"/>
+      <x:c r="G10" s="84" t="str">
+        <x:v>Not reviewed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="85" t="str"/>
+      <x:c r="B11" s="86" t="str"/>
+      <x:c r="C11" s="92" t="str"/>
+      <x:c r="D11" s="86" t="str"/>
+      <x:c r="E11" s="86" t="str"/>
+      <x:c r="F11" s="86" t="str"/>
+      <x:c r="G11" s="87" t="str">
+        <x:v>Not reviewed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="85" t="str"/>
+      <x:c r="B12" s="86" t="str"/>
+      <x:c r="C12" s="92" t="str"/>
+      <x:c r="D12" s="86" t="str"/>
+      <x:c r="E12" s="86" t="str"/>
+      <x:c r="F12" s="86" t="str"/>
+      <x:c r="G12" s="87" t="str">
+        <x:v>Not reviewed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="85" t="str"/>
+      <x:c r="B13" s="86" t="str"/>
+      <x:c r="C13" s="92" t="str"/>
+      <x:c r="D13" s="86" t="str"/>
+      <x:c r="E13" s="86" t="str"/>
+      <x:c r="F13" s="86" t="str"/>
+      <x:c r="G13" s="87" t="str">
+        <x:v>Not reviewed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="85" t="str"/>
+      <x:c r="B14" s="86" t="str"/>
+      <x:c r="C14" s="92" t="str"/>
+      <x:c r="D14" s="86" t="str"/>
+      <x:c r="E14" s="86" t="str"/>
+      <x:c r="F14" s="86" t="str"/>
+      <x:c r="G14" s="87" t="str">
+        <x:v>Not reviewed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="88" t="str"/>
+      <x:c r="B15" s="89" t="str"/>
+      <x:c r="C15" s="93" t="str"/>
+      <x:c r="D15" s="89" t="str"/>
+      <x:c r="E15" s="89" t="str"/>
+      <x:c r="F15" s="89" t="str"/>
+      <x:c r="G15" s="90" t="str">
+        <x:v>Not reviewed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="25" t="str">
+        <x:v>Evidence status</x:v>
+      </x:c>
+      <x:c r="B17" s="30" t="str">
+        <x:f>IF(COUNTIF(G10:G15,"Reviewed")=6,"EVIDENCE COMPLETE","EVIDENCE INCOMPLETE")</x:f>
+        <x:v>EVIDENCE INCOMPLETE</x:v>
+      </x:c>
+      <x:c r="C17" s="30"/>
+    </x:row>
+    <x:row r="19" ht="23" customHeight="1">
+      <x:c r="A19" s="11" t="str">
+        <x:v>MOTION</x:v>
+      </x:c>
+      <x:c r="B19" s="11"/>
+      <x:c r="C19" s="11"/>
+      <x:c r="D19" s="11"/>
+      <x:c r="E19" s="11"/>
+      <x:c r="F19" s="11"/>
+      <x:c r="G19" s="11"/>
+      <x:c r="H19" s="11"/>
+    </x:row>
+    <x:row r="20" ht="30" customHeight="1">
+      <x:c r="A20" s="37" t="str">
+        <x:v>Write the exact motion presented to the committee. It must name the recommendation, scope, and any conditions.</x:v>
+      </x:c>
+      <x:c r="B20" s="37"/>
+      <x:c r="C20" s="37"/>
+      <x:c r="D20" s="37"/>
+      <x:c r="E20" s="37"/>
+      <x:c r="F20" s="37"/>
+      <x:c r="G20" s="37"/>
+    </x:row>
+    <x:row r="21" ht="42" customHeight="1">
+      <x:c r="A21" s="63"/>
+      <x:c r="B21" s="110"/>
+      <x:c r="C21" s="110"/>
+      <x:c r="D21" s="110"/>
+      <x:c r="E21" s="110"/>
+      <x:c r="F21" s="110"/>
+      <x:c r="G21" s="64"/>
+    </x:row>
+    <x:row r="23" ht="23" customHeight="1">
+      <x:c r="A23" s="11" t="str">
+        <x:v>COMMITTEE VOTE</x:v>
+      </x:c>
+      <x:c r="B23" s="11"/>
+      <x:c r="C23" s="11"/>
+      <x:c r="D23" s="11"/>
+      <x:c r="E23" s="11"/>
+      <x:c r="F23" s="11"/>
+      <x:c r="G23" s="11"/>
+      <x:c r="H23" s="11"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="21" t="str">
+        <x:v>Committee seat</x:v>
+      </x:c>
+      <x:c r="B24" s="21" t="str">
+        <x:v>Member name</x:v>
+      </x:c>
+      <x:c r="C24" s="21" t="str">
+        <x:v>Vote</x:v>
+      </x:c>
+      <x:c r="D24" s="21" t="str">
+        <x:v>Reservation / condition</x:v>
+      </x:c>
+      <x:c r="E24" s="21" t="str">
+        <x:v>Evidence cited</x:v>
+      </x:c>
+      <x:c r="F24" s="21" t="str">
+        <x:v>Initials</x:v>
+      </x:c>
+      <x:c r="G24" s="21" t="str">
+        <x:v>Follow-up owner</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="114" t="str">
+        <x:v>Client &amp; Macro</x:v>
+      </x:c>
+      <x:c r="B25" s="82" t="str"/>
+      <x:c r="C25" s="83" t="str"/>
+      <x:c r="D25" s="83" t="str"/>
+      <x:c r="E25" s="83" t="str"/>
+      <x:c r="F25" s="83" t="str"/>
+      <x:c r="G25" s="84" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="114" t="str">
+        <x:v>Fixed Income</x:v>
+      </x:c>
+      <x:c r="B26" s="85" t="str"/>
+      <x:c r="C26" s="86" t="str"/>
+      <x:c r="D26" s="86" t="str"/>
+      <x:c r="E26" s="86" t="str"/>
+      <x:c r="F26" s="86" t="str"/>
+      <x:c r="G26" s="87" t="str"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="114" t="str">
+        <x:v>Fund &amp; ETF</x:v>
+      </x:c>
+      <x:c r="B27" s="85" t="str"/>
+      <x:c r="C27" s="86" t="str"/>
+      <x:c r="D27" s="86" t="str"/>
+      <x:c r="E27" s="86" t="str"/>
+      <x:c r="F27" s="86" t="str"/>
+      <x:c r="G27" s="87" t="str"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="114" t="str">
+        <x:v>Portfolio &amp; Risk</x:v>
+      </x:c>
+      <x:c r="B28" s="88" t="str"/>
+      <x:c r="C28" s="89" t="str"/>
+      <x:c r="D28" s="89" t="str"/>
+      <x:c r="E28" s="89" t="str"/>
+      <x:c r="F28" s="89" t="str"/>
+      <x:c r="G28" s="90" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="25" t="str">
+        <x:v>Decision status</x:v>
+      </x:c>
+      <x:c r="B30" s="28" t="str">
+        <x:f>IF(COUNTIF(C25:C28,"Revise")+COUNTIF(C25:C28,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C28,"Approve")=4,"APPROVED","INCOMPLETE"))</x:f>
+        <x:v>INCOMPLETE</x:v>
+      </x:c>
+      <x:c r="C30" s="29"/>
+    </x:row>
+    <x:row r="32" ht="23" customHeight="1">
+      <x:c r="A32" s="11" t="str">
+        <x:v>DISSENT, RESERVATIONS &amp; CONDITIONS</x:v>
+      </x:c>
+      <x:c r="B32" s="11"/>
+      <x:c r="C32" s="11"/>
+      <x:c r="D32" s="11"/>
+      <x:c r="E32" s="11"/>
+      <x:c r="F32" s="11"/>
+      <x:c r="G32" s="11"/>
+      <x:c r="H32" s="11"/>
+    </x:row>
+    <x:row r="33" ht="34" customHeight="1">
+      <x:c r="A33" s="82"/>
+      <x:c r="B33" s="83"/>
+      <x:c r="C33" s="83"/>
+      <x:c r="D33" s="83"/>
+      <x:c r="E33" s="83"/>
+      <x:c r="F33" s="83"/>
+      <x:c r="G33" s="84"/>
+    </x:row>
+    <x:row r="34" ht="34" customHeight="1">
+      <x:c r="A34" s="88"/>
+      <x:c r="B34" s="89"/>
+      <x:c r="C34" s="89"/>
+      <x:c r="D34" s="89"/>
+      <x:c r="E34" s="89"/>
+      <x:c r="F34" s="89"/>
+      <x:c r="G34" s="90"/>
+    </x:row>
+    <x:row r="36" ht="23" customHeight="1">
+      <x:c r="A36" s="11" t="str">
+        <x:v>ACTION ITEMS</x:v>
+      </x:c>
+      <x:c r="B36" s="11"/>
+      <x:c r="C36" s="11"/>
+      <x:c r="D36" s="11"/>
+      <x:c r="E36" s="11"/>
+      <x:c r="F36" s="11"/>
+      <x:c r="G36" s="11"/>
+      <x:c r="H36" s="11"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="21" t="str">
+        <x:v>Action required</x:v>
+      </x:c>
+      <x:c r="B37" s="21" t="str">
+        <x:v>Owner</x:v>
+      </x:c>
+      <x:c r="C37" s="21" t="str">
+        <x:v>Due date</x:v>
+      </x:c>
+      <x:c r="D37" s="21" t="str">
+        <x:v>Evidence of completion</x:v>
+      </x:c>
+      <x:c r="E37" s="21" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="F37" s="21" t="str">
+        <x:v>Committee check</x:v>
+      </x:c>
+      <x:c r="G37" s="21" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="82" t="str"/>
+      <x:c r="B38" s="83" t="str"/>
+      <x:c r="C38" s="91" t="str"/>
+      <x:c r="D38" s="83" t="str"/>
+      <x:c r="E38" s="83" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="F38" s="83" t="str"/>
+      <x:c r="G38" s="84" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="85" t="str"/>
+      <x:c r="B39" s="86" t="str"/>
+      <x:c r="C39" s="92" t="str"/>
+      <x:c r="D39" s="86" t="str"/>
+      <x:c r="E39" s="86" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="F39" s="86" t="str"/>
+      <x:c r="G39" s="87" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="85" t="str"/>
+      <x:c r="B40" s="86" t="str"/>
+      <x:c r="C40" s="92" t="str"/>
+      <x:c r="D40" s="86" t="str"/>
+      <x:c r="E40" s="86" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="F40" s="86" t="str"/>
+      <x:c r="G40" s="87" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="85" t="str"/>
+      <x:c r="B41" s="86" t="str"/>
+      <x:c r="C41" s="92" t="str"/>
+      <x:c r="D41" s="86" t="str"/>
+      <x:c r="E41" s="86" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="F41" s="86" t="str"/>
+      <x:c r="G41" s="87" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="88" t="str"/>
+      <x:c r="B42" s="89" t="str"/>
+      <x:c r="C42" s="93" t="str"/>
+      <x:c r="D42" s="89" t="str"/>
+      <x:c r="E42" s="89" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="F42" s="89" t="str"/>
+      <x:c r="G42" s="90" t="str"/>
+    </x:row>
+    <x:row r="44" ht="32" customHeight="1">
+      <x:c r="A44" s="104" t="str">
+        <x:v>Approval requires four Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
+      </x:c>
+      <x:c r="B44" s="104"/>
+      <x:c r="C44" s="104"/>
+      <x:c r="D44" s="104"/>
+      <x:c r="E44" s="104"/>
+      <x:c r="F44" s="104"/>
+      <x:c r="G44" s="104"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="B4:C4"/>
+    <x:mergeCell ref="B5:C5"/>
+    <x:mergeCell ref="B6:C6"/>
+    <x:mergeCell ref="E4:G4"/>
+    <x:mergeCell ref="E5:G5"/>
+    <x:mergeCell ref="E6:G6"/>
+    <x:mergeCell ref="A8:H8"/>
+    <x:mergeCell ref="B17:C17"/>
+    <x:mergeCell ref="A19:H19"/>
+    <x:mergeCell ref="A20:G20"/>
+    <x:mergeCell ref="A21:G21"/>
+    <x:mergeCell ref="A23:H23"/>
+    <x:mergeCell ref="B30:C30"/>
+    <x:mergeCell ref="A32:H32"/>
+    <x:mergeCell ref="A33:G34"/>
+    <x:mergeCell ref="A36:H36"/>
+    <x:mergeCell ref="A44:G44"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="B30:C30">
+    <x:cfRule type="containsText" dxfId="46" priority="1" operator="containsText" text="APPROVED"/>
+    <x:cfRule type="containsText" dxfId="47" priority="2" operator="containsText" text="REVISION"/>
+    <x:cfRule type="containsText" dxfId="48" priority="3" operator="containsText" text="INCOMPLETE"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="3">
+    <x:dataValidation type="list" sqref="G10:G15">
+      <x:formula1>"Not reviewed,Reviewed,Needs follow-up"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="C25:C28">
+      <x:formula1>"Approve,Revise,Reject"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E38:E42">
+      <x:formula1>"Open,Complete"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
@@ -3923,292 +5571,292 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="97" t="str"/>
-      <x:c r="B5" s="86" t="str"/>
-      <x:c r="C5" s="86" t="str"/>
-      <x:c r="D5" s="86" t="str"/>
-      <x:c r="E5" s="86" t="str"/>
-      <x:c r="F5" s="86" t="str"/>
-      <x:c r="G5" s="86" t="str"/>
-      <x:c r="H5" s="86" t="str"/>
-      <x:c r="I5" s="65" t="str"/>
+      <x:c r="A5" s="115" t="str"/>
+      <x:c r="B5" s="83" t="str"/>
+      <x:c r="C5" s="83" t="str"/>
+      <x:c r="D5" s="83" t="str"/>
+      <x:c r="E5" s="83" t="str"/>
+      <x:c r="F5" s="83" t="str"/>
+      <x:c r="G5" s="83" t="str"/>
+      <x:c r="H5" s="83" t="str"/>
+      <x:c r="I5" s="84" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="98" t="str"/>
-      <x:c r="B6" s="87" t="str"/>
-      <x:c r="C6" s="87" t="str"/>
-      <x:c r="D6" s="87" t="str"/>
-      <x:c r="E6" s="87" t="str"/>
-      <x:c r="F6" s="87" t="str"/>
-      <x:c r="G6" s="87" t="str"/>
-      <x:c r="H6" s="87" t="str"/>
-      <x:c r="I6" s="67" t="str"/>
+      <x:c r="A6" s="116" t="str"/>
+      <x:c r="B6" s="86" t="str"/>
+      <x:c r="C6" s="86" t="str"/>
+      <x:c r="D6" s="86" t="str"/>
+      <x:c r="E6" s="86" t="str"/>
+      <x:c r="F6" s="86" t="str"/>
+      <x:c r="G6" s="86" t="str"/>
+      <x:c r="H6" s="86" t="str"/>
+      <x:c r="I6" s="87" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="98" t="str"/>
-      <x:c r="B7" s="87" t="str"/>
-      <x:c r="C7" s="87" t="str"/>
-      <x:c r="D7" s="87" t="str"/>
-      <x:c r="E7" s="87" t="str"/>
-      <x:c r="F7" s="87" t="str"/>
-      <x:c r="G7" s="87" t="str"/>
-      <x:c r="H7" s="87" t="str"/>
-      <x:c r="I7" s="67" t="str"/>
+      <x:c r="A7" s="116" t="str"/>
+      <x:c r="B7" s="86" t="str"/>
+      <x:c r="C7" s="86" t="str"/>
+      <x:c r="D7" s="86" t="str"/>
+      <x:c r="E7" s="86" t="str"/>
+      <x:c r="F7" s="86" t="str"/>
+      <x:c r="G7" s="86" t="str"/>
+      <x:c r="H7" s="86" t="str"/>
+      <x:c r="I7" s="87" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="98" t="str"/>
-      <x:c r="B8" s="87" t="str"/>
-      <x:c r="C8" s="87" t="str"/>
-      <x:c r="D8" s="87" t="str"/>
-      <x:c r="E8" s="87" t="str"/>
-      <x:c r="F8" s="87" t="str"/>
-      <x:c r="G8" s="87" t="str"/>
-      <x:c r="H8" s="87" t="str"/>
-      <x:c r="I8" s="67" t="str"/>
+      <x:c r="A8" s="116" t="str"/>
+      <x:c r="B8" s="86" t="str"/>
+      <x:c r="C8" s="86" t="str"/>
+      <x:c r="D8" s="86" t="str"/>
+      <x:c r="E8" s="86" t="str"/>
+      <x:c r="F8" s="86" t="str"/>
+      <x:c r="G8" s="86" t="str"/>
+      <x:c r="H8" s="86" t="str"/>
+      <x:c r="I8" s="87" t="str"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="98" t="str"/>
-      <x:c r="B9" s="87" t="str"/>
-      <x:c r="C9" s="87" t="str"/>
-      <x:c r="D9" s="87" t="str"/>
-      <x:c r="E9" s="87" t="str"/>
-      <x:c r="F9" s="87" t="str"/>
-      <x:c r="G9" s="87" t="str"/>
-      <x:c r="H9" s="87" t="str"/>
-      <x:c r="I9" s="67" t="str"/>
+      <x:c r="A9" s="116" t="str"/>
+      <x:c r="B9" s="86" t="str"/>
+      <x:c r="C9" s="86" t="str"/>
+      <x:c r="D9" s="86" t="str"/>
+      <x:c r="E9" s="86" t="str"/>
+      <x:c r="F9" s="86" t="str"/>
+      <x:c r="G9" s="86" t="str"/>
+      <x:c r="H9" s="86" t="str"/>
+      <x:c r="I9" s="87" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="98" t="str"/>
-      <x:c r="B10" s="87" t="str"/>
-      <x:c r="C10" s="87" t="str"/>
-      <x:c r="D10" s="87" t="str"/>
-      <x:c r="E10" s="87" t="str"/>
-      <x:c r="F10" s="87" t="str"/>
-      <x:c r="G10" s="87" t="str"/>
-      <x:c r="H10" s="87" t="str"/>
-      <x:c r="I10" s="67" t="str"/>
+      <x:c r="A10" s="116" t="str"/>
+      <x:c r="B10" s="86" t="str"/>
+      <x:c r="C10" s="86" t="str"/>
+      <x:c r="D10" s="86" t="str"/>
+      <x:c r="E10" s="86" t="str"/>
+      <x:c r="F10" s="86" t="str"/>
+      <x:c r="G10" s="86" t="str"/>
+      <x:c r="H10" s="86" t="str"/>
+      <x:c r="I10" s="87" t="str"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="98" t="str"/>
-      <x:c r="B11" s="87" t="str"/>
-      <x:c r="C11" s="87" t="str"/>
-      <x:c r="D11" s="87" t="str"/>
-      <x:c r="E11" s="87" t="str"/>
-      <x:c r="F11" s="87" t="str"/>
-      <x:c r="G11" s="87" t="str"/>
-      <x:c r="H11" s="87" t="str"/>
-      <x:c r="I11" s="67" t="str"/>
+      <x:c r="A11" s="116" t="str"/>
+      <x:c r="B11" s="86" t="str"/>
+      <x:c r="C11" s="86" t="str"/>
+      <x:c r="D11" s="86" t="str"/>
+      <x:c r="E11" s="86" t="str"/>
+      <x:c r="F11" s="86" t="str"/>
+      <x:c r="G11" s="86" t="str"/>
+      <x:c r="H11" s="86" t="str"/>
+      <x:c r="I11" s="87" t="str"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="98" t="str"/>
-      <x:c r="B12" s="87" t="str"/>
-      <x:c r="C12" s="87" t="str"/>
-      <x:c r="D12" s="87" t="str"/>
-      <x:c r="E12" s="87" t="str"/>
-      <x:c r="F12" s="87" t="str"/>
-      <x:c r="G12" s="87" t="str"/>
-      <x:c r="H12" s="87" t="str"/>
-      <x:c r="I12" s="67" t="str"/>
+      <x:c r="A12" s="116" t="str"/>
+      <x:c r="B12" s="86" t="str"/>
+      <x:c r="C12" s="86" t="str"/>
+      <x:c r="D12" s="86" t="str"/>
+      <x:c r="E12" s="86" t="str"/>
+      <x:c r="F12" s="86" t="str"/>
+      <x:c r="G12" s="86" t="str"/>
+      <x:c r="H12" s="86" t="str"/>
+      <x:c r="I12" s="87" t="str"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="98" t="str"/>
-      <x:c r="B13" s="87" t="str"/>
-      <x:c r="C13" s="87" t="str"/>
-      <x:c r="D13" s="87" t="str"/>
-      <x:c r="E13" s="87" t="str"/>
-      <x:c r="F13" s="87" t="str"/>
-      <x:c r="G13" s="87" t="str"/>
-      <x:c r="H13" s="87" t="str"/>
-      <x:c r="I13" s="67" t="str"/>
+      <x:c r="A13" s="116" t="str"/>
+      <x:c r="B13" s="86" t="str"/>
+      <x:c r="C13" s="86" t="str"/>
+      <x:c r="D13" s="86" t="str"/>
+      <x:c r="E13" s="86" t="str"/>
+      <x:c r="F13" s="86" t="str"/>
+      <x:c r="G13" s="86" t="str"/>
+      <x:c r="H13" s="86" t="str"/>
+      <x:c r="I13" s="87" t="str"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="98" t="str"/>
-      <x:c r="B14" s="87" t="str"/>
-      <x:c r="C14" s="87" t="str"/>
-      <x:c r="D14" s="87" t="str"/>
-      <x:c r="E14" s="87" t="str"/>
-      <x:c r="F14" s="87" t="str"/>
-      <x:c r="G14" s="87" t="str"/>
-      <x:c r="H14" s="87" t="str"/>
-      <x:c r="I14" s="67" t="str"/>
+      <x:c r="A14" s="116" t="str"/>
+      <x:c r="B14" s="86" t="str"/>
+      <x:c r="C14" s="86" t="str"/>
+      <x:c r="D14" s="86" t="str"/>
+      <x:c r="E14" s="86" t="str"/>
+      <x:c r="F14" s="86" t="str"/>
+      <x:c r="G14" s="86" t="str"/>
+      <x:c r="H14" s="86" t="str"/>
+      <x:c r="I14" s="87" t="str"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="98" t="str"/>
-      <x:c r="B15" s="87" t="str"/>
-      <x:c r="C15" s="87" t="str"/>
-      <x:c r="D15" s="87" t="str"/>
-      <x:c r="E15" s="87" t="str"/>
-      <x:c r="F15" s="87" t="str"/>
-      <x:c r="G15" s="87" t="str"/>
-      <x:c r="H15" s="87" t="str"/>
-      <x:c r="I15" s="67" t="str"/>
+      <x:c r="A15" s="116" t="str"/>
+      <x:c r="B15" s="86" t="str"/>
+      <x:c r="C15" s="86" t="str"/>
+      <x:c r="D15" s="86" t="str"/>
+      <x:c r="E15" s="86" t="str"/>
+      <x:c r="F15" s="86" t="str"/>
+      <x:c r="G15" s="86" t="str"/>
+      <x:c r="H15" s="86" t="str"/>
+      <x:c r="I15" s="87" t="str"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="98" t="str"/>
-      <x:c r="B16" s="87" t="str"/>
-      <x:c r="C16" s="87" t="str"/>
-      <x:c r="D16" s="87" t="str"/>
-      <x:c r="E16" s="87" t="str"/>
-      <x:c r="F16" s="87" t="str"/>
-      <x:c r="G16" s="87" t="str"/>
-      <x:c r="H16" s="87" t="str"/>
-      <x:c r="I16" s="67" t="str"/>
+      <x:c r="A16" s="116" t="str"/>
+      <x:c r="B16" s="86" t="str"/>
+      <x:c r="C16" s="86" t="str"/>
+      <x:c r="D16" s="86" t="str"/>
+      <x:c r="E16" s="86" t="str"/>
+      <x:c r="F16" s="86" t="str"/>
+      <x:c r="G16" s="86" t="str"/>
+      <x:c r="H16" s="86" t="str"/>
+      <x:c r="I16" s="87" t="str"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="98" t="str"/>
-      <x:c r="B17" s="87" t="str"/>
-      <x:c r="C17" s="87" t="str"/>
-      <x:c r="D17" s="87" t="str"/>
-      <x:c r="E17" s="87" t="str"/>
-      <x:c r="F17" s="87" t="str"/>
-      <x:c r="G17" s="87" t="str"/>
-      <x:c r="H17" s="87" t="str"/>
-      <x:c r="I17" s="67" t="str"/>
+      <x:c r="A17" s="116" t="str"/>
+      <x:c r="B17" s="86" t="str"/>
+      <x:c r="C17" s="86" t="str"/>
+      <x:c r="D17" s="86" t="str"/>
+      <x:c r="E17" s="86" t="str"/>
+      <x:c r="F17" s="86" t="str"/>
+      <x:c r="G17" s="86" t="str"/>
+      <x:c r="H17" s="86" t="str"/>
+      <x:c r="I17" s="87" t="str"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="98" t="str"/>
-      <x:c r="B18" s="87" t="str"/>
-      <x:c r="C18" s="87" t="str"/>
-      <x:c r="D18" s="87" t="str"/>
-      <x:c r="E18" s="87" t="str"/>
-      <x:c r="F18" s="87" t="str"/>
-      <x:c r="G18" s="87" t="str"/>
-      <x:c r="H18" s="87" t="str"/>
-      <x:c r="I18" s="67" t="str"/>
+      <x:c r="A18" s="116" t="str"/>
+      <x:c r="B18" s="86" t="str"/>
+      <x:c r="C18" s="86" t="str"/>
+      <x:c r="D18" s="86" t="str"/>
+      <x:c r="E18" s="86" t="str"/>
+      <x:c r="F18" s="86" t="str"/>
+      <x:c r="G18" s="86" t="str"/>
+      <x:c r="H18" s="86" t="str"/>
+      <x:c r="I18" s="87" t="str"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="98" t="str"/>
-      <x:c r="B19" s="87" t="str"/>
-      <x:c r="C19" s="87" t="str"/>
-      <x:c r="D19" s="87" t="str"/>
-      <x:c r="E19" s="87" t="str"/>
-      <x:c r="F19" s="87" t="str"/>
-      <x:c r="G19" s="87" t="str"/>
-      <x:c r="H19" s="87" t="str"/>
-      <x:c r="I19" s="67" t="str"/>
+      <x:c r="A19" s="116" t="str"/>
+      <x:c r="B19" s="86" t="str"/>
+      <x:c r="C19" s="86" t="str"/>
+      <x:c r="D19" s="86" t="str"/>
+      <x:c r="E19" s="86" t="str"/>
+      <x:c r="F19" s="86" t="str"/>
+      <x:c r="G19" s="86" t="str"/>
+      <x:c r="H19" s="86" t="str"/>
+      <x:c r="I19" s="87" t="str"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="98" t="str"/>
-      <x:c r="B20" s="87" t="str"/>
-      <x:c r="C20" s="87" t="str"/>
-      <x:c r="D20" s="87" t="str"/>
-      <x:c r="E20" s="87" t="str"/>
-      <x:c r="F20" s="87" t="str"/>
-      <x:c r="G20" s="87" t="str"/>
-      <x:c r="H20" s="87" t="str"/>
-      <x:c r="I20" s="67" t="str"/>
+      <x:c r="A20" s="116" t="str"/>
+      <x:c r="B20" s="86" t="str"/>
+      <x:c r="C20" s="86" t="str"/>
+      <x:c r="D20" s="86" t="str"/>
+      <x:c r="E20" s="86" t="str"/>
+      <x:c r="F20" s="86" t="str"/>
+      <x:c r="G20" s="86" t="str"/>
+      <x:c r="H20" s="86" t="str"/>
+      <x:c r="I20" s="87" t="str"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="98" t="str"/>
-      <x:c r="B21" s="87" t="str"/>
-      <x:c r="C21" s="87" t="str"/>
-      <x:c r="D21" s="87" t="str"/>
-      <x:c r="E21" s="87" t="str"/>
-      <x:c r="F21" s="87" t="str"/>
-      <x:c r="G21" s="87" t="str"/>
-      <x:c r="H21" s="87" t="str"/>
-      <x:c r="I21" s="67" t="str"/>
+      <x:c r="A21" s="116" t="str"/>
+      <x:c r="B21" s="86" t="str"/>
+      <x:c r="C21" s="86" t="str"/>
+      <x:c r="D21" s="86" t="str"/>
+      <x:c r="E21" s="86" t="str"/>
+      <x:c r="F21" s="86" t="str"/>
+      <x:c r="G21" s="86" t="str"/>
+      <x:c r="H21" s="86" t="str"/>
+      <x:c r="I21" s="87" t="str"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="98" t="str"/>
-      <x:c r="B22" s="87" t="str"/>
-      <x:c r="C22" s="87" t="str"/>
-      <x:c r="D22" s="87" t="str"/>
-      <x:c r="E22" s="87" t="str"/>
-      <x:c r="F22" s="87" t="str"/>
-      <x:c r="G22" s="87" t="str"/>
-      <x:c r="H22" s="87" t="str"/>
-      <x:c r="I22" s="67" t="str"/>
+      <x:c r="A22" s="116" t="str"/>
+      <x:c r="B22" s="86" t="str"/>
+      <x:c r="C22" s="86" t="str"/>
+      <x:c r="D22" s="86" t="str"/>
+      <x:c r="E22" s="86" t="str"/>
+      <x:c r="F22" s="86" t="str"/>
+      <x:c r="G22" s="86" t="str"/>
+      <x:c r="H22" s="86" t="str"/>
+      <x:c r="I22" s="87" t="str"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="98" t="str"/>
-      <x:c r="B23" s="87" t="str"/>
-      <x:c r="C23" s="87" t="str"/>
-      <x:c r="D23" s="87" t="str"/>
-      <x:c r="E23" s="87" t="str"/>
-      <x:c r="F23" s="87" t="str"/>
-      <x:c r="G23" s="87" t="str"/>
-      <x:c r="H23" s="87" t="str"/>
-      <x:c r="I23" s="67" t="str"/>
+      <x:c r="A23" s="116" t="str"/>
+      <x:c r="B23" s="86" t="str"/>
+      <x:c r="C23" s="86" t="str"/>
+      <x:c r="D23" s="86" t="str"/>
+      <x:c r="E23" s="86" t="str"/>
+      <x:c r="F23" s="86" t="str"/>
+      <x:c r="G23" s="86" t="str"/>
+      <x:c r="H23" s="86" t="str"/>
+      <x:c r="I23" s="87" t="str"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="98" t="str"/>
-      <x:c r="B24" s="87" t="str"/>
-      <x:c r="C24" s="87" t="str"/>
-      <x:c r="D24" s="87" t="str"/>
-      <x:c r="E24" s="87" t="str"/>
-      <x:c r="F24" s="87" t="str"/>
-      <x:c r="G24" s="87" t="str"/>
-      <x:c r="H24" s="87" t="str"/>
-      <x:c r="I24" s="67" t="str"/>
+      <x:c r="A24" s="116" t="str"/>
+      <x:c r="B24" s="86" t="str"/>
+      <x:c r="C24" s="86" t="str"/>
+      <x:c r="D24" s="86" t="str"/>
+      <x:c r="E24" s="86" t="str"/>
+      <x:c r="F24" s="86" t="str"/>
+      <x:c r="G24" s="86" t="str"/>
+      <x:c r="H24" s="86" t="str"/>
+      <x:c r="I24" s="87" t="str"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="98" t="str"/>
-      <x:c r="B25" s="87" t="str"/>
-      <x:c r="C25" s="87" t="str"/>
-      <x:c r="D25" s="87" t="str"/>
-      <x:c r="E25" s="87" t="str"/>
-      <x:c r="F25" s="87" t="str"/>
-      <x:c r="G25" s="87" t="str"/>
-      <x:c r="H25" s="87" t="str"/>
-      <x:c r="I25" s="67" t="str"/>
+      <x:c r="A25" s="116" t="str"/>
+      <x:c r="B25" s="86" t="str"/>
+      <x:c r="C25" s="86" t="str"/>
+      <x:c r="D25" s="86" t="str"/>
+      <x:c r="E25" s="86" t="str"/>
+      <x:c r="F25" s="86" t="str"/>
+      <x:c r="G25" s="86" t="str"/>
+      <x:c r="H25" s="86" t="str"/>
+      <x:c r="I25" s="87" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="98" t="str"/>
-      <x:c r="B26" s="87" t="str"/>
-      <x:c r="C26" s="87" t="str"/>
-      <x:c r="D26" s="87" t="str"/>
-      <x:c r="E26" s="87" t="str"/>
-      <x:c r="F26" s="87" t="str"/>
-      <x:c r="G26" s="87" t="str"/>
-      <x:c r="H26" s="87" t="str"/>
-      <x:c r="I26" s="67" t="str"/>
+      <x:c r="A26" s="116" t="str"/>
+      <x:c r="B26" s="86" t="str"/>
+      <x:c r="C26" s="86" t="str"/>
+      <x:c r="D26" s="86" t="str"/>
+      <x:c r="E26" s="86" t="str"/>
+      <x:c r="F26" s="86" t="str"/>
+      <x:c r="G26" s="86" t="str"/>
+      <x:c r="H26" s="86" t="str"/>
+      <x:c r="I26" s="87" t="str"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="98" t="str"/>
-      <x:c r="B27" s="87" t="str"/>
-      <x:c r="C27" s="87" t="str"/>
-      <x:c r="D27" s="87" t="str"/>
-      <x:c r="E27" s="87" t="str"/>
-      <x:c r="F27" s="87" t="str"/>
-      <x:c r="G27" s="87" t="str"/>
-      <x:c r="H27" s="87" t="str"/>
-      <x:c r="I27" s="67" t="str"/>
+      <x:c r="A27" s="116" t="str"/>
+      <x:c r="B27" s="86" t="str"/>
+      <x:c r="C27" s="86" t="str"/>
+      <x:c r="D27" s="86" t="str"/>
+      <x:c r="E27" s="86" t="str"/>
+      <x:c r="F27" s="86" t="str"/>
+      <x:c r="G27" s="86" t="str"/>
+      <x:c r="H27" s="86" t="str"/>
+      <x:c r="I27" s="87" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="98" t="str"/>
-      <x:c r="B28" s="87" t="str"/>
-      <x:c r="C28" s="87" t="str"/>
-      <x:c r="D28" s="87" t="str"/>
-      <x:c r="E28" s="87" t="str"/>
-      <x:c r="F28" s="87" t="str"/>
-      <x:c r="G28" s="87" t="str"/>
-      <x:c r="H28" s="87" t="str"/>
-      <x:c r="I28" s="67" t="str"/>
+      <x:c r="A28" s="116" t="str"/>
+      <x:c r="B28" s="86" t="str"/>
+      <x:c r="C28" s="86" t="str"/>
+      <x:c r="D28" s="86" t="str"/>
+      <x:c r="E28" s="86" t="str"/>
+      <x:c r="F28" s="86" t="str"/>
+      <x:c r="G28" s="86" t="str"/>
+      <x:c r="H28" s="86" t="str"/>
+      <x:c r="I28" s="87" t="str"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="79" t="str"/>
-      <x:c r="B29" s="88" t="str"/>
-      <x:c r="C29" s="88" t="str"/>
-      <x:c r="D29" s="88" t="str"/>
-      <x:c r="E29" s="88" t="str"/>
-      <x:c r="F29" s="88" t="str"/>
-      <x:c r="G29" s="88" t="str"/>
-      <x:c r="H29" s="88" t="str"/>
-      <x:c r="I29" s="69" t="str"/>
+      <x:c r="A29" s="111" t="str"/>
+      <x:c r="B29" s="89" t="str"/>
+      <x:c r="C29" s="89" t="str"/>
+      <x:c r="D29" s="89" t="str"/>
+      <x:c r="E29" s="89" t="str"/>
+      <x:c r="F29" s="89" t="str"/>
+      <x:c r="G29" s="89" t="str"/>
+      <x:c r="H29" s="89" t="str"/>
+      <x:c r="I29" s="90" t="str"/>
     </x:row>
     <x:row r="31" ht="32" customHeight="1">
-      <x:c r="A31" s="96" t="str">
+      <x:c r="A31" s="104" t="str">
         <x:v>Do not paste confidential client information or proprietary FactSet data into an AI tool. Every AI-assisted factual claim or number must be traceable to a human-verified source.</x:v>
       </x:c>
-      <x:c r="B31" s="96"/>
-      <x:c r="C31" s="96"/>
-      <x:c r="D31" s="96"/>
-      <x:c r="E31" s="96"/>
-      <x:c r="F31" s="96"/>
-      <x:c r="G31" s="96"/>
-      <x:c r="H31" s="96"/>
-      <x:c r="I31" s="96"/>
+      <x:c r="B31" s="104"/>
+      <x:c r="C31" s="104"/>
+      <x:c r="D31" s="104"/>
+      <x:c r="E31" s="104"/>
+      <x:c r="F31" s="104"/>
+      <x:c r="G31" s="104"/>
+      <x:c r="H31" s="104"/>
+      <x:c r="I31" s="104"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/files/BUS331_Investment_Committee_Decision_Record_Student.xlsx
+++ b/files/BUS331_Investment_Committee_Decision_Record_Student.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Re5d9bb9fc6394467"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMMITTEE ROSTER" sheetId="2" r:id="Rcf5eb79eba084c63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANALYST DECISION LOG" sheetId="3" r:id="Rcf54d98cd75449b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 1" sheetId="4" r:id="R07842bd965ca4690"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 2 CLIENT 1" sheetId="5" r:id="R0b2893e44b3a4b14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 2 CLIENT 2" sheetId="6" r:id="R903d9252853245b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 2 CLIENT 3" sheetId="7" r:id="Rd7ba186e58af45a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 3" sheetId="8" r:id="R9bed630886b9475c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI AUDIT LOG" sheetId="9" r:id="R7ebd1a91354543e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="rId4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMMITTEE ROSTER" sheetId="2" r:id="rId5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANALYST DECISION LOG" sheetId="3" r:id="rId6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 1" sheetId="4" r:id="rId7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 2 CLIENT 1" sheetId="5" r:id="rId8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 2 CLIENT 2" sheetId="6" r:id="rId9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 2 CLIENT 3" sheetId="7" r:id="rId10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASE 3" sheetId="8" r:id="rId11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI AUDIT LOG" sheetId="9" r:id="rId12"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1410,10 +1410,10 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="str">
-        <x:v>AI interview + challenge</x:v>
+        <x:v>Alternative + trade-off</x:v>
       </x:c>
       <x:c r="B8" s="16" t="str">
-        <x:v>Summarize the bounded client interview and the strongest counterargument; do not paste a transcript as analysis.</x:v>
+        <x:v>Record the strongest realistic alternative rejected and the key trade-off behind the recommendation. Portfolio Manager entries record integration choices; Risk and Derivatives entries record residual risk and hedge/no-hedge evidence.</x:v>
       </x:c>
       <x:c r="C8" s="16" t="str"/>
       <x:c r="D8" s="16" t="str"/>
@@ -1641,7 +1641,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Assign one student to each committee seat. Roles define leadership; all members share the final decision.</x:v>
+        <x:v>Assign one student to each of five committee seats. Roles define distinct decision rights; all members share the final decision.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -1709,38 +1709,56 @@
     </x:row>
     <x:row r="7" ht="72" customHeight="1">
       <x:c r="A7" s="52" t="str">
-        <x:v>Fund and ETF Analyst</x:v>
+        <x:v>Equity Analyst</x:v>
       </x:c>
       <x:c r="B7" s="53" t="str"/>
       <x:c r="C7" s="54" t="str">
-        <x:v>Own pooled-vehicle due diligence, diversification, benchmark fit, fees, liquidity, tax considerations, and active-versus-passive implementation.</x:v>
+        <x:v>Own equity-fund and ETF due diligence and the limited use of individual equities, including exposure, style, sector, holdings, costs, liquidity, overlap, idiosyncratic risk, and position-size evidence.</x:v>
       </x:c>
       <x:c r="D7" s="54" t="str">
-        <x:v>Identify the client's diversification, access, liquidity, cost, tax, values, and vehicle requirements before screening products.</x:v>
+        <x:v>Translate the client's growth needs, time horizon, values, tax position, liquidity, and concentration limits into equity-selection guardrails.</x:v>
       </x:c>
       <x:c r="E7" s="54" t="str">
-        <x:v>Evaluate funds and ETFs using objective, holdings, benchmark, fees, liquidity, tax efficiency, and tracking evidence.</x:v>
+        <x:v>Recommend equity funds and ETFs as the primary equity vehicles and analyze any limited individual equities, including rationale, idiosyncratic risk, and position size.</x:v>
       </x:c>
       <x:c r="F7" s="54" t="str">
-        <x:v>Defend vehicle selection, implementation feasibility, diversification, and product-level due diligence.</x:v>
+        <x:v>Defend equity exposures, vehicle choices, limited individual-security decisions, rejected alternatives, and their client fit.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="72" customHeight="1">
       <x:c r="A8" s="52" t="str">
-        <x:v>Portfolio Manager and Risk Analyst</x:v>
+        <x:v>Portfolio Manager</x:v>
       </x:c>
       <x:c r="B8" s="53" t="str"/>
       <x:c r="C8" s="54" t="str">
-        <x:v>Own portfolio integration, risk capacity versus willingness, the drawdown tripwire, decision-log quality, stress testing, and mandate-breach escalation.</x:v>
+        <x:v>Own portfolio integration: resolve overlap and concentration, set final selection and weights, record explicit trade-offs, maintain decision-log quality, and move the integrated recommendation to a vote.</x:v>
       </x:c>
       <x:c r="D8" s="54" t="str">
-        <x:v>Reconcile risk capacity and willingness, set provisional portfolio guardrails, challenge assumptions, and audit the Analyst Decision Log.</x:v>
+        <x:v>Reconcile risk capacity and willingness, set provisional portfolio guardrails, coordinate the committee challenge, and audit the Analyst Decision Log.</x:v>
       </x:c>
       <x:c r="E8" s="54" t="str">
-        <x:v>Integrate the allocation, run bear-case stress tests, compare mitigants, identify breaches, and require corrective action.</x:v>
+        <x:v>Integrate analyst recommendations, resolve duplication and concentration, choose the final 8–10 holdings and weights, and record the trade-offs behind every integration decision.</x:v>
       </x:c>
       <x:c r="F8" s="54" t="str">
-        <x:v>State the integrated recommendation, present the strongest downside case, and lead preparation for adversarial Q&amp;A.</x:v>
+        <x:v>State and defend the integrated recommendation, portfolio construction decisions, final weights, rejected integrations, and implementation priorities.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="72" customHeight="1">
+      <x:c r="A9" s="52" t="str">
+        <x:v>Risk and Derivatives Analyst</x:v>
+      </x:c>
+      <x:c r="B9" s="53" t="str"/>
+      <x:c r="C9" s="54" t="str">
+        <x:v>Own portfolio-level risk diagnosis, stress testing, residual-risk evidence, mandate-breach escalation, and the hedge or no-hedge conclusion; do not manufacture a derivative position when no targeted hedge is justified.</x:v>
+      </x:c>
+      <x:c r="D9" s="54" t="str">
+        <x:v>Define the downside questions, drawdown tripwire, stress priorities, and residual-risk evidence the final portfolio must address.</x:v>
+      </x:c>
+      <x:c r="E9" s="54" t="str">
+        <x:v>Run portfolio-level stress tests, identify residual risk, and document either one targeted hedge or a fully supported no-hedge conclusion, including cost, liquidity, trade-offs, residual risk, and adjustment or removal conditions.</x:v>
+      </x:c>
+      <x:c r="F9" s="54" t="str">
+        <x:v>Defend the stress evidence, residual risk, hedge or no-hedge decision, limits of the analysis, and conditions that would change the risk response.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="23" customHeight="1">
@@ -1880,7 +1898,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Human-first judgment → AI interview and challenge → human verification → final reasoning → downstream guardrail</x:v>
+        <x:v>Recommendation → alternative rejected → key trade-off → verification → final reasoning → downstream guardrail</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -1904,7 +1922,7 @@
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="58" t="str">
-        <x:v>Before using AI, each of the four roles records at least one initial judgment for each assigned client. Minimum Phase 1 evidence: 12 complete role-by-client entries across the team.</x:v>
+        <x:v>Each of the five roles records at least one recommendation for each assigned client. Every material entry includes an alternative rejected and a key trade-off. Minimum Phase 1 evidence: 15 complete role-by-client entries across the team.</x:v>
       </x:c>
       <x:c r="B4" s="58"/>
       <x:c r="C4" s="58"/>
@@ -1998,10 +2016,10 @@
         <x:v>Claim type</x:v>
       </x:c>
       <x:c r="I7" s="21" t="str">
-        <x:v>AI challenge prompt / purpose</x:v>
+        <x:v>Alternative(s) rejected</x:v>
       </x:c>
       <x:c r="J7" s="21" t="str">
-        <x:v>AI output summary</x:v>
+        <x:v>Key trade-off</x:v>
       </x:c>
       <x:c r="K7" s="21" t="str">
         <x:v>Claim to verify</x:v>
@@ -2829,13 +2847,13 @@
         <x:v>Minimum required</x:v>
       </x:c>
       <x:c r="H40" s="57" t="n">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J40" s="25" t="str">
         <x:v>Log readiness</x:v>
       </x:c>
       <x:c r="K40" s="100" t="str">
-        <x:f>IF(OR(E6="",H6="",K6=""),"ENTER 3 CLIENTS",IF(COUNTIF(B47:D50,"READY")&lt;H40,"COVERAGE INCOMPLETE",IF(COUNTIF(T8:T37,"INCOMPLETE")+E40&gt;0,"REVIEW LOG","READY FOR PHASE 1 GATE")))</x:f>
+        <x:f>IF(OR(E6="",H6="",K6=""),"ENTER 3 CLIENTS",IF(COUNTIF(B47:D51,"READY")&lt;H40,"COVERAGE INCOMPLETE",IF(COUNTIF(T8:T37,"INCOMPLETE")+E40&gt;0,"REVIEW LOG","READY FOR PHASE 1 GATE")))</x:f>
         <x:v>ENTER 3 CLIENTS</x:v>
       </x:c>
       <x:c r="L40" s="101"/>
@@ -2843,7 +2861,7 @@
     </x:row>
     <x:row r="42" ht="34" customHeight="1">
       <x:c r="A42" s="104" t="str">
-        <x:v>Evidence-ready means the entry shows the initial judgment, the AI challenge, a human-verified source and as-of date, what changed, the final reasoning, a downstream guardrail, and peer review. Contradicted or unverifiable material claims must be revised or carried to the committee as an explicit open issue.</x:v>
+        <x:v>Evidence-ready means the entry shows the recommendation or initial judgment, an alternative rejected, a key trade-off, a human-verified source and as-of date, what changed, the final reasoning, a downstream guardrail, and peer review. Portfolio Manager entries identify integration decisions; Risk and Derivatives entries identify residual risk and hedge/no-hedge evidence. Contradicted or unverifiable material claims must be revised or carried to the committee as an explicit open issue.</x:v>
       </x:c>
       <x:c r="B42" s="104"/>
       <x:c r="C42" s="104"/>
@@ -2950,7 +2968,7 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="52" t="str">
-        <x:v>Fund and ETF Analyst</x:v>
+        <x:v>Equity Analyst</x:v>
       </x:c>
       <x:c r="B49" s="107" t="str">
         <x:f>IF(OR($E$6="",COUNTIFS($C$8:$C$37,$E$6,$D$8:$D$37,$A49,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
@@ -2971,7 +2989,7 @@
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="52" t="str">
-        <x:v>Portfolio Manager and Risk Analyst</x:v>
+        <x:v>Portfolio Manager</x:v>
       </x:c>
       <x:c r="B50" s="107" t="str">
         <x:f>IF(OR($E$6="",COUNTIFS($C$8:$C$37,$E$6,$D$8:$D$37,$A50,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
@@ -2990,9 +3008,30 @@
         <x:v>MISSING</x:v>
       </x:c>
     </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="52" t="str">
+        <x:v>Risk and Derivatives Analyst</x:v>
+      </x:c>
+      <x:c r="B51" s="107" t="str">
+        <x:f>IF(OR($E$6="",COUNTIFS($C$8:$C$37,$E$6,$D$8:$D$37,$A51,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+      <x:c r="C51" s="107" t="str">
+        <x:f>IF(OR($H$6="",COUNTIFS($C$8:$C$37,$H$6,$D$8:$D$37,$A51,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+      <x:c r="D51" s="107" t="str">
+        <x:f>IF(OR($K$6="",COUNTIFS($C$8:$C$37,$K$6,$D$8:$D$37,$A51,$T$8:$T$37,"EVIDENCE READY")=0),"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+      <x:c r="E51" s="107" t="str">
+        <x:f>IF(COUNTIF(B51:D51,"MISSING")&gt;0,"MISSING","READY")</x:f>
+        <x:v>MISSING</x:v>
+      </x:c>
+    </x:row>
     <x:row r="52" ht="30" customHeight="1">
       <x:c r="A52" s="104" t="str">
-        <x:v>The Phase 1 gate remains closed until every role has at least one evidence-ready entry for each of the three assigned clients. The client names in row 6 must match the Client column exactly.</x:v>
+        <x:v>The Phase 1 gate remains closed until every one of the five roles has at least one evidence-ready entry for each of the three assigned clients. The client names in row 6 must match the Client column exactly.</x:v>
       </x:c>
       <x:c r="B52" s="104"/>
       <x:c r="C52" s="104"/>
@@ -3050,7 +3089,7 @@
     <x:cfRule type="containsText" dxfId="25" priority="13" operator="containsText" text="MISSING"/>
     <x:cfRule type="containsText" dxfId="26" priority="14" operator="containsText" text="ENTER"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="B47:E50">
+  <x:conditionalFormatting sqref="B47:E51">
     <x:cfRule type="containsText" dxfId="27" priority="15" operator="containsText" text="EVIDENCE READY"/>
     <x:cfRule type="containsText" dxfId="28" priority="16" operator="containsText" text="REVISE"/>
     <x:cfRule type="containsText" dxfId="29" priority="17" operator="containsText" text="INCOMPLETE"/>
@@ -3061,7 +3100,7 @@
   </x:conditionalFormatting>
   <x:dataValidations count="5">
     <x:dataValidation type="list" sqref="D8:D37">
-      <x:formula1>"Client and Macro Strategist,Fixed-Income Analyst,Fund and ETF Analyst,Portfolio Manager and Risk Analyst"</x:formula1>
+      <x:formula1>"Client and Macro Strategist,Fixed-Income Analyst,Equity Analyst,Portfolio Manager,Risk and Derivatives Analyst"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="G8:G37">
       <x:formula1>"Low,Medium,High"</x:formula1>
@@ -3108,7 +3147,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Frame the Mandate | All four committee members review, vote, and sign this record.</x:v>
+        <x:v>Frame the Mandate | All five committee members review, vote, and sign this record.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -3361,7 +3400,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="114" t="str">
-        <x:v>Fund &amp; ETF</x:v>
+        <x:v>Equity</x:v>
       </x:c>
       <x:c r="B27" s="85" t="str"/>
       <x:c r="C27" s="86" t="str"/>
@@ -3372,21 +3411,32 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="114" t="str">
-        <x:v>Portfolio &amp; Risk</x:v>
-      </x:c>
-      <x:c r="B28" s="88" t="str"/>
-      <x:c r="C28" s="89" t="str"/>
-      <x:c r="D28" s="89" t="str"/>
-      <x:c r="E28" s="89" t="str"/>
-      <x:c r="F28" s="89" t="str"/>
-      <x:c r="G28" s="90" t="str"/>
+        <x:v>Portfolio Manager</x:v>
+      </x:c>
+      <x:c r="B28" s="85" t="str"/>
+      <x:c r="C28" s="86" t="str"/>
+      <x:c r="D28" s="86" t="str"/>
+      <x:c r="E28" s="86" t="str"/>
+      <x:c r="F28" s="86" t="str"/>
+      <x:c r="G28" s="87" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="114" t="str">
+        <x:v>Risk &amp; Derivatives</x:v>
+      </x:c>
+      <x:c r="B29" s="88" t="str"/>
+      <x:c r="C29" s="89" t="str"/>
+      <x:c r="D29" s="89" t="str"/>
+      <x:c r="E29" s="89" t="str"/>
+      <x:c r="F29" s="89" t="str"/>
+      <x:c r="G29" s="90" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="25" t="str">
         <x:v>Decision status</x:v>
       </x:c>
       <x:c r="B30" s="28" t="str">
-        <x:f>IF(COUNTIF(C25:C28,"Revise")+COUNTIF(C25:C28,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C28,"Approve")=4,"APPROVED","INCOMPLETE"))</x:f>
+        <x:f>IF(COUNTIF(C25:C29,"Revise")+COUNTIF(C25:C29,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C29,"Approve")=5,"APPROVED","INCOMPLETE"))</x:f>
         <x:v>INCOMPLETE</x:v>
       </x:c>
       <x:c r="C30" s="29"/>
@@ -3513,7 +3563,7 @@
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
       <x:c r="A44" s="104" t="str">
-        <x:v>Approval requires four Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
+        <x:v>Approval requires five Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
       </x:c>
       <x:c r="B44" s="104"/>
       <x:c r="C44" s="104"/>
@@ -3553,7 +3603,7 @@
     <x:dataValidation type="list" sqref="G10:G15">
       <x:formula1>"Not reviewed,Reviewed,Needs follow-up"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="C25:C28">
+    <x:dataValidation type="list" sqref="C25:C29">
       <x:formula1>"Approve,Revise,Reject"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="E38:E42">
@@ -3592,7 +3642,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Build &amp; Challenge | All four committee members review, vote, and sign this record.</x:v>
+        <x:v>Build &amp; Challenge | All five committee members review, vote, and sign this record.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -3845,7 +3895,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="114" t="str">
-        <x:v>Fund &amp; ETF</x:v>
+        <x:v>Equity</x:v>
       </x:c>
       <x:c r="B27" s="85" t="str"/>
       <x:c r="C27" s="86" t="str"/>
@@ -3856,21 +3906,32 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="114" t="str">
-        <x:v>Portfolio &amp; Risk</x:v>
-      </x:c>
-      <x:c r="B28" s="88" t="str"/>
-      <x:c r="C28" s="89" t="str"/>
-      <x:c r="D28" s="89" t="str"/>
-      <x:c r="E28" s="89" t="str"/>
-      <x:c r="F28" s="89" t="str"/>
-      <x:c r="G28" s="90" t="str"/>
+        <x:v>Portfolio Manager</x:v>
+      </x:c>
+      <x:c r="B28" s="85" t="str"/>
+      <x:c r="C28" s="86" t="str"/>
+      <x:c r="D28" s="86" t="str"/>
+      <x:c r="E28" s="86" t="str"/>
+      <x:c r="F28" s="86" t="str"/>
+      <x:c r="G28" s="87" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="114" t="str">
+        <x:v>Risk &amp; Derivatives</x:v>
+      </x:c>
+      <x:c r="B29" s="88" t="str"/>
+      <x:c r="C29" s="89" t="str"/>
+      <x:c r="D29" s="89" t="str"/>
+      <x:c r="E29" s="89" t="str"/>
+      <x:c r="F29" s="89" t="str"/>
+      <x:c r="G29" s="90" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="25" t="str">
         <x:v>Decision status</x:v>
       </x:c>
       <x:c r="B30" s="28" t="str">
-        <x:f>IF(COUNTIF(C25:C28,"Revise")+COUNTIF(C25:C28,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C28,"Approve")=4,"APPROVED","INCOMPLETE"))</x:f>
+        <x:f>IF(COUNTIF(C25:C29,"Revise")+COUNTIF(C25:C29,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C29,"Approve")=5,"APPROVED","INCOMPLETE"))</x:f>
         <x:v>INCOMPLETE</x:v>
       </x:c>
       <x:c r="C30" s="29"/>
@@ -3997,7 +4058,7 @@
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
       <x:c r="A44" s="104" t="str">
-        <x:v>Approval requires four Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
+        <x:v>Approval requires five Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
       </x:c>
       <x:c r="B44" s="104"/>
       <x:c r="C44" s="104"/>
@@ -4037,7 +4098,7 @@
     <x:dataValidation type="list" sqref="G10:G15">
       <x:formula1>"Not reviewed,Reviewed,Needs follow-up"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="C25:C28">
+    <x:dataValidation type="list" sqref="C25:C29">
       <x:formula1>"Approve,Revise,Reject"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="E38:E42">
@@ -4076,7 +4137,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Build &amp; Challenge | All four committee members review, vote, and sign this record.</x:v>
+        <x:v>Build &amp; Challenge | All five committee members review, vote, and sign this record.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -4329,7 +4390,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="114" t="str">
-        <x:v>Fund &amp; ETF</x:v>
+        <x:v>Equity</x:v>
       </x:c>
       <x:c r="B27" s="85" t="str"/>
       <x:c r="C27" s="86" t="str"/>
@@ -4340,21 +4401,32 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="114" t="str">
-        <x:v>Portfolio &amp; Risk</x:v>
-      </x:c>
-      <x:c r="B28" s="88" t="str"/>
-      <x:c r="C28" s="89" t="str"/>
-      <x:c r="D28" s="89" t="str"/>
-      <x:c r="E28" s="89" t="str"/>
-      <x:c r="F28" s="89" t="str"/>
-      <x:c r="G28" s="90" t="str"/>
+        <x:v>Portfolio Manager</x:v>
+      </x:c>
+      <x:c r="B28" s="85" t="str"/>
+      <x:c r="C28" s="86" t="str"/>
+      <x:c r="D28" s="86" t="str"/>
+      <x:c r="E28" s="86" t="str"/>
+      <x:c r="F28" s="86" t="str"/>
+      <x:c r="G28" s="87" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="114" t="str">
+        <x:v>Risk &amp; Derivatives</x:v>
+      </x:c>
+      <x:c r="B29" s="88" t="str"/>
+      <x:c r="C29" s="89" t="str"/>
+      <x:c r="D29" s="89" t="str"/>
+      <x:c r="E29" s="89" t="str"/>
+      <x:c r="F29" s="89" t="str"/>
+      <x:c r="G29" s="90" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="25" t="str">
         <x:v>Decision status</x:v>
       </x:c>
       <x:c r="B30" s="28" t="str">
-        <x:f>IF(COUNTIF(C25:C28,"Revise")+COUNTIF(C25:C28,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C28,"Approve")=4,"APPROVED","INCOMPLETE"))</x:f>
+        <x:f>IF(COUNTIF(C25:C29,"Revise")+COUNTIF(C25:C29,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C29,"Approve")=5,"APPROVED","INCOMPLETE"))</x:f>
         <x:v>INCOMPLETE</x:v>
       </x:c>
       <x:c r="C30" s="29"/>
@@ -4481,7 +4553,7 @@
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
       <x:c r="A44" s="104" t="str">
-        <x:v>Approval requires four Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
+        <x:v>Approval requires five Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
       </x:c>
       <x:c r="B44" s="104"/>
       <x:c r="C44" s="104"/>
@@ -4521,7 +4593,7 @@
     <x:dataValidation type="list" sqref="G10:G15">
       <x:formula1>"Not reviewed,Reviewed,Needs follow-up"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="C25:C28">
+    <x:dataValidation type="list" sqref="C25:C29">
       <x:formula1>"Approve,Revise,Reject"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="E38:E42">
@@ -4560,7 +4632,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Build &amp; Challenge | All four committee members review, vote, and sign this record.</x:v>
+        <x:v>Build &amp; Challenge | All five committee members review, vote, and sign this record.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -4813,7 +4885,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="114" t="str">
-        <x:v>Fund &amp; ETF</x:v>
+        <x:v>Equity</x:v>
       </x:c>
       <x:c r="B27" s="85" t="str"/>
       <x:c r="C27" s="86" t="str"/>
@@ -4824,21 +4896,32 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="114" t="str">
-        <x:v>Portfolio &amp; Risk</x:v>
-      </x:c>
-      <x:c r="B28" s="88" t="str"/>
-      <x:c r="C28" s="89" t="str"/>
-      <x:c r="D28" s="89" t="str"/>
-      <x:c r="E28" s="89" t="str"/>
-      <x:c r="F28" s="89" t="str"/>
-      <x:c r="G28" s="90" t="str"/>
+        <x:v>Portfolio Manager</x:v>
+      </x:c>
+      <x:c r="B28" s="85" t="str"/>
+      <x:c r="C28" s="86" t="str"/>
+      <x:c r="D28" s="86" t="str"/>
+      <x:c r="E28" s="86" t="str"/>
+      <x:c r="F28" s="86" t="str"/>
+      <x:c r="G28" s="87" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="114" t="str">
+        <x:v>Risk &amp; Derivatives</x:v>
+      </x:c>
+      <x:c r="B29" s="88" t="str"/>
+      <x:c r="C29" s="89" t="str"/>
+      <x:c r="D29" s="89" t="str"/>
+      <x:c r="E29" s="89" t="str"/>
+      <x:c r="F29" s="89" t="str"/>
+      <x:c r="G29" s="90" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="25" t="str">
         <x:v>Decision status</x:v>
       </x:c>
       <x:c r="B30" s="28" t="str">
-        <x:f>IF(COUNTIF(C25:C28,"Revise")+COUNTIF(C25:C28,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C28,"Approve")=4,"APPROVED","INCOMPLETE"))</x:f>
+        <x:f>IF(COUNTIF(C25:C29,"Revise")+COUNTIF(C25:C29,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C29,"Approve")=5,"APPROVED","INCOMPLETE"))</x:f>
         <x:v>INCOMPLETE</x:v>
       </x:c>
       <x:c r="C30" s="29"/>
@@ -4965,7 +5048,7 @@
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
       <x:c r="A44" s="104" t="str">
-        <x:v>Approval requires four Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
+        <x:v>Approval requires five Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
       </x:c>
       <x:c r="B44" s="104"/>
       <x:c r="C44" s="104"/>
@@ -5005,7 +5088,7 @@
     <x:dataValidation type="list" sqref="G10:G15">
       <x:formula1>"Not reviewed,Reviewed,Needs follow-up"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="C25:C28">
+    <x:dataValidation type="list" sqref="C25:C29">
       <x:formula1>"Approve,Revise,Reject"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="E38:E42">
@@ -5044,7 +5127,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Defend the Recommendation | All four committee members review, vote, and sign this record.</x:v>
+        <x:v>Defend the Recommendation | All five committee members review, vote, and sign this record.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -5297,7 +5380,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="114" t="str">
-        <x:v>Fund &amp; ETF</x:v>
+        <x:v>Equity</x:v>
       </x:c>
       <x:c r="B27" s="85" t="str"/>
       <x:c r="C27" s="86" t="str"/>
@@ -5308,21 +5391,32 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="114" t="str">
-        <x:v>Portfolio &amp; Risk</x:v>
-      </x:c>
-      <x:c r="B28" s="88" t="str"/>
-      <x:c r="C28" s="89" t="str"/>
-      <x:c r="D28" s="89" t="str"/>
-      <x:c r="E28" s="89" t="str"/>
-      <x:c r="F28" s="89" t="str"/>
-      <x:c r="G28" s="90" t="str"/>
+        <x:v>Portfolio Manager</x:v>
+      </x:c>
+      <x:c r="B28" s="85" t="str"/>
+      <x:c r="C28" s="86" t="str"/>
+      <x:c r="D28" s="86" t="str"/>
+      <x:c r="E28" s="86" t="str"/>
+      <x:c r="F28" s="86" t="str"/>
+      <x:c r="G28" s="87" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="114" t="str">
+        <x:v>Risk &amp; Derivatives</x:v>
+      </x:c>
+      <x:c r="B29" s="88" t="str"/>
+      <x:c r="C29" s="89" t="str"/>
+      <x:c r="D29" s="89" t="str"/>
+      <x:c r="E29" s="89" t="str"/>
+      <x:c r="F29" s="89" t="str"/>
+      <x:c r="G29" s="90" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="25" t="str">
         <x:v>Decision status</x:v>
       </x:c>
       <x:c r="B30" s="28" t="str">
-        <x:f>IF(COUNTIF(C25:C28,"Revise")+COUNTIF(C25:C28,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C28,"Approve")=4,"APPROVED","INCOMPLETE"))</x:f>
+        <x:f>IF(COUNTIF(C25:C29,"Revise")+COUNTIF(C25:C29,"Reject")&gt;0,"REVISION REQUIRED",IF(COUNTIF(C25:C29,"Approve")=5,"APPROVED","INCOMPLETE"))</x:f>
         <x:v>INCOMPLETE</x:v>
       </x:c>
       <x:c r="C30" s="29"/>
@@ -5449,7 +5543,7 @@
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
       <x:c r="A44" s="104" t="str">
-        <x:v>Approval requires four Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
+        <x:v>Approval requires five Approve votes. Any Revise or Reject vote produces REVISION REQUIRED; document the change and reconvene before the next gate.</x:v>
       </x:c>
       <x:c r="B44" s="104"/>
       <x:c r="C44" s="104"/>
@@ -5489,7 +5583,7 @@
     <x:dataValidation type="list" sqref="G10:G15">
       <x:formula1>"Not reviewed,Reviewed,Needs follow-up"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="C25:C28">
+    <x:dataValidation type="list" sqref="C25:C29">
       <x:formula1>"Approve,Revise,Reject"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="E38:E42">
